--- a/GESMS_전도영혼구원_표준자료양식_V3.0.xlsx
+++ b/GESMS_전도영혼구원_표준자료양식_V3.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500" activeTab="1"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500" activeTab="2"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="사용안내" sheetId="1" r:id="rId4"/>
@@ -23,9 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="234">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="238">
   <x:si>
     <x:t>송옥섭</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월 2회 무료급식 제공</x:t>
   </x:si>
   <x:si>
     <x:t>예수님 믿고 구원 받기를</x:t>
@@ -35,6 +38,9 @@
   </x:si>
   <x:si>
     <x:t>누나의 건강(암)이 회복되기를</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-004</x:t>
   </x:si>
   <x:si>
     <x:t>청년</x:t>
@@ -50,6 +56,12 @@
   </x:si>
   <x:si>
     <x:t>사랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 인근 노숙인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생수나눔 제공</x:t>
   </x:si>
   <x:si>
     <x:t>운영 팁: '진행상태'와 '다음연락일'을 꾸준히 갱신하면 앱의 전도현황이 정확해집니다.</x:t>
@@ -334,25 +346,19 @@
     <x:t>P-0004</x:t>
   </x:si>
   <x:si>
-    <x:t>지역 어르신 섬김과 관계 형성</x:t>
-  </x:si>
-  <x:si>
     <x:t>전도현황, 연락대상, 단계별 통계</x:t>
   </x:si>
   <x:si>
     <x:t>예산, 참여인원, 성과, 결과</x:t>
   </x:si>
   <x:si>
-    <x:t>월 1회 반찬 전달과 안부 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초청장 전달, 기도회, 예배 초청</x:t>
-  </x:si>
-  <x:si>
     <x:t>진행률, 분야별 현황, 성과 집계</x:t>
   </x:si>
   <x:si>
     <x:t>※ 한 사람당 한 행 작성 · 노란색 열은 필수 · 날짜는 YYYY-MM-DD 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 노숙인을 위한 봉사</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-003</x:t>
@@ -389,12 +395,6 @@
   </x:si>
   <x:si>
     <x:t>2026-08-01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도대상자 및 가족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도대상자 예배 초청</x:t>
   </x:si>
   <x:si>
     <x:t>대상지역/대상자</x:t>
@@ -685,10 +685,19 @@
     <x:t>첫만남</x:t>
   </x:si>
   <x:si>
+    <x:t>군포영문 인근 초등학생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역 초등생 무료 라면급식</x:t>
+  </x:si>
+  <x:si>
     <x:t>사회복지</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레드쉴드 라면Day</x:t>
   </x:si>
   <x:si>
     <x:t>무료급식</x:t>
@@ -718,13 +727,16 @@
     <x:t>김문희</x:t>
   </x:si>
   <x:si>
+    <x:t>월 2회 토요일 라면 제공</x:t>
+  </x:si>
+  <x:si>
     <x:t>생수나눔 봉사</x:t>
   </x:si>
   <x:si>
     <x:t>고향 친구</x:t>
   </x:si>
   <x:si>
-    <x:t>수원역</x:t>
+    <x:t>미정</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1364,7 +1376,7 @@
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
     <x:cellStyle name="Normal" xfId="1"/>
   </x:cellStyles>
-  <x:dxfs count="21">
+  <x:dxfs count="23">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
@@ -2039,6 +2051,126 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:sz val="10"/>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:bgColor rgb="ff2e6f95"/>
+            </x:patternFill>
+          </x:fill>
+          <x:alignment horizontal="center" wrapText="1"/>
+          <x:border>
+            <x:left>
+              <x:color indexed="64"/>
+            </x:left>
+            <x:right>
+              <x:color indexed="64"/>
+            </x:right>
+            <x:top>
+              <x:color indexed="64"/>
+            </x:top>
+            <x:bottom>
+              <x:color indexed="64"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:sz val="10"/>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:bgColor rgb="ff2e6f95"/>
+            </x:patternFill>
+          </x:fill>
+          <x:alignment horizontal="center" wrapText="1"/>
+          <x:border>
+            <x:left>
+              <x:color indexed="64"/>
+            </x:left>
+            <x:right>
+              <x:color indexed="64"/>
+            </x:right>
+            <x:top>
+              <x:color indexed="64"/>
+            </x:top>
+            <x:bottom>
+              <x:color indexed="64"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:sz val="10"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+          <x:border>
+            <x:left>
+              <x:color indexed="64"/>
+            </x:left>
+            <x:right>
+              <x:color indexed="64"/>
+            </x:right>
+            <x:top>
+              <x:color indexed="64"/>
+            </x:top>
+            <x:bottom>
+              <x:color indexed="64"/>
+            </x:bottom>
+            <x:horizontal>
+              <x:color indexed="64"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:sz val="10"/>
+          </x:font>
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+          <x:border>
+            <x:left>
+              <x:color indexed="64"/>
+            </x:left>
+            <x:right>
+              <x:color indexed="64"/>
+            </x:right>
+            <x:top>
+              <x:color indexed="64"/>
+            </x:top>
+            <x:bottom>
+              <x:color indexed="64"/>
+            </x:bottom>
+            <x:horizontal>
+              <x:color indexed="64"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="Normal Style 1 - Accent 1" defaultPivotStyle="Light Style 1 - Accent 1">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -2066,7 +2198,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:date1904 val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -2278,7 +2410,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:date1904 val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -2351,13 +2483,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2466,7 +2598,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2546,7 +2678,7 @@
     <x:tableColumn id="10" name="기도제목상세"/>
     <x:tableColumn id="11" name="기도시작일" dataDxfId="17"/>
     <x:tableColumn id="12" name="진행상태" dataDxfId="16"/>
-    <x:tableColumn id="13" name="기도중"/>
+    <x:tableColumn id="13" name="기도중" dataDxfId="22"/>
     <x:tableColumn id="14" name="관계형성" dataDxfId="13"/>
     <x:tableColumn id="15" name="첫만남" dataDxfId="13"/>
     <x:tableColumn id="16" name="초청" dataDxfId="13"/>
@@ -2929,25 +3061,25 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I4" s="2"/>
       <x:c r="J4" s="2"/>
@@ -2996,22 +3128,22 @@
     </x:row>
     <x:row r="5" spans="1:52" ht="26.350000000000001">
       <x:c r="A5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
         <x:v>182</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
         <x:v>184</x:v>
@@ -3066,10 +3198,10 @@
     </x:row>
     <x:row r="6" spans="1:52" ht="26.350000000000001">
       <x:c r="A6" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
         <x:v>136</x:v>
@@ -3078,16 +3210,16 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="2"/>
@@ -3136,10 +3268,10 @@
     </x:row>
     <x:row r="7" spans="1:52" ht="26.350000000000001">
       <x:c r="A7" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
         <x:v>132</x:v>
@@ -3148,16 +3280,16 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="2"/>
@@ -3260,7 +3392,7 @@
     </x:row>
     <x:row r="9" spans="1:52">
       <x:c r="A9" s="34" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="34"/>
       <x:c r="C9" s="34"/>
@@ -3551,7 +3683,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C14" s="2"/>
       <x:c r="D14" s="2"/>
@@ -14755,8 +14887,7 @@
     <x:col min="9" max="9" width="14" style="15" customWidth="1"/>
     <x:col min="10" max="10" width="45.08984375" style="1" customWidth="1"/>
     <x:col min="11" max="12" width="13" style="15" customWidth="1"/>
-    <x:col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <x:col min="14" max="16" width="9" style="15" customWidth="1"/>
+    <x:col min="13" max="16" width="9" style="15" customWidth="1"/>
     <x:col min="17" max="17" width="10" style="15" customWidth="1"/>
     <x:col min="18" max="18" width="9" style="15" customWidth="1"/>
     <x:col min="19" max="20" width="10" style="15" customWidth="1"/>
@@ -14770,7 +14901,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:52">
       <x:c r="A1" s="32" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" s="32"/>
       <x:c r="C1" s="32"/>
@@ -14880,7 +15011,7 @@
     </x:row>
     <x:row r="3" spans="1:52">
       <x:c r="A3" s="33" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B3" s="33"/>
       <x:c r="C3" s="33"/>
@@ -14936,7 +15067,7 @@
     </x:row>
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="19" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="19" t="s">
         <x:v>148</x:v>
@@ -14948,34 +15079,34 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G4" s="18" t="s">
         <x:v>167</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J4" s="19" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L4" s="19" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
         <x:v>168</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
         <x:v>219</x:v>
@@ -14984,46 +15115,46 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="U4" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="V4" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W4" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="X4" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="Y4" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Z4" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AA4" s="3" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="T4" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="U4" s="3" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="V4" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="W4" s="3" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="X4" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Y4" s="3" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="Z4" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AA4" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="AB4" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="AC4" s="3" t="s">
         <x:v>154</x:v>
       </x:c>
       <x:c r="AD4" s="19" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AE4" s="2"/>
       <x:c r="AF4" s="2"/>
@@ -15050,7 +15181,7 @@
     </x:row>
     <x:row r="5" spans="1:52">
       <x:c r="A5" s="7" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="20" t="s">
         <x:v>191</x:v>
@@ -15075,7 +15206,7 @@
       <x:c r="L5" s="31" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M5" s="6"/>
+      <x:c r="M5" s="16"/>
       <x:c r="N5" s="16"/>
       <x:c r="O5" s="16"/>
       <x:c r="P5" s="16"/>
@@ -15118,7 +15249,7 @@
     </x:row>
     <x:row r="6" spans="1:52">
       <x:c r="A6" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
         <x:v>205</x:v>
@@ -15131,10 +15262,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="F6" s="16" t="s">
-        <x:v>232</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G6" s="23" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H6" s="16" t="s">
         <x:v>180</x:v>
@@ -15143,7 +15274,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K6" s="24">
         <x:v>45809</x:v>
@@ -15151,9 +15282,7 @@
       <x:c r="L6" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M6" s="6" t="s">
-        <x:v>161</x:v>
-      </x:c>
+      <x:c r="M6" s="16"/>
       <x:c r="N6" s="16"/>
       <x:c r="O6" s="16"/>
       <x:c r="P6" s="16"/>
@@ -15196,7 +15325,7 @@
     </x:row>
     <x:row r="7" spans="1:52">
       <x:c r="A7" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B7" s="20" t="s">
         <x:v>208</x:v>
@@ -15221,7 +15350,7 @@
       <x:c r="L7" s="31" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M7" s="6"/>
+      <x:c r="M7" s="16"/>
       <x:c r="N7" s="16"/>
       <x:c r="O7" s="16"/>
       <x:c r="P7" s="16"/>
@@ -15264,7 +15393,7 @@
     </x:row>
     <x:row r="8" spans="1:52">
       <x:c r="A8" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
         <x:v>174</x:v>
@@ -15280,7 +15409,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="G8" s="23" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H8" s="16" t="s">
         <x:v>180</x:v>
@@ -15289,7 +15418,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="24">
         <x:v>43831</x:v>
@@ -15297,7 +15426,7 @@
       <x:c r="L8" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M8" s="6"/>
+      <x:c r="M8" s="16"/>
       <x:c r="N8" s="16"/>
       <x:c r="O8" s="16"/>
       <x:c r="P8" s="16"/>
@@ -15342,7 +15471,7 @@
     </x:row>
     <x:row r="9" spans="1:52">
       <x:c r="A9" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B9" s="20" t="s">
         <x:v>209</x:v>
@@ -15367,7 +15496,7 @@
       <x:c r="L9" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M9" s="6"/>
+      <x:c r="M9" s="16"/>
       <x:c r="N9" s="16"/>
       <x:c r="O9" s="16"/>
       <x:c r="P9" s="16"/>
@@ -15410,7 +15539,7 @@
     </x:row>
     <x:row r="10" spans="1:52">
       <x:c r="A10" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
         <x:v>190</x:v>
@@ -15435,7 +15564,7 @@
       <x:c r="L10" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M10" s="6"/>
+      <x:c r="M10" s="16"/>
       <x:c r="N10" s="16"/>
       <x:c r="O10" s="16"/>
       <x:c r="P10" s="16"/>
@@ -15478,7 +15607,7 @@
     </x:row>
     <x:row r="11" spans="1:52">
       <x:c r="A11" s="7" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B11" s="20" t="s">
         <x:v>179</x:v>
@@ -15503,7 +15632,7 @@
       <x:c r="L11" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M11" s="6"/>
+      <x:c r="M11" s="16"/>
       <x:c r="N11" s="16"/>
       <x:c r="O11" s="16"/>
       <x:c r="P11" s="16"/>
@@ -15546,7 +15675,7 @@
     </x:row>
     <x:row r="12" spans="1:52">
       <x:c r="A12" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
         <x:v>206</x:v>
@@ -15559,10 +15688,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="F12" s="16" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G12" s="23" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H12" s="16" t="s">
         <x:v>180</x:v>
@@ -15571,7 +15700,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K12" s="24">
         <x:v>42860</x:v>
@@ -15579,9 +15708,7 @@
       <x:c r="L12" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M12" s="6" t="s">
-        <x:v>161</x:v>
-      </x:c>
+      <x:c r="M12" s="16"/>
       <x:c r="N12" s="16"/>
       <x:c r="O12" s="16"/>
       <x:c r="P12" s="16"/>
@@ -15624,7 +15751,7 @@
     </x:row>
     <x:row r="13" spans="1:52">
       <x:c r="A13" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="20" t="s">
         <x:v>199</x:v>
@@ -15649,7 +15776,7 @@
       <x:c r="L13" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M13" s="6"/>
+      <x:c r="M13" s="16"/>
       <x:c r="N13" s="16"/>
       <x:c r="O13" s="16"/>
       <x:c r="P13" s="16"/>
@@ -15692,7 +15819,7 @@
     </x:row>
     <x:row r="14" spans="1:52">
       <x:c r="A14" s="7" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B14" s="21" t="s">
         <x:v>188</x:v>
@@ -15705,10 +15832,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="F14" s="16" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G14" s="23" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H14" s="16" t="s">
         <x:v>180</x:v>
@@ -15723,7 +15850,7 @@
       <x:c r="L14" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M14" s="6"/>
+      <x:c r="M14" s="16"/>
       <x:c r="N14" s="16"/>
       <x:c r="O14" s="16"/>
       <x:c r="P14" s="16"/>
@@ -15766,7 +15893,7 @@
     </x:row>
     <x:row r="15" spans="1:52">
       <x:c r="A15" s="7" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B15" s="20" t="s">
         <x:v>177</x:v>
@@ -15791,7 +15918,7 @@
       <x:c r="L15" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M15" s="6"/>
+      <x:c r="M15" s="16"/>
       <x:c r="N15" s="16"/>
       <x:c r="O15" s="16"/>
       <x:c r="P15" s="16"/>
@@ -15834,7 +15961,7 @@
     </x:row>
     <x:row r="16" spans="1:52">
       <x:c r="A16" s="7" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B16" s="21" t="s">
         <x:v>187</x:v>
@@ -15847,10 +15974,10 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="F16" s="16" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G16" s="23" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H16" s="16" t="s">
         <x:v>180</x:v>
@@ -15867,7 +15994,7 @@
       <x:c r="L16" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M16" s="6"/>
+      <x:c r="M16" s="16"/>
       <x:c r="N16" s="16"/>
       <x:c r="O16" s="16"/>
       <x:c r="P16" s="16"/>
@@ -15910,7 +16037,7 @@
     </x:row>
     <x:row r="17" spans="1:52">
       <x:c r="A17" s="7" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B17" s="20" t="s">
         <x:v>176</x:v>
@@ -15935,7 +16062,7 @@
       <x:c r="L17" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M17" s="6"/>
+      <x:c r="M17" s="16"/>
       <x:c r="N17" s="16"/>
       <x:c r="O17" s="16"/>
       <x:c r="P17" s="16"/>
@@ -15978,7 +16105,7 @@
     </x:row>
     <x:row r="18" spans="1:52">
       <x:c r="A18" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B18" s="21" t="s">
         <x:v>201</x:v>
@@ -16003,7 +16130,7 @@
       <x:c r="L18" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M18" s="6"/>
+      <x:c r="M18" s="16"/>
       <x:c r="N18" s="16"/>
       <x:c r="O18" s="16"/>
       <x:c r="P18" s="16"/>
@@ -16046,7 +16173,7 @@
     </x:row>
     <x:row r="19" spans="1:52">
       <x:c r="A19" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B19" s="20" t="s">
         <x:v>203</x:v>
@@ -16059,10 +16186,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="F19" s="16" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="23" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H19" s="16" t="s">
         <x:v>180</x:v>
@@ -16071,7 +16198,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="J19" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K19" s="24">
         <x:v>44228</x:v>
@@ -16079,9 +16206,7 @@
       <x:c r="L19" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M19" s="6" t="s">
-        <x:v>161</x:v>
-      </x:c>
+      <x:c r="M19" s="16"/>
       <x:c r="N19" s="16"/>
       <x:c r="O19" s="16"/>
       <x:c r="P19" s="16"/>
@@ -16124,7 +16249,7 @@
     </x:row>
     <x:row r="20" spans="1:52">
       <x:c r="A20" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B20" s="21" t="s">
         <x:v>210</x:v>
@@ -16149,7 +16274,7 @@
       <x:c r="L20" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M20" s="6"/>
+      <x:c r="M20" s="16"/>
       <x:c r="N20" s="16"/>
       <x:c r="O20" s="16"/>
       <x:c r="P20" s="16"/>
@@ -16192,7 +16317,7 @@
     </x:row>
     <x:row r="21" spans="1:52">
       <x:c r="A21" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B21" s="20" t="s">
         <x:v>202</x:v>
@@ -16217,7 +16342,7 @@
       <x:c r="L21" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M21" s="6"/>
+      <x:c r="M21" s="16"/>
       <x:c r="N21" s="16"/>
       <x:c r="O21" s="16"/>
       <x:c r="P21" s="16"/>
@@ -16260,7 +16385,7 @@
     </x:row>
     <x:row r="22" spans="1:52">
       <x:c r="A22" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="21" t="s">
         <x:v>204</x:v>
@@ -16285,7 +16410,7 @@
       <x:c r="L22" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M22" s="6"/>
+      <x:c r="M22" s="16"/>
       <x:c r="N22" s="16"/>
       <x:c r="O22" s="16"/>
       <x:c r="P22" s="16"/>
@@ -16328,7 +16453,7 @@
     </x:row>
     <x:row r="23" spans="1:52">
       <x:c r="A23" s="7" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="20" t="s">
         <x:v>178</x:v>
@@ -16353,7 +16478,7 @@
       <x:c r="L23" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M23" s="6"/>
+      <x:c r="M23" s="16"/>
       <x:c r="N23" s="16"/>
       <x:c r="O23" s="16"/>
       <x:c r="P23" s="16"/>
@@ -16396,7 +16521,7 @@
     </x:row>
     <x:row r="24" spans="1:52">
       <x:c r="A24" s="7" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B24" s="21" t="s">
         <x:v>197</x:v>
@@ -16421,7 +16546,7 @@
       <x:c r="L24" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M24" s="6"/>
+      <x:c r="M24" s="16"/>
       <x:c r="N24" s="16"/>
       <x:c r="O24" s="16"/>
       <x:c r="P24" s="16"/>
@@ -16464,10 +16589,10 @@
     </x:row>
     <x:row r="25" spans="1:52">
       <x:c r="A25" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B25" s="20" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
         <x:v>149</x:v>
@@ -16489,7 +16614,7 @@
       <x:c r="L25" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M25" s="6"/>
+      <x:c r="M25" s="16"/>
       <x:c r="N25" s="16"/>
       <x:c r="O25" s="16"/>
       <x:c r="P25" s="16"/>
@@ -16532,7 +16657,7 @@
     </x:row>
     <x:row r="26" spans="1:52">
       <x:c r="A26" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B26" s="21" t="s">
         <x:v>173</x:v>
@@ -16557,7 +16682,7 @@
       <x:c r="L26" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M26" s="6"/>
+      <x:c r="M26" s="16"/>
       <x:c r="N26" s="16"/>
       <x:c r="O26" s="16"/>
       <x:c r="P26" s="16"/>
@@ -16600,7 +16725,7 @@
     </x:row>
     <x:row r="27" spans="1:52">
       <x:c r="A27" s="7" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B27" s="20" t="s">
         <x:v>189</x:v>
@@ -16625,7 +16750,7 @@
       <x:c r="L27" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M27" s="6"/>
+      <x:c r="M27" s="16"/>
       <x:c r="N27" s="16"/>
       <x:c r="O27" s="16"/>
       <x:c r="P27" s="16"/>
@@ -16668,7 +16793,7 @@
     </x:row>
     <x:row r="28" spans="1:52">
       <x:c r="A28" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B28" s="21" t="s">
         <x:v>186</x:v>
@@ -16693,7 +16818,7 @@
       <x:c r="L28" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M28" s="6"/>
+      <x:c r="M28" s="16"/>
       <x:c r="N28" s="16"/>
       <x:c r="O28" s="16"/>
       <x:c r="P28" s="16"/>
@@ -16736,7 +16861,7 @@
     </x:row>
     <x:row r="29" spans="1:52">
       <x:c r="A29" s="7" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B29" s="20" t="s">
         <x:v>207</x:v>
@@ -16761,7 +16886,7 @@
       <x:c r="L29" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M29" s="6"/>
+      <x:c r="M29" s="16"/>
       <x:c r="N29" s="16"/>
       <x:c r="O29" s="16"/>
       <x:c r="P29" s="16"/>
@@ -16804,7 +16929,7 @@
     </x:row>
     <x:row r="30" spans="1:52">
       <x:c r="A30" s="7" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B30" s="21" t="s">
         <x:v>175</x:v>
@@ -16829,7 +16954,7 @@
       <x:c r="L30" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M30" s="6"/>
+      <x:c r="M30" s="16"/>
       <x:c r="N30" s="16"/>
       <x:c r="O30" s="16"/>
       <x:c r="P30" s="16"/>
@@ -16872,7 +16997,7 @@
     </x:row>
     <x:row r="31" spans="1:52">
       <x:c r="A31" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="20" t="s">
         <x:v>194</x:v>
@@ -16897,7 +17022,7 @@
       <x:c r="L31" s="23" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="M31" s="6"/>
+      <x:c r="M31" s="16"/>
       <x:c r="N31" s="16"/>
       <x:c r="O31" s="16"/>
       <x:c r="P31" s="16"/>
@@ -16951,7 +17076,7 @@
       <x:c r="J32" s="7"/>
       <x:c r="K32" s="24"/>
       <x:c r="L32" s="23"/>
-      <x:c r="M32" s="6"/>
+      <x:c r="M32" s="16"/>
       <x:c r="N32" s="16"/>
       <x:c r="O32" s="16"/>
       <x:c r="P32" s="16"/>
@@ -17005,7 +17130,7 @@
       <x:c r="J33" s="7"/>
       <x:c r="K33" s="24"/>
       <x:c r="L33" s="23"/>
-      <x:c r="M33" s="6"/>
+      <x:c r="M33" s="16"/>
       <x:c r="N33" s="16"/>
       <x:c r="O33" s="16"/>
       <x:c r="P33" s="16"/>
@@ -17059,7 +17184,7 @@
       <x:c r="J34" s="7"/>
       <x:c r="K34" s="24"/>
       <x:c r="L34" s="23"/>
-      <x:c r="M34" s="6"/>
+      <x:c r="M34" s="16"/>
       <x:c r="N34" s="16"/>
       <x:c r="O34" s="16"/>
       <x:c r="P34" s="16"/>
@@ -17113,7 +17238,7 @@
       <x:c r="J35" s="7"/>
       <x:c r="K35" s="24"/>
       <x:c r="L35" s="23"/>
-      <x:c r="M35" s="6"/>
+      <x:c r="M35" s="16"/>
       <x:c r="N35" s="16"/>
       <x:c r="O35" s="16"/>
       <x:c r="P35" s="16"/>
@@ -17167,7 +17292,7 @@
       <x:c r="J36" s="7"/>
       <x:c r="K36" s="24"/>
       <x:c r="L36" s="23"/>
-      <x:c r="M36" s="6"/>
+      <x:c r="M36" s="16"/>
       <x:c r="N36" s="16"/>
       <x:c r="O36" s="16"/>
       <x:c r="P36" s="16"/>
@@ -17221,7 +17346,7 @@
       <x:c r="J37" s="7"/>
       <x:c r="K37" s="24"/>
       <x:c r="L37" s="23"/>
-      <x:c r="M37" s="6"/>
+      <x:c r="M37" s="16"/>
       <x:c r="N37" s="16"/>
       <x:c r="O37" s="16"/>
       <x:c r="P37" s="16"/>
@@ -17275,7 +17400,7 @@
       <x:c r="J38" s="7"/>
       <x:c r="K38" s="24"/>
       <x:c r="L38" s="23"/>
-      <x:c r="M38" s="6"/>
+      <x:c r="M38" s="16"/>
       <x:c r="N38" s="16"/>
       <x:c r="O38" s="16"/>
       <x:c r="P38" s="16"/>
@@ -17329,7 +17454,7 @@
       <x:c r="J39" s="7"/>
       <x:c r="K39" s="24"/>
       <x:c r="L39" s="23"/>
-      <x:c r="M39" s="6"/>
+      <x:c r="M39" s="16"/>
       <x:c r="N39" s="16"/>
       <x:c r="O39" s="16"/>
       <x:c r="P39" s="16"/>
@@ -17383,7 +17508,7 @@
       <x:c r="J40" s="7"/>
       <x:c r="K40" s="24"/>
       <x:c r="L40" s="23"/>
-      <x:c r="M40" s="6"/>
+      <x:c r="M40" s="16"/>
       <x:c r="N40" s="16"/>
       <x:c r="O40" s="16"/>
       <x:c r="P40" s="16"/>
@@ -17437,7 +17562,7 @@
       <x:c r="J41" s="7"/>
       <x:c r="K41" s="24"/>
       <x:c r="L41" s="23"/>
-      <x:c r="M41" s="6"/>
+      <x:c r="M41" s="16"/>
       <x:c r="N41" s="16"/>
       <x:c r="O41" s="16"/>
       <x:c r="P41" s="16"/>
@@ -17491,7 +17616,7 @@
       <x:c r="J42" s="7"/>
       <x:c r="K42" s="24"/>
       <x:c r="L42" s="23"/>
-      <x:c r="M42" s="6"/>
+      <x:c r="M42" s="16"/>
       <x:c r="N42" s="16"/>
       <x:c r="O42" s="16"/>
       <x:c r="P42" s="16"/>
@@ -17545,7 +17670,7 @@
       <x:c r="J43" s="7"/>
       <x:c r="K43" s="24"/>
       <x:c r="L43" s="23"/>
-      <x:c r="M43" s="6"/>
+      <x:c r="M43" s="16"/>
       <x:c r="N43" s="16"/>
       <x:c r="O43" s="16"/>
       <x:c r="P43" s="16"/>
@@ -17599,7 +17724,7 @@
       <x:c r="J44" s="7"/>
       <x:c r="K44" s="24"/>
       <x:c r="L44" s="23"/>
-      <x:c r="M44" s="6"/>
+      <x:c r="M44" s="16"/>
       <x:c r="N44" s="16"/>
       <x:c r="O44" s="16"/>
       <x:c r="P44" s="16"/>
@@ -17653,7 +17778,7 @@
       <x:c r="J45" s="7"/>
       <x:c r="K45" s="24"/>
       <x:c r="L45" s="23"/>
-      <x:c r="M45" s="6"/>
+      <x:c r="M45" s="16"/>
       <x:c r="N45" s="16"/>
       <x:c r="O45" s="16"/>
       <x:c r="P45" s="16"/>
@@ -17707,7 +17832,7 @@
       <x:c r="J46" s="7"/>
       <x:c r="K46" s="24"/>
       <x:c r="L46" s="23"/>
-      <x:c r="M46" s="6"/>
+      <x:c r="M46" s="16"/>
       <x:c r="N46" s="16"/>
       <x:c r="O46" s="16"/>
       <x:c r="P46" s="16"/>
@@ -17761,7 +17886,7 @@
       <x:c r="J47" s="7"/>
       <x:c r="K47" s="24"/>
       <x:c r="L47" s="23"/>
-      <x:c r="M47" s="6"/>
+      <x:c r="M47" s="16"/>
       <x:c r="N47" s="16"/>
       <x:c r="O47" s="16"/>
       <x:c r="P47" s="16"/>
@@ -17815,7 +17940,7 @@
       <x:c r="J48" s="7"/>
       <x:c r="K48" s="24"/>
       <x:c r="L48" s="23"/>
-      <x:c r="M48" s="6"/>
+      <x:c r="M48" s="16"/>
       <x:c r="N48" s="16"/>
       <x:c r="O48" s="16"/>
       <x:c r="P48" s="16"/>
@@ -17869,7 +17994,7 @@
       <x:c r="J49" s="7"/>
       <x:c r="K49" s="24"/>
       <x:c r="L49" s="23"/>
-      <x:c r="M49" s="6"/>
+      <x:c r="M49" s="16"/>
       <x:c r="N49" s="16"/>
       <x:c r="O49" s="16"/>
       <x:c r="P49" s="16"/>
@@ -17923,7 +18048,7 @@
       <x:c r="J50" s="7"/>
       <x:c r="K50" s="24"/>
       <x:c r="L50" s="23"/>
-      <x:c r="M50" s="6"/>
+      <x:c r="M50" s="16"/>
       <x:c r="N50" s="16"/>
       <x:c r="O50" s="16"/>
       <x:c r="P50" s="16"/>
@@ -17977,7 +18102,7 @@
       <x:c r="J51" s="7"/>
       <x:c r="K51" s="24"/>
       <x:c r="L51" s="23"/>
-      <x:c r="M51" s="6"/>
+      <x:c r="M51" s="16"/>
       <x:c r="N51" s="16"/>
       <x:c r="O51" s="16"/>
       <x:c r="P51" s="16"/>
@@ -18031,7 +18156,7 @@
       <x:c r="J52" s="7"/>
       <x:c r="K52" s="24"/>
       <x:c r="L52" s="23"/>
-      <x:c r="M52" s="6"/>
+      <x:c r="M52" s="16"/>
       <x:c r="N52" s="16"/>
       <x:c r="O52" s="16"/>
       <x:c r="P52" s="16"/>
@@ -18085,7 +18210,7 @@
       <x:c r="J53" s="7"/>
       <x:c r="K53" s="24"/>
       <x:c r="L53" s="23"/>
-      <x:c r="M53" s="6"/>
+      <x:c r="M53" s="16"/>
       <x:c r="N53" s="16"/>
       <x:c r="O53" s="16"/>
       <x:c r="P53" s="16"/>
@@ -18139,7 +18264,7 @@
       <x:c r="J54" s="7"/>
       <x:c r="K54" s="24"/>
       <x:c r="L54" s="23"/>
-      <x:c r="M54" s="6"/>
+      <x:c r="M54" s="16"/>
       <x:c r="N54" s="16"/>
       <x:c r="O54" s="16"/>
       <x:c r="P54" s="16"/>
@@ -18193,7 +18318,7 @@
       <x:c r="J55" s="7"/>
       <x:c r="K55" s="24"/>
       <x:c r="L55" s="23"/>
-      <x:c r="M55" s="6"/>
+      <x:c r="M55" s="16"/>
       <x:c r="N55" s="16"/>
       <x:c r="O55" s="16"/>
       <x:c r="P55" s="16"/>
@@ -18247,7 +18372,7 @@
       <x:c r="J56" s="7"/>
       <x:c r="K56" s="24"/>
       <x:c r="L56" s="23"/>
-      <x:c r="M56" s="6"/>
+      <x:c r="M56" s="16"/>
       <x:c r="N56" s="16"/>
       <x:c r="O56" s="16"/>
       <x:c r="P56" s="16"/>
@@ -18301,7 +18426,7 @@
       <x:c r="J57" s="7"/>
       <x:c r="K57" s="24"/>
       <x:c r="L57" s="23"/>
-      <x:c r="M57" s="6"/>
+      <x:c r="M57" s="16"/>
       <x:c r="N57" s="16"/>
       <x:c r="O57" s="16"/>
       <x:c r="P57" s="16"/>
@@ -18355,7 +18480,7 @@
       <x:c r="J58" s="7"/>
       <x:c r="K58" s="24"/>
       <x:c r="L58" s="23"/>
-      <x:c r="M58" s="6"/>
+      <x:c r="M58" s="16"/>
       <x:c r="N58" s="16"/>
       <x:c r="O58" s="16"/>
       <x:c r="P58" s="16"/>
@@ -18409,7 +18534,7 @@
       <x:c r="J59" s="7"/>
       <x:c r="K59" s="24"/>
       <x:c r="L59" s="23"/>
-      <x:c r="M59" s="6"/>
+      <x:c r="M59" s="16"/>
       <x:c r="N59" s="16"/>
       <x:c r="O59" s="16"/>
       <x:c r="P59" s="16"/>
@@ -18463,7 +18588,7 @@
       <x:c r="J60" s="7"/>
       <x:c r="K60" s="24"/>
       <x:c r="L60" s="23"/>
-      <x:c r="M60" s="6"/>
+      <x:c r="M60" s="16"/>
       <x:c r="N60" s="16"/>
       <x:c r="O60" s="16"/>
       <x:c r="P60" s="16"/>
@@ -18517,7 +18642,7 @@
       <x:c r="J61" s="7"/>
       <x:c r="K61" s="24"/>
       <x:c r="L61" s="23"/>
-      <x:c r="M61" s="6"/>
+      <x:c r="M61" s="16"/>
       <x:c r="N61" s="16"/>
       <x:c r="O61" s="16"/>
       <x:c r="P61" s="16"/>
@@ -18571,7 +18696,7 @@
       <x:c r="J62" s="7"/>
       <x:c r="K62" s="24"/>
       <x:c r="L62" s="23"/>
-      <x:c r="M62" s="6"/>
+      <x:c r="M62" s="16"/>
       <x:c r="N62" s="16"/>
       <x:c r="O62" s="16"/>
       <x:c r="P62" s="16"/>
@@ -18625,7 +18750,7 @@
       <x:c r="J63" s="7"/>
       <x:c r="K63" s="24"/>
       <x:c r="L63" s="23"/>
-      <x:c r="M63" s="6"/>
+      <x:c r="M63" s="16"/>
       <x:c r="N63" s="16"/>
       <x:c r="O63" s="16"/>
       <x:c r="P63" s="16"/>
@@ -18679,7 +18804,7 @@
       <x:c r="J64" s="7"/>
       <x:c r="K64" s="24"/>
       <x:c r="L64" s="23"/>
-      <x:c r="M64" s="6"/>
+      <x:c r="M64" s="16"/>
       <x:c r="N64" s="16"/>
       <x:c r="O64" s="16"/>
       <x:c r="P64" s="16"/>
@@ -18733,7 +18858,7 @@
       <x:c r="J65" s="7"/>
       <x:c r="K65" s="24"/>
       <x:c r="L65" s="23"/>
-      <x:c r="M65" s="6"/>
+      <x:c r="M65" s="16"/>
       <x:c r="N65" s="16"/>
       <x:c r="O65" s="16"/>
       <x:c r="P65" s="16"/>
@@ -18787,7 +18912,7 @@
       <x:c r="J66" s="7"/>
       <x:c r="K66" s="24"/>
       <x:c r="L66" s="23"/>
-      <x:c r="M66" s="6"/>
+      <x:c r="M66" s="16"/>
       <x:c r="N66" s="16"/>
       <x:c r="O66" s="16"/>
       <x:c r="P66" s="16"/>
@@ -18841,7 +18966,7 @@
       <x:c r="J67" s="7"/>
       <x:c r="K67" s="24"/>
       <x:c r="L67" s="23"/>
-      <x:c r="M67" s="6"/>
+      <x:c r="M67" s="16"/>
       <x:c r="N67" s="16"/>
       <x:c r="O67" s="16"/>
       <x:c r="P67" s="16"/>
@@ -18895,7 +19020,7 @@
       <x:c r="J68" s="7"/>
       <x:c r="K68" s="24"/>
       <x:c r="L68" s="23"/>
-      <x:c r="M68" s="6"/>
+      <x:c r="M68" s="16"/>
       <x:c r="N68" s="16"/>
       <x:c r="O68" s="16"/>
       <x:c r="P68" s="16"/>
@@ -18949,7 +19074,7 @@
       <x:c r="J69" s="7"/>
       <x:c r="K69" s="24"/>
       <x:c r="L69" s="23"/>
-      <x:c r="M69" s="6"/>
+      <x:c r="M69" s="16"/>
       <x:c r="N69" s="16"/>
       <x:c r="O69" s="16"/>
       <x:c r="P69" s="16"/>
@@ -19003,7 +19128,7 @@
       <x:c r="J70" s="7"/>
       <x:c r="K70" s="24"/>
       <x:c r="L70" s="23"/>
-      <x:c r="M70" s="6"/>
+      <x:c r="M70" s="16"/>
       <x:c r="N70" s="16"/>
       <x:c r="O70" s="16"/>
       <x:c r="P70" s="16"/>
@@ -19057,7 +19182,7 @@
       <x:c r="J71" s="7"/>
       <x:c r="K71" s="24"/>
       <x:c r="L71" s="23"/>
-      <x:c r="M71" s="6"/>
+      <x:c r="M71" s="16"/>
       <x:c r="N71" s="16"/>
       <x:c r="O71" s="16"/>
       <x:c r="P71" s="16"/>
@@ -19111,7 +19236,7 @@
       <x:c r="J72" s="7"/>
       <x:c r="K72" s="24"/>
       <x:c r="L72" s="23"/>
-      <x:c r="M72" s="6"/>
+      <x:c r="M72" s="16"/>
       <x:c r="N72" s="16"/>
       <x:c r="O72" s="16"/>
       <x:c r="P72" s="16"/>
@@ -19165,7 +19290,7 @@
       <x:c r="J73" s="7"/>
       <x:c r="K73" s="24"/>
       <x:c r="L73" s="23"/>
-      <x:c r="M73" s="6"/>
+      <x:c r="M73" s="16"/>
       <x:c r="N73" s="16"/>
       <x:c r="O73" s="16"/>
       <x:c r="P73" s="16"/>
@@ -19219,7 +19344,7 @@
       <x:c r="J74" s="7"/>
       <x:c r="K74" s="24"/>
       <x:c r="L74" s="23"/>
-      <x:c r="M74" s="6"/>
+      <x:c r="M74" s="16"/>
       <x:c r="N74" s="16"/>
       <x:c r="O74" s="16"/>
       <x:c r="P74" s="16"/>
@@ -19273,7 +19398,7 @@
       <x:c r="J75" s="7"/>
       <x:c r="K75" s="24"/>
       <x:c r="L75" s="23"/>
-      <x:c r="M75" s="6"/>
+      <x:c r="M75" s="16"/>
       <x:c r="N75" s="16"/>
       <x:c r="O75" s="16"/>
       <x:c r="P75" s="16"/>
@@ -19327,7 +19452,7 @@
       <x:c r="J76" s="7"/>
       <x:c r="K76" s="24"/>
       <x:c r="L76" s="23"/>
-      <x:c r="M76" s="6"/>
+      <x:c r="M76" s="16"/>
       <x:c r="N76" s="16"/>
       <x:c r="O76" s="16"/>
       <x:c r="P76" s="16"/>
@@ -19381,7 +19506,7 @@
       <x:c r="J77" s="7"/>
       <x:c r="K77" s="24"/>
       <x:c r="L77" s="23"/>
-      <x:c r="M77" s="6"/>
+      <x:c r="M77" s="16"/>
       <x:c r="N77" s="16"/>
       <x:c r="O77" s="16"/>
       <x:c r="P77" s="16"/>
@@ -19435,7 +19560,7 @@
       <x:c r="J78" s="7"/>
       <x:c r="K78" s="24"/>
       <x:c r="L78" s="23"/>
-      <x:c r="M78" s="6"/>
+      <x:c r="M78" s="16"/>
       <x:c r="N78" s="16"/>
       <x:c r="O78" s="16"/>
       <x:c r="P78" s="16"/>
@@ -19489,7 +19614,7 @@
       <x:c r="J79" s="7"/>
       <x:c r="K79" s="24"/>
       <x:c r="L79" s="23"/>
-      <x:c r="M79" s="6"/>
+      <x:c r="M79" s="16"/>
       <x:c r="N79" s="16"/>
       <x:c r="O79" s="16"/>
       <x:c r="P79" s="16"/>
@@ -19543,7 +19668,7 @@
       <x:c r="J80" s="7"/>
       <x:c r="K80" s="24"/>
       <x:c r="L80" s="23"/>
-      <x:c r="M80" s="6"/>
+      <x:c r="M80" s="16"/>
       <x:c r="N80" s="16"/>
       <x:c r="O80" s="16"/>
       <x:c r="P80" s="16"/>
@@ -19597,7 +19722,7 @@
       <x:c r="J81" s="7"/>
       <x:c r="K81" s="24"/>
       <x:c r="L81" s="23"/>
-      <x:c r="M81" s="6"/>
+      <x:c r="M81" s="16"/>
       <x:c r="N81" s="16"/>
       <x:c r="O81" s="16"/>
       <x:c r="P81" s="16"/>
@@ -19651,7 +19776,7 @@
       <x:c r="J82" s="7"/>
       <x:c r="K82" s="24"/>
       <x:c r="L82" s="23"/>
-      <x:c r="M82" s="6"/>
+      <x:c r="M82" s="16"/>
       <x:c r="N82" s="16"/>
       <x:c r="O82" s="16"/>
       <x:c r="P82" s="16"/>
@@ -19705,7 +19830,7 @@
       <x:c r="J83" s="7"/>
       <x:c r="K83" s="24"/>
       <x:c r="L83" s="23"/>
-      <x:c r="M83" s="6"/>
+      <x:c r="M83" s="16"/>
       <x:c r="N83" s="16"/>
       <x:c r="O83" s="16"/>
       <x:c r="P83" s="16"/>
@@ -19759,7 +19884,7 @@
       <x:c r="J84" s="7"/>
       <x:c r="K84" s="24"/>
       <x:c r="L84" s="23"/>
-      <x:c r="M84" s="6"/>
+      <x:c r="M84" s="16"/>
       <x:c r="N84" s="16"/>
       <x:c r="O84" s="16"/>
       <x:c r="P84" s="16"/>
@@ -19813,7 +19938,7 @@
       <x:c r="J85" s="7"/>
       <x:c r="K85" s="24"/>
       <x:c r="L85" s="23"/>
-      <x:c r="M85" s="6"/>
+      <x:c r="M85" s="16"/>
       <x:c r="N85" s="16"/>
       <x:c r="O85" s="16"/>
       <x:c r="P85" s="16"/>
@@ -19867,7 +19992,7 @@
       <x:c r="J86" s="7"/>
       <x:c r="K86" s="24"/>
       <x:c r="L86" s="23"/>
-      <x:c r="M86" s="6"/>
+      <x:c r="M86" s="16"/>
       <x:c r="N86" s="16"/>
       <x:c r="O86" s="16"/>
       <x:c r="P86" s="16"/>
@@ -19921,7 +20046,7 @@
       <x:c r="J87" s="7"/>
       <x:c r="K87" s="24"/>
       <x:c r="L87" s="23"/>
-      <x:c r="M87" s="6"/>
+      <x:c r="M87" s="16"/>
       <x:c r="N87" s="16"/>
       <x:c r="O87" s="16"/>
       <x:c r="P87" s="16"/>
@@ -19975,7 +20100,7 @@
       <x:c r="J88" s="7"/>
       <x:c r="K88" s="24"/>
       <x:c r="L88" s="23"/>
-      <x:c r="M88" s="6"/>
+      <x:c r="M88" s="16"/>
       <x:c r="N88" s="16"/>
       <x:c r="O88" s="16"/>
       <x:c r="P88" s="16"/>
@@ -20029,7 +20154,7 @@
       <x:c r="J89" s="7"/>
       <x:c r="K89" s="24"/>
       <x:c r="L89" s="23"/>
-      <x:c r="M89" s="6"/>
+      <x:c r="M89" s="16"/>
       <x:c r="N89" s="16"/>
       <x:c r="O89" s="16"/>
       <x:c r="P89" s="16"/>
@@ -20083,7 +20208,7 @@
       <x:c r="J90" s="7"/>
       <x:c r="K90" s="24"/>
       <x:c r="L90" s="23"/>
-      <x:c r="M90" s="6"/>
+      <x:c r="M90" s="16"/>
       <x:c r="N90" s="16"/>
       <x:c r="O90" s="16"/>
       <x:c r="P90" s="16"/>
@@ -20137,7 +20262,7 @@
       <x:c r="J91" s="7"/>
       <x:c r="K91" s="24"/>
       <x:c r="L91" s="23"/>
-      <x:c r="M91" s="6"/>
+      <x:c r="M91" s="16"/>
       <x:c r="N91" s="16"/>
       <x:c r="O91" s="16"/>
       <x:c r="P91" s="16"/>
@@ -20191,7 +20316,7 @@
       <x:c r="J92" s="7"/>
       <x:c r="K92" s="24"/>
       <x:c r="L92" s="23"/>
-      <x:c r="M92" s="6"/>
+      <x:c r="M92" s="16"/>
       <x:c r="N92" s="16"/>
       <x:c r="O92" s="16"/>
       <x:c r="P92" s="16"/>
@@ -20245,7 +20370,7 @@
       <x:c r="J93" s="7"/>
       <x:c r="K93" s="24"/>
       <x:c r="L93" s="23"/>
-      <x:c r="M93" s="6"/>
+      <x:c r="M93" s="16"/>
       <x:c r="N93" s="16"/>
       <x:c r="O93" s="16"/>
       <x:c r="P93" s="16"/>
@@ -20299,7 +20424,7 @@
       <x:c r="J94" s="7"/>
       <x:c r="K94" s="24"/>
       <x:c r="L94" s="23"/>
-      <x:c r="M94" s="6"/>
+      <x:c r="M94" s="16"/>
       <x:c r="N94" s="16"/>
       <x:c r="O94" s="16"/>
       <x:c r="P94" s="16"/>
@@ -20353,7 +20478,7 @@
       <x:c r="J95" s="7"/>
       <x:c r="K95" s="24"/>
       <x:c r="L95" s="23"/>
-      <x:c r="M95" s="6"/>
+      <x:c r="M95" s="16"/>
       <x:c r="N95" s="16"/>
       <x:c r="O95" s="16"/>
       <x:c r="P95" s="16"/>
@@ -20407,7 +20532,7 @@
       <x:c r="J96" s="7"/>
       <x:c r="K96" s="24"/>
       <x:c r="L96" s="23"/>
-      <x:c r="M96" s="6"/>
+      <x:c r="M96" s="16"/>
       <x:c r="N96" s="16"/>
       <x:c r="O96" s="16"/>
       <x:c r="P96" s="16"/>
@@ -20461,7 +20586,7 @@
       <x:c r="J97" s="7"/>
       <x:c r="K97" s="24"/>
       <x:c r="L97" s="23"/>
-      <x:c r="M97" s="6"/>
+      <x:c r="M97" s="16"/>
       <x:c r="N97" s="16"/>
       <x:c r="O97" s="16"/>
       <x:c r="P97" s="16"/>
@@ -20515,7 +20640,7 @@
       <x:c r="J98" s="7"/>
       <x:c r="K98" s="24"/>
       <x:c r="L98" s="23"/>
-      <x:c r="M98" s="6"/>
+      <x:c r="M98" s="16"/>
       <x:c r="N98" s="16"/>
       <x:c r="O98" s="16"/>
       <x:c r="P98" s="16"/>
@@ -20569,7 +20694,7 @@
       <x:c r="J99" s="7"/>
       <x:c r="K99" s="24"/>
       <x:c r="L99" s="23"/>
-      <x:c r="M99" s="6"/>
+      <x:c r="M99" s="16"/>
       <x:c r="N99" s="16"/>
       <x:c r="O99" s="16"/>
       <x:c r="P99" s="16"/>
@@ -20623,7 +20748,7 @@
       <x:c r="J100" s="7"/>
       <x:c r="K100" s="24"/>
       <x:c r="L100" s="23"/>
-      <x:c r="M100" s="6"/>
+      <x:c r="M100" s="16"/>
       <x:c r="N100" s="16"/>
       <x:c r="O100" s="16"/>
       <x:c r="P100" s="16"/>
@@ -20677,7 +20802,7 @@
       <x:c r="J101" s="7"/>
       <x:c r="K101" s="24"/>
       <x:c r="L101" s="23"/>
-      <x:c r="M101" s="6"/>
+      <x:c r="M101" s="16"/>
       <x:c r="N101" s="16"/>
       <x:c r="O101" s="16"/>
       <x:c r="P101" s="16"/>
@@ -20731,7 +20856,7 @@
       <x:c r="J102" s="7"/>
       <x:c r="K102" s="24"/>
       <x:c r="L102" s="23"/>
-      <x:c r="M102" s="6"/>
+      <x:c r="M102" s="16"/>
       <x:c r="N102" s="16"/>
       <x:c r="O102" s="16"/>
       <x:c r="P102" s="16"/>
@@ -20785,7 +20910,7 @@
       <x:c r="J103" s="7"/>
       <x:c r="K103" s="24"/>
       <x:c r="L103" s="23"/>
-      <x:c r="M103" s="6"/>
+      <x:c r="M103" s="16"/>
       <x:c r="N103" s="16"/>
       <x:c r="O103" s="16"/>
       <x:c r="P103" s="16"/>
@@ -20839,7 +20964,7 @@
       <x:c r="J104" s="7"/>
       <x:c r="K104" s="24"/>
       <x:c r="L104" s="23"/>
-      <x:c r="M104" s="6"/>
+      <x:c r="M104" s="16"/>
       <x:c r="N104" s="16"/>
       <x:c r="O104" s="16"/>
       <x:c r="P104" s="16"/>
@@ -20893,7 +21018,7 @@
       <x:c r="J105" s="7"/>
       <x:c r="K105" s="24"/>
       <x:c r="L105" s="23"/>
-      <x:c r="M105" s="6"/>
+      <x:c r="M105" s="16"/>
       <x:c r="N105" s="16"/>
       <x:c r="O105" s="16"/>
       <x:c r="P105" s="16"/>
@@ -20947,7 +21072,7 @@
       <x:c r="J106" s="7"/>
       <x:c r="K106" s="24"/>
       <x:c r="L106" s="23"/>
-      <x:c r="M106" s="6"/>
+      <x:c r="M106" s="16"/>
       <x:c r="N106" s="16"/>
       <x:c r="O106" s="16"/>
       <x:c r="P106" s="16"/>
@@ -21001,7 +21126,7 @@
       <x:c r="J107" s="7"/>
       <x:c r="K107" s="24"/>
       <x:c r="L107" s="23"/>
-      <x:c r="M107" s="6"/>
+      <x:c r="M107" s="16"/>
       <x:c r="N107" s="16"/>
       <x:c r="O107" s="16"/>
       <x:c r="P107" s="16"/>
@@ -21055,7 +21180,7 @@
       <x:c r="J108" s="7"/>
       <x:c r="K108" s="24"/>
       <x:c r="L108" s="23"/>
-      <x:c r="M108" s="6"/>
+      <x:c r="M108" s="16"/>
       <x:c r="N108" s="16"/>
       <x:c r="O108" s="16"/>
       <x:c r="P108" s="16"/>
@@ -21109,7 +21234,7 @@
       <x:c r="J109" s="7"/>
       <x:c r="K109" s="24"/>
       <x:c r="L109" s="23"/>
-      <x:c r="M109" s="6"/>
+      <x:c r="M109" s="16"/>
       <x:c r="N109" s="16"/>
       <x:c r="O109" s="16"/>
       <x:c r="P109" s="16"/>
@@ -21163,7 +21288,7 @@
       <x:c r="J110" s="7"/>
       <x:c r="K110" s="24"/>
       <x:c r="L110" s="23"/>
-      <x:c r="M110" s="6"/>
+      <x:c r="M110" s="16"/>
       <x:c r="N110" s="16"/>
       <x:c r="O110" s="16"/>
       <x:c r="P110" s="16"/>
@@ -21217,7 +21342,7 @@
       <x:c r="J111" s="7"/>
       <x:c r="K111" s="24"/>
       <x:c r="L111" s="23"/>
-      <x:c r="M111" s="6"/>
+      <x:c r="M111" s="16"/>
       <x:c r="N111" s="16"/>
       <x:c r="O111" s="16"/>
       <x:c r="P111" s="16"/>
@@ -21271,7 +21396,7 @@
       <x:c r="J112" s="7"/>
       <x:c r="K112" s="24"/>
       <x:c r="L112" s="23"/>
-      <x:c r="M112" s="6"/>
+      <x:c r="M112" s="16"/>
       <x:c r="N112" s="16"/>
       <x:c r="O112" s="16"/>
       <x:c r="P112" s="16"/>
@@ -21325,7 +21450,7 @@
       <x:c r="J113" s="7"/>
       <x:c r="K113" s="24"/>
       <x:c r="L113" s="23"/>
-      <x:c r="M113" s="6"/>
+      <x:c r="M113" s="16"/>
       <x:c r="N113" s="16"/>
       <x:c r="O113" s="16"/>
       <x:c r="P113" s="16"/>
@@ -21379,7 +21504,7 @@
       <x:c r="J114" s="7"/>
       <x:c r="K114" s="24"/>
       <x:c r="L114" s="23"/>
-      <x:c r="M114" s="6"/>
+      <x:c r="M114" s="16"/>
       <x:c r="N114" s="16"/>
       <x:c r="O114" s="16"/>
       <x:c r="P114" s="16"/>
@@ -21433,7 +21558,7 @@
       <x:c r="J115" s="7"/>
       <x:c r="K115" s="24"/>
       <x:c r="L115" s="23"/>
-      <x:c r="M115" s="6"/>
+      <x:c r="M115" s="16"/>
       <x:c r="N115" s="16"/>
       <x:c r="O115" s="16"/>
       <x:c r="P115" s="16"/>
@@ -21487,7 +21612,7 @@
       <x:c r="J116" s="7"/>
       <x:c r="K116" s="24"/>
       <x:c r="L116" s="23"/>
-      <x:c r="M116" s="6"/>
+      <x:c r="M116" s="16"/>
       <x:c r="N116" s="16"/>
       <x:c r="O116" s="16"/>
       <x:c r="P116" s="16"/>
@@ -21541,7 +21666,7 @@
       <x:c r="J117" s="7"/>
       <x:c r="K117" s="24"/>
       <x:c r="L117" s="23"/>
-      <x:c r="M117" s="6"/>
+      <x:c r="M117" s="16"/>
       <x:c r="N117" s="16"/>
       <x:c r="O117" s="16"/>
       <x:c r="P117" s="16"/>
@@ -21595,7 +21720,7 @@
       <x:c r="J118" s="7"/>
       <x:c r="K118" s="24"/>
       <x:c r="L118" s="23"/>
-      <x:c r="M118" s="6"/>
+      <x:c r="M118" s="16"/>
       <x:c r="N118" s="16"/>
       <x:c r="O118" s="16"/>
       <x:c r="P118" s="16"/>
@@ -21649,7 +21774,7 @@
       <x:c r="J119" s="7"/>
       <x:c r="K119" s="24"/>
       <x:c r="L119" s="23"/>
-      <x:c r="M119" s="6"/>
+      <x:c r="M119" s="16"/>
       <x:c r="N119" s="16"/>
       <x:c r="O119" s="16"/>
       <x:c r="P119" s="16"/>
@@ -21703,7 +21828,7 @@
       <x:c r="J120" s="7"/>
       <x:c r="K120" s="24"/>
       <x:c r="L120" s="23"/>
-      <x:c r="M120" s="6"/>
+      <x:c r="M120" s="16"/>
       <x:c r="N120" s="16"/>
       <x:c r="O120" s="16"/>
       <x:c r="P120" s="16"/>
@@ -21757,7 +21882,7 @@
       <x:c r="J121" s="7"/>
       <x:c r="K121" s="24"/>
       <x:c r="L121" s="23"/>
-      <x:c r="M121" s="6"/>
+      <x:c r="M121" s="16"/>
       <x:c r="N121" s="16"/>
       <x:c r="O121" s="16"/>
       <x:c r="P121" s="16"/>
@@ -21811,7 +21936,7 @@
       <x:c r="J122" s="7"/>
       <x:c r="K122" s="24"/>
       <x:c r="L122" s="23"/>
-      <x:c r="M122" s="6"/>
+      <x:c r="M122" s="16"/>
       <x:c r="N122" s="16"/>
       <x:c r="O122" s="16"/>
       <x:c r="P122" s="16"/>
@@ -21865,7 +21990,7 @@
       <x:c r="J123" s="7"/>
       <x:c r="K123" s="24"/>
       <x:c r="L123" s="23"/>
-      <x:c r="M123" s="6"/>
+      <x:c r="M123" s="16"/>
       <x:c r="N123" s="16"/>
       <x:c r="O123" s="16"/>
       <x:c r="P123" s="16"/>
@@ -21919,7 +22044,7 @@
       <x:c r="J124" s="7"/>
       <x:c r="K124" s="24"/>
       <x:c r="L124" s="23"/>
-      <x:c r="M124" s="6"/>
+      <x:c r="M124" s="16"/>
       <x:c r="N124" s="16"/>
       <x:c r="O124" s="16"/>
       <x:c r="P124" s="16"/>
@@ -21973,7 +22098,7 @@
       <x:c r="J125" s="7"/>
       <x:c r="K125" s="24"/>
       <x:c r="L125" s="23"/>
-      <x:c r="M125" s="6"/>
+      <x:c r="M125" s="16"/>
       <x:c r="N125" s="16"/>
       <x:c r="O125" s="16"/>
       <x:c r="P125" s="16"/>
@@ -22027,7 +22152,7 @@
       <x:c r="J126" s="7"/>
       <x:c r="K126" s="24"/>
       <x:c r="L126" s="23"/>
-      <x:c r="M126" s="6"/>
+      <x:c r="M126" s="16"/>
       <x:c r="N126" s="16"/>
       <x:c r="O126" s="16"/>
       <x:c r="P126" s="16"/>
@@ -22081,7 +22206,7 @@
       <x:c r="J127" s="7"/>
       <x:c r="K127" s="24"/>
       <x:c r="L127" s="23"/>
-      <x:c r="M127" s="6"/>
+      <x:c r="M127" s="16"/>
       <x:c r="N127" s="16"/>
       <x:c r="O127" s="16"/>
       <x:c r="P127" s="16"/>
@@ -22135,7 +22260,7 @@
       <x:c r="J128" s="7"/>
       <x:c r="K128" s="24"/>
       <x:c r="L128" s="23"/>
-      <x:c r="M128" s="6"/>
+      <x:c r="M128" s="16"/>
       <x:c r="N128" s="16"/>
       <x:c r="O128" s="16"/>
       <x:c r="P128" s="16"/>
@@ -22189,7 +22314,7 @@
       <x:c r="J129" s="7"/>
       <x:c r="K129" s="24"/>
       <x:c r="L129" s="23"/>
-      <x:c r="M129" s="6"/>
+      <x:c r="M129" s="16"/>
       <x:c r="N129" s="16"/>
       <x:c r="O129" s="16"/>
       <x:c r="P129" s="16"/>
@@ -22243,7 +22368,7 @@
       <x:c r="J130" s="7"/>
       <x:c r="K130" s="24"/>
       <x:c r="L130" s="23"/>
-      <x:c r="M130" s="6"/>
+      <x:c r="M130" s="16"/>
       <x:c r="N130" s="16"/>
       <x:c r="O130" s="16"/>
       <x:c r="P130" s="16"/>
@@ -22297,7 +22422,7 @@
       <x:c r="J131" s="7"/>
       <x:c r="K131" s="24"/>
       <x:c r="L131" s="23"/>
-      <x:c r="M131" s="6"/>
+      <x:c r="M131" s="16"/>
       <x:c r="N131" s="16"/>
       <x:c r="O131" s="16"/>
       <x:c r="P131" s="16"/>
@@ -22351,7 +22476,7 @@
       <x:c r="J132" s="7"/>
       <x:c r="K132" s="24"/>
       <x:c r="L132" s="23"/>
-      <x:c r="M132" s="6"/>
+      <x:c r="M132" s="16"/>
       <x:c r="N132" s="16"/>
       <x:c r="O132" s="16"/>
       <x:c r="P132" s="16"/>
@@ -22405,7 +22530,7 @@
       <x:c r="J133" s="7"/>
       <x:c r="K133" s="24"/>
       <x:c r="L133" s="23"/>
-      <x:c r="M133" s="6"/>
+      <x:c r="M133" s="16"/>
       <x:c r="N133" s="16"/>
       <x:c r="O133" s="16"/>
       <x:c r="P133" s="16"/>
@@ -22459,7 +22584,7 @@
       <x:c r="J134" s="7"/>
       <x:c r="K134" s="24"/>
       <x:c r="L134" s="23"/>
-      <x:c r="M134" s="6"/>
+      <x:c r="M134" s="16"/>
       <x:c r="N134" s="16"/>
       <x:c r="O134" s="16"/>
       <x:c r="P134" s="16"/>
@@ -22513,7 +22638,7 @@
       <x:c r="J135" s="7"/>
       <x:c r="K135" s="24"/>
       <x:c r="L135" s="23"/>
-      <x:c r="M135" s="6"/>
+      <x:c r="M135" s="16"/>
       <x:c r="N135" s="16"/>
       <x:c r="O135" s="16"/>
       <x:c r="P135" s="16"/>
@@ -22567,7 +22692,7 @@
       <x:c r="J136" s="7"/>
       <x:c r="K136" s="24"/>
       <x:c r="L136" s="23"/>
-      <x:c r="M136" s="6"/>
+      <x:c r="M136" s="16"/>
       <x:c r="N136" s="16"/>
       <x:c r="O136" s="16"/>
       <x:c r="P136" s="16"/>
@@ -22621,7 +22746,7 @@
       <x:c r="J137" s="7"/>
       <x:c r="K137" s="24"/>
       <x:c r="L137" s="23"/>
-      <x:c r="M137" s="6"/>
+      <x:c r="M137" s="16"/>
       <x:c r="N137" s="16"/>
       <x:c r="O137" s="16"/>
       <x:c r="P137" s="16"/>
@@ -22675,7 +22800,7 @@
       <x:c r="J138" s="7"/>
       <x:c r="K138" s="24"/>
       <x:c r="L138" s="23"/>
-      <x:c r="M138" s="6"/>
+      <x:c r="M138" s="16"/>
       <x:c r="N138" s="16"/>
       <x:c r="O138" s="16"/>
       <x:c r="P138" s="16"/>
@@ -22729,7 +22854,7 @@
       <x:c r="J139" s="7"/>
       <x:c r="K139" s="24"/>
       <x:c r="L139" s="23"/>
-      <x:c r="M139" s="6"/>
+      <x:c r="M139" s="16"/>
       <x:c r="N139" s="16"/>
       <x:c r="O139" s="16"/>
       <x:c r="P139" s="16"/>
@@ -22783,7 +22908,7 @@
       <x:c r="J140" s="7"/>
       <x:c r="K140" s="24"/>
       <x:c r="L140" s="23"/>
-      <x:c r="M140" s="6"/>
+      <x:c r="M140" s="16"/>
       <x:c r="N140" s="16"/>
       <x:c r="O140" s="16"/>
       <x:c r="P140" s="16"/>
@@ -22837,7 +22962,7 @@
       <x:c r="J141" s="7"/>
       <x:c r="K141" s="24"/>
       <x:c r="L141" s="23"/>
-      <x:c r="M141" s="6"/>
+      <x:c r="M141" s="16"/>
       <x:c r="N141" s="16"/>
       <x:c r="O141" s="16"/>
       <x:c r="P141" s="16"/>
@@ -22891,7 +23016,7 @@
       <x:c r="J142" s="7"/>
       <x:c r="K142" s="24"/>
       <x:c r="L142" s="23"/>
-      <x:c r="M142" s="6"/>
+      <x:c r="M142" s="16"/>
       <x:c r="N142" s="16"/>
       <x:c r="O142" s="16"/>
       <x:c r="P142" s="16"/>
@@ -22945,7 +23070,7 @@
       <x:c r="J143" s="7"/>
       <x:c r="K143" s="24"/>
       <x:c r="L143" s="23"/>
-      <x:c r="M143" s="6"/>
+      <x:c r="M143" s="16"/>
       <x:c r="N143" s="16"/>
       <x:c r="O143" s="16"/>
       <x:c r="P143" s="16"/>
@@ -22999,7 +23124,7 @@
       <x:c r="J144" s="7"/>
       <x:c r="K144" s="24"/>
       <x:c r="L144" s="23"/>
-      <x:c r="M144" s="6"/>
+      <x:c r="M144" s="16"/>
       <x:c r="N144" s="16"/>
       <x:c r="O144" s="16"/>
       <x:c r="P144" s="16"/>
@@ -23053,7 +23178,7 @@
       <x:c r="J145" s="7"/>
       <x:c r="K145" s="24"/>
       <x:c r="L145" s="23"/>
-      <x:c r="M145" s="6"/>
+      <x:c r="M145" s="16"/>
       <x:c r="N145" s="16"/>
       <x:c r="O145" s="16"/>
       <x:c r="P145" s="16"/>
@@ -23107,7 +23232,7 @@
       <x:c r="J146" s="7"/>
       <x:c r="K146" s="24"/>
       <x:c r="L146" s="23"/>
-      <x:c r="M146" s="6"/>
+      <x:c r="M146" s="16"/>
       <x:c r="N146" s="16"/>
       <x:c r="O146" s="16"/>
       <x:c r="P146" s="16"/>
@@ -23161,7 +23286,7 @@
       <x:c r="J147" s="7"/>
       <x:c r="K147" s="24"/>
       <x:c r="L147" s="23"/>
-      <x:c r="M147" s="6"/>
+      <x:c r="M147" s="16"/>
       <x:c r="N147" s="16"/>
       <x:c r="O147" s="16"/>
       <x:c r="P147" s="16"/>
@@ -23215,7 +23340,7 @@
       <x:c r="J148" s="7"/>
       <x:c r="K148" s="24"/>
       <x:c r="L148" s="23"/>
-      <x:c r="M148" s="6"/>
+      <x:c r="M148" s="16"/>
       <x:c r="N148" s="16"/>
       <x:c r="O148" s="16"/>
       <x:c r="P148" s="16"/>
@@ -23269,7 +23394,7 @@
       <x:c r="J149" s="7"/>
       <x:c r="K149" s="24"/>
       <x:c r="L149" s="23"/>
-      <x:c r="M149" s="6"/>
+      <x:c r="M149" s="16"/>
       <x:c r="N149" s="16"/>
       <x:c r="O149" s="16"/>
       <x:c r="P149" s="16"/>
@@ -23323,7 +23448,7 @@
       <x:c r="J150" s="7"/>
       <x:c r="K150" s="24"/>
       <x:c r="L150" s="23"/>
-      <x:c r="M150" s="6"/>
+      <x:c r="M150" s="16"/>
       <x:c r="N150" s="16"/>
       <x:c r="O150" s="16"/>
       <x:c r="P150" s="16"/>
@@ -23377,7 +23502,7 @@
       <x:c r="J151" s="7"/>
       <x:c r="K151" s="24"/>
       <x:c r="L151" s="23"/>
-      <x:c r="M151" s="6"/>
+      <x:c r="M151" s="16"/>
       <x:c r="N151" s="16"/>
       <x:c r="O151" s="16"/>
       <x:c r="P151" s="16"/>
@@ -23431,7 +23556,7 @@
       <x:c r="J152" s="7"/>
       <x:c r="K152" s="24"/>
       <x:c r="L152" s="23"/>
-      <x:c r="M152" s="6"/>
+      <x:c r="M152" s="16"/>
       <x:c r="N152" s="16"/>
       <x:c r="O152" s="16"/>
       <x:c r="P152" s="16"/>
@@ -23485,7 +23610,7 @@
       <x:c r="J153" s="7"/>
       <x:c r="K153" s="24"/>
       <x:c r="L153" s="23"/>
-      <x:c r="M153" s="6"/>
+      <x:c r="M153" s="16"/>
       <x:c r="N153" s="16"/>
       <x:c r="O153" s="16"/>
       <x:c r="P153" s="16"/>
@@ -23539,7 +23664,7 @@
       <x:c r="J154" s="7"/>
       <x:c r="K154" s="24"/>
       <x:c r="L154" s="23"/>
-      <x:c r="M154" s="6"/>
+      <x:c r="M154" s="16"/>
       <x:c r="N154" s="16"/>
       <x:c r="O154" s="16"/>
       <x:c r="P154" s="16"/>
@@ -23593,7 +23718,7 @@
       <x:c r="J155" s="7"/>
       <x:c r="K155" s="24"/>
       <x:c r="L155" s="23"/>
-      <x:c r="M155" s="6"/>
+      <x:c r="M155" s="16"/>
       <x:c r="N155" s="16"/>
       <x:c r="O155" s="16"/>
       <x:c r="P155" s="16"/>
@@ -23647,7 +23772,7 @@
       <x:c r="J156" s="7"/>
       <x:c r="K156" s="24"/>
       <x:c r="L156" s="23"/>
-      <x:c r="M156" s="6"/>
+      <x:c r="M156" s="16"/>
       <x:c r="N156" s="16"/>
       <x:c r="O156" s="16"/>
       <x:c r="P156" s="16"/>
@@ -23701,7 +23826,7 @@
       <x:c r="J157" s="7"/>
       <x:c r="K157" s="24"/>
       <x:c r="L157" s="23"/>
-      <x:c r="M157" s="6"/>
+      <x:c r="M157" s="16"/>
       <x:c r="N157" s="16"/>
       <x:c r="O157" s="16"/>
       <x:c r="P157" s="16"/>
@@ -23755,7 +23880,7 @@
       <x:c r="J158" s="7"/>
       <x:c r="K158" s="24"/>
       <x:c r="L158" s="23"/>
-      <x:c r="M158" s="6"/>
+      <x:c r="M158" s="16"/>
       <x:c r="N158" s="16"/>
       <x:c r="O158" s="16"/>
       <x:c r="P158" s="16"/>
@@ -23809,7 +23934,7 @@
       <x:c r="J159" s="7"/>
       <x:c r="K159" s="24"/>
       <x:c r="L159" s="23"/>
-      <x:c r="M159" s="6"/>
+      <x:c r="M159" s="16"/>
       <x:c r="N159" s="16"/>
       <x:c r="O159" s="16"/>
       <x:c r="P159" s="16"/>
@@ -23863,7 +23988,7 @@
       <x:c r="J160" s="7"/>
       <x:c r="K160" s="24"/>
       <x:c r="L160" s="23"/>
-      <x:c r="M160" s="6"/>
+      <x:c r="M160" s="16"/>
       <x:c r="N160" s="16"/>
       <x:c r="O160" s="16"/>
       <x:c r="P160" s="16"/>
@@ -23917,7 +24042,7 @@
       <x:c r="J161" s="7"/>
       <x:c r="K161" s="24"/>
       <x:c r="L161" s="23"/>
-      <x:c r="M161" s="6"/>
+      <x:c r="M161" s="16"/>
       <x:c r="N161" s="16"/>
       <x:c r="O161" s="16"/>
       <x:c r="P161" s="16"/>
@@ -23971,7 +24096,7 @@
       <x:c r="J162" s="7"/>
       <x:c r="K162" s="24"/>
       <x:c r="L162" s="23"/>
-      <x:c r="M162" s="6"/>
+      <x:c r="M162" s="16"/>
       <x:c r="N162" s="16"/>
       <x:c r="O162" s="16"/>
       <x:c r="P162" s="16"/>
@@ -24025,7 +24150,7 @@
       <x:c r="J163" s="7"/>
       <x:c r="K163" s="24"/>
       <x:c r="L163" s="23"/>
-      <x:c r="M163" s="6"/>
+      <x:c r="M163" s="16"/>
       <x:c r="N163" s="16"/>
       <x:c r="O163" s="16"/>
       <x:c r="P163" s="16"/>
@@ -24079,7 +24204,7 @@
       <x:c r="J164" s="7"/>
       <x:c r="K164" s="24"/>
       <x:c r="L164" s="23"/>
-      <x:c r="M164" s="6"/>
+      <x:c r="M164" s="16"/>
       <x:c r="N164" s="16"/>
       <x:c r="O164" s="16"/>
       <x:c r="P164" s="16"/>
@@ -24133,7 +24258,7 @@
       <x:c r="J165" s="7"/>
       <x:c r="K165" s="24"/>
       <x:c r="L165" s="23"/>
-      <x:c r="M165" s="6"/>
+      <x:c r="M165" s="16"/>
       <x:c r="N165" s="16"/>
       <x:c r="O165" s="16"/>
       <x:c r="P165" s="16"/>
@@ -24187,7 +24312,7 @@
       <x:c r="J166" s="7"/>
       <x:c r="K166" s="24"/>
       <x:c r="L166" s="23"/>
-      <x:c r="M166" s="6"/>
+      <x:c r="M166" s="16"/>
       <x:c r="N166" s="16"/>
       <x:c r="O166" s="16"/>
       <x:c r="P166" s="16"/>
@@ -24241,7 +24366,7 @@
       <x:c r="J167" s="7"/>
       <x:c r="K167" s="24"/>
       <x:c r="L167" s="23"/>
-      <x:c r="M167" s="6"/>
+      <x:c r="M167" s="16"/>
       <x:c r="N167" s="16"/>
       <x:c r="O167" s="16"/>
       <x:c r="P167" s="16"/>
@@ -24295,7 +24420,7 @@
       <x:c r="J168" s="7"/>
       <x:c r="K168" s="24"/>
       <x:c r="L168" s="23"/>
-      <x:c r="M168" s="6"/>
+      <x:c r="M168" s="16"/>
       <x:c r="N168" s="16"/>
       <x:c r="O168" s="16"/>
       <x:c r="P168" s="16"/>
@@ -24349,7 +24474,7 @@
       <x:c r="J169" s="7"/>
       <x:c r="K169" s="24"/>
       <x:c r="L169" s="23"/>
-      <x:c r="M169" s="6"/>
+      <x:c r="M169" s="16"/>
       <x:c r="N169" s="16"/>
       <x:c r="O169" s="16"/>
       <x:c r="P169" s="16"/>
@@ -24403,7 +24528,7 @@
       <x:c r="J170" s="7"/>
       <x:c r="K170" s="24"/>
       <x:c r="L170" s="23"/>
-      <x:c r="M170" s="6"/>
+      <x:c r="M170" s="16"/>
       <x:c r="N170" s="16"/>
       <x:c r="O170" s="16"/>
       <x:c r="P170" s="16"/>
@@ -24457,7 +24582,7 @@
       <x:c r="J171" s="7"/>
       <x:c r="K171" s="24"/>
       <x:c r="L171" s="23"/>
-      <x:c r="M171" s="6"/>
+      <x:c r="M171" s="16"/>
       <x:c r="N171" s="16"/>
       <x:c r="O171" s="16"/>
       <x:c r="P171" s="16"/>
@@ -24511,7 +24636,7 @@
       <x:c r="J172" s="7"/>
       <x:c r="K172" s="24"/>
       <x:c r="L172" s="23"/>
-      <x:c r="M172" s="6"/>
+      <x:c r="M172" s="16"/>
       <x:c r="N172" s="16"/>
       <x:c r="O172" s="16"/>
       <x:c r="P172" s="16"/>
@@ -24565,7 +24690,7 @@
       <x:c r="J173" s="7"/>
       <x:c r="K173" s="24"/>
       <x:c r="L173" s="23"/>
-      <x:c r="M173" s="6"/>
+      <x:c r="M173" s="16"/>
       <x:c r="N173" s="16"/>
       <x:c r="O173" s="16"/>
       <x:c r="P173" s="16"/>
@@ -24619,7 +24744,7 @@
       <x:c r="J174" s="7"/>
       <x:c r="K174" s="24"/>
       <x:c r="L174" s="23"/>
-      <x:c r="M174" s="6"/>
+      <x:c r="M174" s="16"/>
       <x:c r="N174" s="16"/>
       <x:c r="O174" s="16"/>
       <x:c r="P174" s="16"/>
@@ -24673,7 +24798,7 @@
       <x:c r="J175" s="7"/>
       <x:c r="K175" s="24"/>
       <x:c r="L175" s="23"/>
-      <x:c r="M175" s="6"/>
+      <x:c r="M175" s="16"/>
       <x:c r="N175" s="16"/>
       <x:c r="O175" s="16"/>
       <x:c r="P175" s="16"/>
@@ -24727,7 +24852,7 @@
       <x:c r="J176" s="7"/>
       <x:c r="K176" s="24"/>
       <x:c r="L176" s="23"/>
-      <x:c r="M176" s="6"/>
+      <x:c r="M176" s="16"/>
       <x:c r="N176" s="16"/>
       <x:c r="O176" s="16"/>
       <x:c r="P176" s="16"/>
@@ -24781,7 +24906,7 @@
       <x:c r="J177" s="7"/>
       <x:c r="K177" s="24"/>
       <x:c r="L177" s="23"/>
-      <x:c r="M177" s="6"/>
+      <x:c r="M177" s="16"/>
       <x:c r="N177" s="16"/>
       <x:c r="O177" s="16"/>
       <x:c r="P177" s="16"/>
@@ -24835,7 +24960,7 @@
       <x:c r="J178" s="7"/>
       <x:c r="K178" s="24"/>
       <x:c r="L178" s="23"/>
-      <x:c r="M178" s="6"/>
+      <x:c r="M178" s="16"/>
       <x:c r="N178" s="16"/>
       <x:c r="O178" s="16"/>
       <x:c r="P178" s="16"/>
@@ -24889,7 +25014,7 @@
       <x:c r="J179" s="7"/>
       <x:c r="K179" s="24"/>
       <x:c r="L179" s="23"/>
-      <x:c r="M179" s="6"/>
+      <x:c r="M179" s="16"/>
       <x:c r="N179" s="16"/>
       <x:c r="O179" s="16"/>
       <x:c r="P179" s="16"/>
@@ -24943,7 +25068,7 @@
       <x:c r="J180" s="7"/>
       <x:c r="K180" s="24"/>
       <x:c r="L180" s="23"/>
-      <x:c r="M180" s="6"/>
+      <x:c r="M180" s="16"/>
       <x:c r="N180" s="16"/>
       <x:c r="O180" s="16"/>
       <x:c r="P180" s="16"/>
@@ -24997,7 +25122,7 @@
       <x:c r="J181" s="7"/>
       <x:c r="K181" s="24"/>
       <x:c r="L181" s="23"/>
-      <x:c r="M181" s="6"/>
+      <x:c r="M181" s="16"/>
       <x:c r="N181" s="16"/>
       <x:c r="O181" s="16"/>
       <x:c r="P181" s="16"/>
@@ -25051,7 +25176,7 @@
       <x:c r="J182" s="7"/>
       <x:c r="K182" s="24"/>
       <x:c r="L182" s="23"/>
-      <x:c r="M182" s="6"/>
+      <x:c r="M182" s="16"/>
       <x:c r="N182" s="16"/>
       <x:c r="O182" s="16"/>
       <x:c r="P182" s="16"/>
@@ -25105,7 +25230,7 @@
       <x:c r="J183" s="7"/>
       <x:c r="K183" s="24"/>
       <x:c r="L183" s="23"/>
-      <x:c r="M183" s="6"/>
+      <x:c r="M183" s="16"/>
       <x:c r="N183" s="16"/>
       <x:c r="O183" s="16"/>
       <x:c r="P183" s="16"/>
@@ -25159,7 +25284,7 @@
       <x:c r="J184" s="7"/>
       <x:c r="K184" s="24"/>
       <x:c r="L184" s="23"/>
-      <x:c r="M184" s="6"/>
+      <x:c r="M184" s="16"/>
       <x:c r="N184" s="16"/>
       <x:c r="O184" s="16"/>
       <x:c r="P184" s="16"/>
@@ -25213,7 +25338,7 @@
       <x:c r="J185" s="7"/>
       <x:c r="K185" s="24"/>
       <x:c r="L185" s="23"/>
-      <x:c r="M185" s="6"/>
+      <x:c r="M185" s="16"/>
       <x:c r="N185" s="16"/>
       <x:c r="O185" s="16"/>
       <x:c r="P185" s="16"/>
@@ -25267,7 +25392,7 @@
       <x:c r="J186" s="7"/>
       <x:c r="K186" s="24"/>
       <x:c r="L186" s="23"/>
-      <x:c r="M186" s="6"/>
+      <x:c r="M186" s="16"/>
       <x:c r="N186" s="16"/>
       <x:c r="O186" s="16"/>
       <x:c r="P186" s="16"/>
@@ -25321,7 +25446,7 @@
       <x:c r="J187" s="7"/>
       <x:c r="K187" s="24"/>
       <x:c r="L187" s="23"/>
-      <x:c r="M187" s="6"/>
+      <x:c r="M187" s="16"/>
       <x:c r="N187" s="16"/>
       <x:c r="O187" s="16"/>
       <x:c r="P187" s="16"/>
@@ -25375,7 +25500,7 @@
       <x:c r="J188" s="7"/>
       <x:c r="K188" s="24"/>
       <x:c r="L188" s="23"/>
-      <x:c r="M188" s="6"/>
+      <x:c r="M188" s="16"/>
       <x:c r="N188" s="16"/>
       <x:c r="O188" s="16"/>
       <x:c r="P188" s="16"/>
@@ -25429,7 +25554,7 @@
       <x:c r="J189" s="7"/>
       <x:c r="K189" s="24"/>
       <x:c r="L189" s="23"/>
-      <x:c r="M189" s="6"/>
+      <x:c r="M189" s="16"/>
       <x:c r="N189" s="16"/>
       <x:c r="O189" s="16"/>
       <x:c r="P189" s="16"/>
@@ -25483,7 +25608,7 @@
       <x:c r="J190" s="7"/>
       <x:c r="K190" s="24"/>
       <x:c r="L190" s="23"/>
-      <x:c r="M190" s="6"/>
+      <x:c r="M190" s="16"/>
       <x:c r="N190" s="16"/>
       <x:c r="O190" s="16"/>
       <x:c r="P190" s="16"/>
@@ -25537,7 +25662,7 @@
       <x:c r="J191" s="7"/>
       <x:c r="K191" s="24"/>
       <x:c r="L191" s="23"/>
-      <x:c r="M191" s="6"/>
+      <x:c r="M191" s="16"/>
       <x:c r="N191" s="16"/>
       <x:c r="O191" s="16"/>
       <x:c r="P191" s="16"/>
@@ -25591,7 +25716,7 @@
       <x:c r="J192" s="7"/>
       <x:c r="K192" s="24"/>
       <x:c r="L192" s="23"/>
-      <x:c r="M192" s="6"/>
+      <x:c r="M192" s="16"/>
       <x:c r="N192" s="16"/>
       <x:c r="O192" s="16"/>
       <x:c r="P192" s="16"/>
@@ -25645,7 +25770,7 @@
       <x:c r="J193" s="7"/>
       <x:c r="K193" s="24"/>
       <x:c r="L193" s="23"/>
-      <x:c r="M193" s="6"/>
+      <x:c r="M193" s="16"/>
       <x:c r="N193" s="16"/>
       <x:c r="O193" s="16"/>
       <x:c r="P193" s="16"/>
@@ -25699,7 +25824,7 @@
       <x:c r="J194" s="7"/>
       <x:c r="K194" s="24"/>
       <x:c r="L194" s="23"/>
-      <x:c r="M194" s="6"/>
+      <x:c r="M194" s="16"/>
       <x:c r="N194" s="16"/>
       <x:c r="O194" s="16"/>
       <x:c r="P194" s="16"/>
@@ -25753,7 +25878,7 @@
       <x:c r="J195" s="7"/>
       <x:c r="K195" s="24"/>
       <x:c r="L195" s="23"/>
-      <x:c r="M195" s="6"/>
+      <x:c r="M195" s="16"/>
       <x:c r="N195" s="16"/>
       <x:c r="O195" s="16"/>
       <x:c r="P195" s="16"/>
@@ -25807,7 +25932,7 @@
       <x:c r="J196" s="7"/>
       <x:c r="K196" s="24"/>
       <x:c r="L196" s="23"/>
-      <x:c r="M196" s="6"/>
+      <x:c r="M196" s="16"/>
       <x:c r="N196" s="16"/>
       <x:c r="O196" s="16"/>
       <x:c r="P196" s="16"/>
@@ -25861,7 +25986,7 @@
       <x:c r="J197" s="7"/>
       <x:c r="K197" s="24"/>
       <x:c r="L197" s="23"/>
-      <x:c r="M197" s="6"/>
+      <x:c r="M197" s="16"/>
       <x:c r="N197" s="16"/>
       <x:c r="O197" s="16"/>
       <x:c r="P197" s="16"/>
@@ -25915,7 +26040,7 @@
       <x:c r="J198" s="7"/>
       <x:c r="K198" s="24"/>
       <x:c r="L198" s="23"/>
-      <x:c r="M198" s="6"/>
+      <x:c r="M198" s="16"/>
       <x:c r="N198" s="16"/>
       <x:c r="O198" s="16"/>
       <x:c r="P198" s="16"/>
@@ -25969,7 +26094,7 @@
       <x:c r="J199" s="7"/>
       <x:c r="K199" s="24"/>
       <x:c r="L199" s="23"/>
-      <x:c r="M199" s="6"/>
+      <x:c r="M199" s="16"/>
       <x:c r="N199" s="16"/>
       <x:c r="O199" s="16"/>
       <x:c r="P199" s="16"/>
@@ -26023,7 +26148,7 @@
       <x:c r="J200" s="7"/>
       <x:c r="K200" s="24"/>
       <x:c r="L200" s="23"/>
-      <x:c r="M200" s="6"/>
+      <x:c r="M200" s="16"/>
       <x:c r="N200" s="16"/>
       <x:c r="O200" s="16"/>
       <x:c r="P200" s="16"/>
@@ -26077,7 +26202,7 @@
       <x:c r="J201" s="2"/>
       <x:c r="K201" s="17"/>
       <x:c r="L201" s="17"/>
-      <x:c r="M201" s="2"/>
+      <x:c r="M201" s="17"/>
       <x:c r="N201" s="17"/>
       <x:c r="O201" s="17"/>
       <x:c r="P201" s="17"/>
@@ -26131,7 +26256,7 @@
       <x:c r="J202" s="2"/>
       <x:c r="K202" s="17"/>
       <x:c r="L202" s="17"/>
-      <x:c r="M202" s="2"/>
+      <x:c r="M202" s="17"/>
       <x:c r="N202" s="17"/>
       <x:c r="O202" s="17"/>
       <x:c r="P202" s="17"/>
@@ -26185,7 +26310,7 @@
       <x:c r="J203" s="2"/>
       <x:c r="K203" s="17"/>
       <x:c r="L203" s="17"/>
-      <x:c r="M203" s="2"/>
+      <x:c r="M203" s="17"/>
       <x:c r="N203" s="17"/>
       <x:c r="O203" s="17"/>
       <x:c r="P203" s="17"/>
@@ -26239,7 +26364,7 @@
       <x:c r="J204" s="2"/>
       <x:c r="K204" s="17"/>
       <x:c r="L204" s="17"/>
-      <x:c r="M204" s="2"/>
+      <x:c r="M204" s="17"/>
       <x:c r="N204" s="17"/>
       <x:c r="O204" s="17"/>
       <x:c r="P204" s="17"/>
@@ -26293,7 +26418,7 @@
       <x:c r="J205" s="2"/>
       <x:c r="K205" s="17"/>
       <x:c r="L205" s="17"/>
-      <x:c r="M205" s="2"/>
+      <x:c r="M205" s="17"/>
       <x:c r="N205" s="17"/>
       <x:c r="O205" s="17"/>
       <x:c r="P205" s="17"/>
@@ -26347,7 +26472,7 @@
       <x:c r="J206" s="2"/>
       <x:c r="K206" s="17"/>
       <x:c r="L206" s="17"/>
-      <x:c r="M206" s="2"/>
+      <x:c r="M206" s="17"/>
       <x:c r="N206" s="17"/>
       <x:c r="O206" s="17"/>
       <x:c r="P206" s="17"/>
@@ -26401,7 +26526,7 @@
       <x:c r="J207" s="2"/>
       <x:c r="K207" s="17"/>
       <x:c r="L207" s="17"/>
-      <x:c r="M207" s="2"/>
+      <x:c r="M207" s="17"/>
       <x:c r="N207" s="17"/>
       <x:c r="O207" s="17"/>
       <x:c r="P207" s="17"/>
@@ -26455,7 +26580,7 @@
       <x:c r="J208" s="2"/>
       <x:c r="K208" s="17"/>
       <x:c r="L208" s="17"/>
-      <x:c r="M208" s="2"/>
+      <x:c r="M208" s="17"/>
       <x:c r="N208" s="17"/>
       <x:c r="O208" s="17"/>
       <x:c r="P208" s="17"/>
@@ -26509,7 +26634,7 @@
       <x:c r="J209" s="2"/>
       <x:c r="K209" s="17"/>
       <x:c r="L209" s="17"/>
-      <x:c r="M209" s="2"/>
+      <x:c r="M209" s="17"/>
       <x:c r="N209" s="17"/>
       <x:c r="O209" s="17"/>
       <x:c r="P209" s="17"/>
@@ -26563,7 +26688,7 @@
       <x:c r="J210" s="2"/>
       <x:c r="K210" s="17"/>
       <x:c r="L210" s="17"/>
-      <x:c r="M210" s="2"/>
+      <x:c r="M210" s="17"/>
       <x:c r="N210" s="17"/>
       <x:c r="O210" s="17"/>
       <x:c r="P210" s="17"/>
@@ -26617,7 +26742,7 @@
       <x:c r="J211" s="2"/>
       <x:c r="K211" s="17"/>
       <x:c r="L211" s="17"/>
-      <x:c r="M211" s="2"/>
+      <x:c r="M211" s="17"/>
       <x:c r="N211" s="17"/>
       <x:c r="O211" s="17"/>
       <x:c r="P211" s="17"/>
@@ -26671,7 +26796,7 @@
       <x:c r="J212" s="2"/>
       <x:c r="K212" s="17"/>
       <x:c r="L212" s="17"/>
-      <x:c r="M212" s="2"/>
+      <x:c r="M212" s="17"/>
       <x:c r="N212" s="17"/>
       <x:c r="O212" s="17"/>
       <x:c r="P212" s="17"/>
@@ -26725,7 +26850,7 @@
       <x:c r="J213" s="2"/>
       <x:c r="K213" s="17"/>
       <x:c r="L213" s="17"/>
-      <x:c r="M213" s="2"/>
+      <x:c r="M213" s="17"/>
       <x:c r="N213" s="17"/>
       <x:c r="O213" s="17"/>
       <x:c r="P213" s="17"/>
@@ -26779,7 +26904,7 @@
       <x:c r="J214" s="2"/>
       <x:c r="K214" s="17"/>
       <x:c r="L214" s="17"/>
-      <x:c r="M214" s="2"/>
+      <x:c r="M214" s="17"/>
       <x:c r="N214" s="17"/>
       <x:c r="O214" s="17"/>
       <x:c r="P214" s="17"/>
@@ -26833,7 +26958,7 @@
       <x:c r="J215" s="2"/>
       <x:c r="K215" s="17"/>
       <x:c r="L215" s="17"/>
-      <x:c r="M215" s="2"/>
+      <x:c r="M215" s="17"/>
       <x:c r="N215" s="17"/>
       <x:c r="O215" s="17"/>
       <x:c r="P215" s="17"/>
@@ -26887,7 +27012,7 @@
       <x:c r="J216" s="2"/>
       <x:c r="K216" s="17"/>
       <x:c r="L216" s="17"/>
-      <x:c r="M216" s="2"/>
+      <x:c r="M216" s="17"/>
       <x:c r="N216" s="17"/>
       <x:c r="O216" s="17"/>
       <x:c r="P216" s="17"/>
@@ -26941,7 +27066,7 @@
       <x:c r="J217" s="2"/>
       <x:c r="K217" s="17"/>
       <x:c r="L217" s="17"/>
-      <x:c r="M217" s="2"/>
+      <x:c r="M217" s="17"/>
       <x:c r="N217" s="17"/>
       <x:c r="O217" s="17"/>
       <x:c r="P217" s="17"/>
@@ -26995,7 +27120,7 @@
       <x:c r="J218" s="2"/>
       <x:c r="K218" s="17"/>
       <x:c r="L218" s="17"/>
-      <x:c r="M218" s="2"/>
+      <x:c r="M218" s="17"/>
       <x:c r="N218" s="17"/>
       <x:c r="O218" s="17"/>
       <x:c r="P218" s="17"/>
@@ -27049,7 +27174,7 @@
       <x:c r="J219" s="2"/>
       <x:c r="K219" s="17"/>
       <x:c r="L219" s="17"/>
-      <x:c r="M219" s="2"/>
+      <x:c r="M219" s="17"/>
       <x:c r="N219" s="17"/>
       <x:c r="O219" s="17"/>
       <x:c r="P219" s="17"/>
@@ -27103,7 +27228,7 @@
       <x:c r="J220" s="2"/>
       <x:c r="K220" s="17"/>
       <x:c r="L220" s="17"/>
-      <x:c r="M220" s="2"/>
+      <x:c r="M220" s="17"/>
       <x:c r="N220" s="17"/>
       <x:c r="O220" s="17"/>
       <x:c r="P220" s="17"/>
@@ -27259,7 +27384,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:52">
       <x:c r="A1" s="32" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="32"/>
       <x:c r="C1" s="32"/>
@@ -27369,7 +27494,7 @@
     </x:row>
     <x:row r="3" spans="1:52">
       <x:c r="A3" s="33" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B3" s="33"/>
       <x:c r="C3" s="33"/>
@@ -27425,7 +27550,7 @@
     </x:row>
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="19" t="s">
         <x:v>159</x:v>
@@ -27434,13 +27559,13 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G4" s="19" t="s">
         <x:v>167</x:v>
@@ -27458,34 +27583,34 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M4" s="3" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N4" s="3" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="O4" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P4" s="3" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="Q4" s="3" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="S4" s="3" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="M4" s="3" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="N4" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="O4" s="3" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="P4" s="3" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="Q4" s="3" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="R4" s="3" t="s">
+      <x:c r="U4" s="3" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="S4" s="3" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="T4" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="U4" s="3" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="V4" s="3" t="s">
         <x:v>154</x:v>
@@ -27522,32 +27647,32 @@
       <x:c r="AZ4" s="2"/>
     </x:row>
     <x:row r="5" spans="1:52">
-      <x:c r="A5" s="25" t="s">
-        <x:v>120</x:v>
+      <x:c r="A5" s="28" t="s">
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C5" s="8" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F5" s="27" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G5" s="25" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="26">
-        <x:v>46217</x:v>
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="I5" s="26">
-        <x:v>46217</x:v>
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="J5" s="25" t="s">
         <x:v>163</x:v>
@@ -27562,20 +27687,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N5" s="2">
-        <x:v>200</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="O5" s="11">
-        <x:v>0.34999999999999998</x:v>
+        <x:v>0.55000000000000004</x:v>
       </x:c>
       <x:c r="P5" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="Q5" s="2" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="R5" s="2">
-        <x:v>30</x:v>
-      </x:c>
+      <x:c r="R5" s="2"/>
       <x:c r="S5" s="2"/>
       <x:c r="T5" s="2"/>
       <x:c r="U5" s="2"/>
@@ -27611,36 +27734,36 @@
       <x:c r="AY5" s="2"/>
       <x:c r="AZ5" s="2"/>
     </x:row>
-    <x:row r="6" spans="1:52">
-      <x:c r="A6" s="25" t="s">
-        <x:v>118</x:v>
+    <x:row r="6" spans="1:52" customFormat="1">
+      <x:c r="A6" s="28" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B6" s="8" t="s">
-        <x:v>231</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="s">
-        <x:v>220</x:v>
+      <x:c r="F6" s="27" t="s">
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G6" s="25" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="26" t="s">
-        <x:v>121</x:v>
+      <x:c r="H6" s="26">
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="I6" s="26">
-        <x:v>46235</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="J6" s="25" t="s">
-        <x:v>183</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K6" s="10">
         <x:v>0</x:v>
@@ -27649,23 +27772,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="2">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="2">
         <x:v>200</x:v>
       </x:c>
       <x:c r="O6" s="11">
-        <x:v>0.10000000000000001</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="P6" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q6" s="2" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="R6" s="2">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="R6" s="2"/>
       <x:c r="S6" s="2"/>
       <x:c r="T6" s="2"/>
       <x:c r="U6" s="2"/>
@@ -27701,38 +27822,58 @@
       <x:c r="AY6" s="2"/>
       <x:c r="AZ6" s="2"/>
     </x:row>
-    <x:row r="7" spans="1:52">
+    <x:row r="7" spans="1:52" customFormat="1">
       <x:c r="A7" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="I7" s="26">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="J7" s="25" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K7" s="10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="2">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N7" s="2">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="O7" s="11">
+        <x:v>0.45000000000000001</x:v>
+      </x:c>
+      <x:c r="P7" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="s">
-        <x:v>222</x:v>
+      <x:c r="Q7" s="2" t="s">
+        <x:v>192</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F7" s="27" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G7" s="29" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="8"/>
-      <x:c r="K7" s="10"/>
-      <x:c r="L7" s="10"/>
-      <x:c r="M7" s="2"/>
-      <x:c r="N7" s="2"/>
-      <x:c r="O7" s="11"/>
-      <x:c r="P7" s="2"/>
-      <x:c r="Q7" s="2"/>
       <x:c r="R7" s="2"/>
       <x:c r="S7" s="2"/>
       <x:c r="T7" s="2"/>
@@ -27769,17 +27910,37 @@
       <x:c r="AY7" s="2"/>
       <x:c r="AZ7" s="2"/>
     </x:row>
-    <x:row r="8" spans="1:52">
-      <x:c r="A8" s="8"/>
-      <x:c r="B8" s="8"/>
-      <x:c r="C8" s="8"/>
-      <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="8"/>
-      <x:c r="G8" s="8"/>
-      <x:c r="H8" s="9"/>
-      <x:c r="I8" s="9"/>
-      <x:c r="J8" s="8"/>
+    <x:row r="8" spans="1:52" customFormat="1">
+      <x:c r="A8" s="28" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="J8" s="29" t="s">
+        <x:v>183</x:v>
+      </x:c>
       <x:c r="K8" s="10"/>
       <x:c r="L8" s="10"/>
       <x:c r="M8" s="2"/>
@@ -39276,13 +39437,13 @@
     <x:mergeCell ref="A1:V2"/>
     <x:mergeCell ref="A3:V3"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="J5:J200">
-    <x:cfRule type="expression" dxfId="20" priority="1">
+  <x:conditionalFormatting sqref="J5:J5 J9:J200">
+    <x:cfRule type="expression" dxfId="20" priority="4">
       <x:formula>J5="완료"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O5:O200">
-    <x:cfRule type="dataBar" priority="2">
+  <x:conditionalFormatting sqref="O5:O5 O9:O200">
+    <x:cfRule type="dataBar" priority="5">
       <x:dataBar>
         <x:cfvo type="min"/>
         <x:cfvo type="max"/>
@@ -39290,19 +39451,50 @@
       </x:dataBar>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="C5:C200">
+  <x:conditionalFormatting sqref="J6:J7">
+    <x:cfRule type="expression" dxfId="18" priority="2">
+      <x:formula>J6="완료"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="O6:O8">
+    <x:cfRule type="dataBar" priority="3">
+      <x:dataBar>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="ff2e6f95"/>
+      </x:dataBar>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J8:J8">
+    <x:cfRule type="expression" dxfId="18" priority="1">
+      <x:formula>J8="완료"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="8">
+    <x:dataValidation type="list" sqref="C9:C200 C5:C5">
       <x:formula1>목록!$G$2:$G$7</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J5:J200">
+    <x:dataValidation type="list" sqref="J9:J200 J5:J5">
       <x:formula1>목록!$H$2:$H$5</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="Q5:Q200">
+    <x:dataValidation type="list" sqref="Q9:Q200 Q5:Q5">
       <x:formula1>목록!$I$2:$I$10</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="decimal" sqref="O5:O200">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C6:C8">
+      <x:formula1>목록!$G$2:$G$7</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J6:J7">
+      <x:formula1>목록!$H$2:$H$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="Q6:Q8">
+      <x:formula1>목록!$I$2:$I$10</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J8:J8">
+      <x:formula1>목록!$H$2:$H$5</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -39324,7 +39516,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:52">
       <x:c r="A1" s="32" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="32"/>
       <x:c r="C1" s="32"/>
@@ -39434,7 +39626,7 @@
     </x:row>
     <x:row r="3" spans="1:52">
       <x:c r="A3" s="35" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="35"/>
       <x:c r="C3" s="35"/>
@@ -39552,11 +39744,11 @@
       </x:c>
       <x:c r="D5" s="36"/>
       <x:c r="E5" s="36" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F5" s="36"/>
       <x:c r="G5" s="36" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H5" s="36"/>
       <x:c r="I5" s="36" t="s">
@@ -39839,7 +40031,7 @@
     </x:row>
     <x:row r="10" spans="1:52">
       <x:c r="A10" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B10" s="12" t="s">
         <x:v>147</x:v>
@@ -39849,13 +40041,13 @@
       </x:c>
       <x:c r="D10" s="2"/>
       <x:c r="E10" s="13" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F10" s="13" t="s">
         <x:v>153</x:v>
       </x:c>
       <x:c r="G10" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H10" s="2"/>
       <x:c r="I10" s="2"/>
@@ -39921,7 +40113,7 @@
       </x:c>
       <x:c r="F11" s="2">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$200,E11,일만상상프로젝트!$B$5:$B$200,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G11" s="10">
         <x:f>SUMIFS(일만상상프로젝트!$K$5:$K$200,일만상상프로젝트!$J$5:$J$200,E11)</x:f>
@@ -39975,7 +40167,7 @@
     </x:row>
     <x:row r="12" spans="1:52">
       <x:c r="A12" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="2">
         <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A12)</x:f>
@@ -40061,7 +40253,7 @@
       </x:c>
       <x:c r="F13" s="2">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$200,E13,일만상상프로젝트!$B$5:$B$200,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G13" s="10">
         <x:f>SUMIFS(일만상상프로젝트!$K$5:$K$200,일만상상프로젝트!$J$5:$J$200,E13)</x:f>
@@ -40185,7 +40377,7 @@
     </x:row>
     <x:row r="15" spans="1:52">
       <x:c r="A15" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="2">
         <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A15)</x:f>
@@ -40309,7 +40501,7 @@
     </x:row>
     <x:row r="17" spans="1:52">
       <x:c r="A17" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="2">
         <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A17)</x:f>
@@ -40371,7 +40563,7 @@
     </x:row>
     <x:row r="18" spans="1:52">
       <x:c r="A18" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B18" s="2">
         <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A18)</x:f>
@@ -40487,7 +40679,7 @@
     </x:row>
     <x:row r="20" spans="1:52">
       <x:c r="A20" s="38" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="38"/>
       <x:c r="C20" s="38"/>
@@ -51386,28 +51578,28 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B1" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C1" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D1" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E1" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F1" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G1" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H1" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I1" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J1" s="14" t="s">
         <x:v>144</x:v>
@@ -51475,7 +51667,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
         <x:v>183</x:v>
@@ -51484,7 +51676,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
@@ -51537,7 +51729,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
         <x:v>146</x:v>
@@ -51549,7 +51741,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
         <x:v>211</x:v>
@@ -51558,7 +51750,7 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="J3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
@@ -51619,7 +51811,7 @@
       </x:c>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
         <x:v>163</x:v>
@@ -51628,7 +51820,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="J4" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
@@ -51689,7 +51881,7 @@
       </x:c>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H5" s="2" t="s">
         <x:v>152</x:v>
@@ -51698,7 +51890,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="J5" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K5" s="2"/>
       <x:c r="L5" s="2"/>
@@ -51749,7 +51941,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
         <x:v>166</x:v>
@@ -51757,14 +51949,14 @@
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J6" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K6" s="2"/>
       <x:c r="L6" s="2"/>
@@ -51877,7 +52069,7 @@
       <x:c r="A8" s="2"/>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
         <x:v>180</x:v>
@@ -51937,7 +52129,7 @@
       <x:c r="A9" s="2"/>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
@@ -51945,7 +52137,7 @@
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
       <x:c r="I9" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J9" s="2"/>
       <x:c r="K9" s="2"/>

--- a/GESMS_전도영혼구원_표준자료양식_V3.0.xlsx
+++ b/GESMS_전도영혼구원_표준자료양식_V3.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500" activeTab="2"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500" activeTab="1"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="사용안내" sheetId="1" r:id="rId4"/>
@@ -24,297 +24,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="371">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="377">
+  <x:si>
+    <x:t>아들박지우 건강과 교회 참석을 위해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 결식아동 무료식사 제공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통계와 목표를 적용할 기준 연도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사업 시작을 하는데 어려움이 없도록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방과후 결식아동 다수로 식사 제공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전도현황, 연락대상, 단계별 통계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포 지역사회 어르신 무료식사 제공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행률, 분야별 현황, 성과 집계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>누나의 건강(암)이 회복되기를</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예산, 참여인원, 성과, 결과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도대상자관리 및 일만상상프로젝트 시트의 자료를 자동 집계합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESMS V10.0 전도·영혼구원 표준자료 입력 양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음연락일은 실제 연락 계획이 있을 때 입력합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>※ 한 사람당 한 행 작성 · 노란색 열은 필수 · 날짜는 YYYY-MM-DD 형식</x:t>
+  </x:si>
   <x:si>
     <x:t>운영 팁: '진행상태'와 '다음연락일'을 꾸준히 갱신하면 앱의 전도현황이 정확해집니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Y</x:t>
+    <x:t>앱에 설정된 최신 버전을 자동으로 표시</x:t>
   </x:si>
   <x:si>
-    <x:t>담당자</x:t>
+    <x:t>P-0028</x:t>
   </x:si>
   <x:si>
-    <x:t>남</x:t>
+    <x:t>P-0029</x:t>
   </x:si>
   <x:si>
-    <x:t>종료일</x:t>
+    <x:t>군포중학교 무료급식(35회)</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
+    <x:t>군포중학교 무료급식(40회)</x:t>
   </x:si>
   <x:si>
-    <x:t>상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초청</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새가족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>친구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건강</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미라클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청년</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접촉</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교역자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담</x:t>
-  </x:si>
-  <x:si>
-    <x:t>값</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장윤주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기숙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한명희</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송선례</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박미연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김문희</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정유진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정의룡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김정화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사랑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김계화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최주현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이수경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>등록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박종훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김인일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김해선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최향옥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱버전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홍순기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윤정호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박형렬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방선근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최재용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사업명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이정아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방원란</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이세진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하희정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송옥섭</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김충남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정다혜</x:t>
-  </x:si>
-  <x:si>
-    <x:t>변순덕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김옥금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박미옥</x:t>
+    <x:t>군포중학교 무료급식(37회)</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(16회)</x:t>
@@ -326,46 +98,58 @@
     <x:t>군포중학교 무료급식(33회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(24회)</x:t>
+    <x:t>군포중학교 무료급식(32회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(40회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포중학교 무료급식(32회)</x:t>
+    <x:t>군포중학교 무료급식(19회)</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(17회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(19회)</x:t>
-  </x:si>
-  <x:si>
     <x:t>군포중학교 무료급식(43회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(37회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포중학교 무료급식(35회)</x:t>
+    <x:t>전도현황 자동 대시보드</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(29회)</x:t>
   </x:si>
   <x:si>
-    <x:t>전도현황 자동 대시보드</x:t>
+    <x:t>군포중학교 무료급식(24회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예수님 믿고 구원 받기를</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(39회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(34회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 노숙인을 위한 봉사</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(20회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(22회)</x:t>
+    <x:t>기도대상자관리 표준양식</x:t>
   </x:si>
   <x:si>
-    <x:t>예수님 믿고 구원 받기를</x:t>
+    <x:t>군포중학교 무료급식(14회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(15회)</x:t>
+    <x:t>군포중학교 무료급식(30회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(27회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(25회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역 초등생 무료 라면급식</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(36회)</x:t>
@@ -374,22 +158,37 @@
     <x:t>군포중학교 무료급식(28회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(38회)</x:t>
+    <x:t>군포중학교 무료급식(41회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(21회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(31회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역사회 무료급식 봉사</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(18회)</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(39회)</x:t>
+    <x:t>군포중학교 무료급식(26회)</x:t>
   </x:si>
   <x:si>
-    <x:t>지역사회 무료급식 봉사</x:t>
+    <x:t>군포중학교 무료급식(22회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(15회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(42회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교 무료급식(38회)</x:t>
   </x:si>
   <x:si>
     <x:t>군포중학교 무료급식(44회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포중학교 무료급식(42회)</x:t>
   </x:si>
   <x:si>
     <x:t>일만상상 프로젝트 표준양식</x:t>
@@ -398,46 +197,346 @@
     <x:t>군포영문 인근 초등학생</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(34회)</x:t>
+    <x:t>김문희</x:t>
   </x:si>
   <x:si>
-    <x:t>화면에 표시할 앱 버전 정보</x:t>
+    <x:t>왕용봉</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(21회)</x:t>
+    <x:t>정유진</x:t>
   </x:si>
   <x:si>
-    <x:t>지역 초등생 무료 라면급식</x:t>
+    <x:t>성별</x:t>
   </x:si>
   <x:si>
-    <x:t>수원역 노숙인을 위한 봉사</x:t>
+    <x:t>남</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(26회)</x:t>
+    <x:t>여</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(41회)</x:t>
+    <x:t>송옥섭</x:t>
   </x:si>
   <x:si>
-    <x:t>기도대상자관리 표준양식</x:t>
+    <x:t>정해걸</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(25회)</x:t>
+    <x:t>Y</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(14회)</x:t>
+    <x:t>김해선</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(31회)</x:t>
+    <x:t>김란옥</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(27회)</x:t>
+    <x:t>성용</x:t>
   </x:si>
   <x:si>
-    <x:t>군포중학교 무료급식(30회)</x:t>
+    <x:t>박미연</x:t>
   </x:si>
   <x:si>
-    <x:t>선택 입력</x:t>
+    <x:t>김종찬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최재용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청년부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박미옥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인정보는 꼭 필요한 범위만 입력하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홈 화면과 전도현황의 연간 영혼구원 목표</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실적은 실제 활동 기준으로 기록하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계별 인원, 목표 달성률, 담당자별 현황</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도대상자와 프로젝트 자료를 자동 집계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연락처, 관계, 최근만남일, 다음연락일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>친구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건강</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초청</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새가족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송선례</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미라클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장윤주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기숙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한명희</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교역자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접촉</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>값</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱버전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박형렬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박종훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김계화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방선근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이정아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정다혜</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김정화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>변순덕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정의룡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김충남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이세진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이수경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하희정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김인일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김옥금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최주현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최향옥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윤정호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사업명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일만상상 프로젝트는 한 사업·행사당 한 행으로 작성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 시트의 수치는 다른 시트에서 자동 계산됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한 영혼의 기도·관계·초청·정착 과정을 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관리번호, 이름, 담당자, 진행상태, 기도제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행상태는 가장 최근 단계 하나만 선택합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도대상자는 한 사람당 한 행으로 작성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트번호, 사업명, 분야, 상태, 담당부서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복음전도와 마을돌봄 사역을 사업 단위로 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사랑그룹</x:t>
   </x:si>
   <x:si>
     <x:t>관리번호</x:t>
@@ -452,16 +551,10 @@
     <x:t>변경 시</x:t>
   </x:si>
   <x:si>
-    <x:t>관계구분</x:t>
+    <x:t>선택 입력</x:t>
   </x:si>
   <x:si>
-    <x:t>작성 시트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월 1회 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도제목상세</x:t>
+    <x:t>관계구분</x:t>
   </x:si>
   <x:si>
     <x:t>핵심 목적</x:t>
@@ -470,148 +563,100 @@
     <x:t>전도현황</x:t>
   </x:si>
   <x:si>
+    <x:t>앱에서 활용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월 1회 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 시트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도제목상세</x:t>
+  </x:si>
+  <x:si>
     <x:t>기도대상자관리</x:t>
   </x:si>
   <x:si>
     <x:t>최근만남일</x:t>
   </x:si>
   <x:si>
-    <x:t>앱에서 활용</x:t>
+    <x:t>기도응답일</x:t>
   </x:si>
   <x:si>
     <x:t>다음연락일</x:t>
   </x:si>
   <x:si>
-    <x:t>기도응답일</x:t>
+    <x:t>군우편입</x:t>
   </x:si>
   <x:si>
-    <x:t>군우편입</x:t>
+    <x:t>프로젝트 상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기도제목구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심활동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새가족등록일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트번호</x:t>
   </x:si>
   <x:si>
     <x:t>사용여부</x:t>
   </x:si>
   <x:si>
-    <x:t>군우편입일</x:t>
+    <x:t>P-0001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사진·자료링크</x:t>
   </x:si>
   <x:si>
     <x:t>기도시작일</x:t>
   </x:si>
   <x:si>
-    <x:t>작성 원칙</x:t>
+    <x:t>관계상세</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트분야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장 동료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공개범위</x:t>
   </x:si>
   <x:si>
     <x:t>진행상태</x:t>
   </x:si>
   <x:si>
-    <x:t>관계상세</x:t>
+    <x:t>작성 원칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군우편입일</x:t>
   </x:si>
   <x:si>
     <x:t>등록교인일</x:t>
   </x:si>
   <x:si>
-    <x:t>공개범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도제목구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트분야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트번호</x:t>
-  </x:si>
-  <x:si>
     <x:t>P-0002</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새가족등록일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핵심활동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사진·자료링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장 동료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>큰 누나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행률(%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수정 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제지출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교회방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교회방문일</x:t>
+    <x:t>연간출석목표</x:t>
   </x:si>
   <x:si>
     <x:t>성과구분</x:t>
   </x:si>
   <x:si>
-    <x:t>연간출석목표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>V10.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관계형성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기준연도</x:t>
-  </x:si>
-  <x:si>
     <x:t>라면Day</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복음전도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>등록교인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교회방문 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담당부서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성과수량</x:t>
   </x:si>
   <x:si>
     <x:t>P-0013</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사업목적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문화교육</x:t>
+    <x:t>프로젝트상태</x:t>
   </x:si>
   <x:si>
     <x:t>예산합계</x:t>
@@ -629,28 +674,100 @@
     <x:t>P-0026</x:t>
   </x:si>
   <x:si>
+    <x:t>교회방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등록교인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제지출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교회방문 이상</x:t>
+  </x:si>
+  <x:si>
     <x:t>P-0027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교회방문일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관계형성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성과수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행률(%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기준연도</x:t>
   </x:si>
   <x:si>
     <x:t>사회복지</x:t>
   </x:si>
   <x:si>
-    <x:t>무료급식</x:t>
+    <x:t>복음전도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사업목적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당부서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문화교육</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수정 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>큰 누나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0016</x:t>
   </x:si>
   <x:si>
     <x:t>고향 친구</x:t>
   </x:si>
   <x:si>
-    <x:t>결과/열매</x:t>
+    <x:t>P-0019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>민선이네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군포중학교</x:t>
   </x:si>
   <x:si>
     <x:t>P-0010</x:t>
   </x:si>
   <x:si>
-    <x:t>생수나눔</x:t>
+    <x:t>P-0021</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0016</x:t>
+    <x:t>P-0005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생수나눔</x:t>
   </x:si>
   <x:si>
     <x:t>P-0004</x:t>
@@ -659,55 +776,31 @@
     <x:t>P-0012</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0005</x:t>
+    <x:t>무료급식</x:t>
   </x:si>
   <x:si>
     <x:t>P-0023</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>민선이네</x:t>
-  </x:si>
-  <x:si>
     <x:t>자선봉사단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0025</x:t>
   </x:si>
   <x:si>
     <x:t>P-0022</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0003</x:t>
+    <x:t>결과/열매</x:t>
   </x:si>
   <x:si>
-    <x:t>P-0021</x:t>
+    <x:t>P-0020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-0018</x:t>
   </x:si>
   <x:si>
     <x:t>P-0015</x:t>
   </x:si>
   <x:si>
     <x:t>P-0014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-0008</x:t>
   </x:si>
   <x:si>
     <x:t>P-0007</x:t>
@@ -719,31 +812,10 @@
     <x:t>오픈하우스</x:t>
   </x:si>
   <x:si>
-    <x:t>※ 한 사람당 한 행 작성 · 노란색 열은 필수 · 날짜는 YYYY-MM-DD 형식</x:t>
+    <x:t>P-0011</x:t>
   </x:si>
   <x:si>
-    <x:t>진행상태는 가장 최근 단계 하나만 선택합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도대상자는 한 사람당 한 행으로 작성합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복음을 열린 마음으로 듣고 예배에 참여하도록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 시트의 수치는 다른 시트에서 자동 계산됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관리번호, 이름, 담당자, 진행상태, 기도제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한 영혼의 기도·관계·초청·정착 과정을 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트번호, 사업명, 분야, 상태, 담당부서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복음전도와 마을돌봄 사역을 사업 단위로 관리</x:t>
+    <x:t>P-0008</x:t>
   </x:si>
   <x:si>
     <x:t>예시 자료는 삭제하고 실제 자료로 교체한 뒤 GitHub에 업로드합니다.</x:t>
@@ -752,31 +824,10 @@
     <x:t>※ 한 사업·행사당 한 행 작성 · 노란색 열은 필수 · 진행률은 0~100%</x:t>
   </x:si>
   <x:si>
-    <x:t>일만상상 프로젝트는 한 사업·행사당 한 행으로 작성합니다.</x:t>
+    <x:t>라면 Day_16</x:t>
   </x:si>
   <x:si>
     <x:t>라면 Day_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포지역 지역사회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생수나눔 봉사_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_16</x:t>
   </x:si>
   <x:si>
     <x:t>라면 Day_12</x:t>
@@ -788,10 +839,28 @@
     <x:t>라면 Day_15</x:t>
   </x:si>
   <x:si>
+    <x:t>군포지역 지역사회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생수나눔 봉사_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_20</x:t>
+  </x:si>
+  <x:si>
     <x:t>라면 Day_18</x:t>
   </x:si>
   <x:si>
-    <x:t>라면 Day_17</x:t>
+    <x:t>라면 Day_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_19</x:t>
   </x:si>
   <x:si>
     <x:t>라면 Day_14</x:t>
@@ -800,10 +869,7 @@
     <x:t>라면 Day_11</x:t>
   </x:si>
   <x:si>
-    <x:t>라면 Day_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_10</x:t>
+    <x:t>M-2026-056</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식_5</x:t>
@@ -812,73 +878,49 @@
     <x:t>라면 Day_27</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-047</x:t>
+    <x:t>M-2026-045</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-056</x:t>
+    <x:t>M-2026-061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_17</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-040</x:t>
   </x:si>
   <x:si>
+    <x:t>M-2026-043</x:t>
+  </x:si>
+  <x:si>
     <x:t>M-2026-037</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-044</x:t>
+    <x:t>M-2026-047</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-045</x:t>
+    <x:t>M-2026-054</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-039</x:t>
+    <x:t>M-2026-050</x:t>
   </x:si>
   <x:si>
     <x:t>라면 Day_28</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-038</x:t>
+    <x:t>M-2026-008</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-050</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-057</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-008</x:t>
+    <x:t>M-2026-039</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-053</x:t>
@@ -887,34 +929,37 @@
     <x:t>M-2026-058</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-060</x:t>
+    <x:t>M-2026-010</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-052</x:t>
+    <x:t>M-2026-006</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-051</x:t>
+    <x:t>M-2026-055</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-059</x:t>
+    <x:t>M-2026-041</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-011</x:t>
+    <x:t>M-2026-020</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-048</x:t>
+    <x:t>M-2026-057</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-007</x:t>
+    <x:t>M-2026-046</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-014</x:t>
+    <x:t>M-2026-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-038</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-017</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-016</x:t>
+    <x:t>M-2026-007</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식_12</x:t>
@@ -923,10 +968,28 @@
     <x:t>M-2026-015</x:t>
   </x:si>
   <x:si>
+    <x:t>M-2026-060</x:t>
+  </x:si>
+  <x:si>
     <x:t>M-2026-018</x:t>
   </x:si>
   <x:si>
+    <x:t>M-2026-051</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-059</x:t>
+  </x:si>
+  <x:si>
     <x:t>M-2026-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-048</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-012</x:t>
@@ -935,13 +998,19 @@
     <x:t>M-2026-009</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-021</x:t>
+    <x:t>M-2026-016</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-022</x:t>
+    <x:t>M-2026-011</x:t>
   </x:si>
   <x:si>
-    <x:t>수원역 무료급식_8</x:t>
+    <x:t>M-2026-032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-021</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식_9</x:t>
@@ -950,16 +1019,19 @@
     <x:t>M-2026-019</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-023</x:t>
+    <x:t>수원역 무료급식_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-022</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식_7</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-032</x:t>
+    <x:t>M-2026-024</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-005</x:t>
+    <x:t>M-2026-025</x:t>
   </x:si>
   <x:si>
     <x:t>수원역 무료급식_10</x:t>
@@ -968,25 +1040,31 @@
     <x:t>M-2026-029</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-024</x:t>
-  </x:si>
-  <x:si>
     <x:t>M-2026-035</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-036</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-027</x:t>
+    <x:t>M-2026-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-023</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 기도대상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연계된 기도대상자</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-031</x:t>
@@ -995,55 +1073,70 @@
     <x:t>M-2026-026</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-033</x:t>
+    <x:t>M-2026-027</x:t>
   </x:si>
   <x:si>
-    <x:t>M-2026-028</x:t>
+    <x:t>직접 입력 없음</x:t>
   </x:si>
   <x:si>
     <x:t>일만상상 프로젝트</x:t>
   </x:si>
   <x:si>
-    <x:t>필요할 때만 수정</x:t>
+    <x:t>연간영혼구원목표</x:t>
   </x:si>
   <x:si>
     <x:t>연도 네 자리 입력</x:t>
   </x:si>
   <x:si>
-    <x:t>전체 기도대상자</x:t>
+    <x:t>일만상상프로젝트</x:t>
   </x:si>
   <x:si>
     <x:t>2026-08-01</x:t>
   </x:si>
   <x:si>
-    <x:t>연계된 기도대상자</x:t>
-  </x:si>
-  <x:si>
     <x:t>소속부서/소그룹</x:t>
   </x:si>
   <x:si>
-    <x:t>직접 입력 없음</x:t>
+    <x:t>라면 Day_26</x:t>
   </x:si>
   <x:si>
-    <x:t>일만상상프로젝트</x:t>
+    <x:t>업무를 통한 관계형성</x:t>
   </x:si>
   <x:si>
-    <x:t>연간영혼구원목표</x:t>
+    <x:t>GESMS 환경설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>값 열의 숫자만 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-2026-002</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-003</x:t>
   </x:si>
   <x:si>
-    <x:t>진행중 프로젝트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>값 열의 숫자만 수정</x:t>
+    <x:t>대상지역/대상자</x:t>
   </x:si>
   <x:si>
     <x:t>M-2026-001</x:t>
   </x:si>
   <x:si>
-    <x:t>대상지역/대상자</x:t>
+    <x:t>이번 주 연락대상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 인근 노숙인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행중 프로젝트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라면 Day_23</x:t>
   </x:si>
   <x:si>
     <x:t>연간 출석 목표 인원</x:t>
@@ -1052,91 +1145,16 @@
     <x:t>라면 Day_24</x:t>
   </x:si>
   <x:si>
-    <x:t>이번 주 연락대상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 인근 노숙인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESMS 환경설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M-2026-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무를 통한 관계형성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라면 Day_25</x:t>
-  </x:si>
-  <x:si>
     <x:t>수원역 무료급식_11</x:t>
   </x:si>
   <x:si>
-    <x:t>다음연락일은 실제 연락 계획이 있을 때 입력합니다.</x:t>
+    <x:t>자동연동</x:t>
   </x:si>
   <x:si>
-    <x:t>GESMS V10.0 전도·영혼구원 표준자료 입력 양식</x:t>
+    <x:t>수정하지 않음</x:t>
   </x:si>
   <x:si>
-    <x:t>기도대상자관리 및 일만상상프로젝트 시트의 자료를 자동 집계합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기도대상자와 프로젝트 자료를 자동 집계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실적은 실제 활동 기준으로 기록하세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인정보는 꼭 필요한 범위만 입력하세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홈 화면과 전도현황의 연간 영혼구원 목표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연락처, 관계, 최근만남일, 다음연락일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계별 인원, 목표 달성률, 담당자별 현황</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포중학교 결식아동 무료식사 제공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통계와 목표를 적용할 기준 연도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포 지역사회 어르신 무료식사 제공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예산, 참여인원, 성과, 결과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸 박지우 건강과 교회 참석을 위해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>누나의 건강(암)이 회복되기를</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사업 시작을 하는데 어려움이 없도록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방과후 결식아동 다수로 식사 제공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전도현황, 연락대상, 단계별 통계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행률, 분야별 현황, 성과 집계</x:t>
+    <x:t>인도자</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1188,18 +1206,50 @@
       <x:color rgb="ffffffff"/>
       <x:b val="1"/>
     </x:font>
-    <x:font>
-      <x:name val="Malgun Gothic"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff163a5f"/>
-      <x:b val="1"/>
-    </x:font>
-    <x:font>
-      <x:name val="Malgun Gothic"/>
-      <x:sz val="10"/>
-      <x:color rgb="ffff0000"/>
-      <x:b val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff163a5f"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff163a5f"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="10"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="10"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -1515,7 +1565,7 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1802,9 +1852,6 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -1969,6 +2016,32 @@
       <mc:Fallback>
         <x:xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -2613,85 +2686,37 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd7dff4"/>
-              <x:bgColor rgb="ffd7dff4"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:left style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:left>
-            <x:right style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:right>
-            <x:top style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:bottom>
-            <x:vertical style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:vertical>
-            <x:horizontal style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:horizontal>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd7dff4"/>
-              <x:bgColor rgb="ffd7dff4"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:left style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:left>
-            <x:right style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:right>
-            <x:top style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:bottom>
-            <x:vertical style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:vertical>
-            <x:horizontal style="thin">
-              <x:color rgb="ffffffff"/>
-            </x:horizontal>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff2e7d32"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -2724,6 +2749,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffb23a48"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -2756,6 +2782,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff2e7d32"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -2809,7 +2836,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/charts/chart0.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:date1904 val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -3021,7 +3048,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:date1904 val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -3209,7 +3236,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/drawings/drawing0.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3275,7 +3302,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrayerTargetsTable" displayName="PrayerTargetsTable" ref="A4:AD200">
+<x:table xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrayerTargetsTable" displayName="PrayerTargetsTable" ref="A4:AD198">
   <x:tableColumns count="30">
     <x:tableColumn id="1" name="관리번호"/>
     <x:tableColumn id="2" name="이름" dataDxfId="14"/>
@@ -3283,7 +3310,7 @@
     <x:tableColumn id="4" name="연락처" dataDxfId="13"/>
     <x:tableColumn id="5" name="관계구분" dataDxfId="13"/>
     <x:tableColumn id="6" name="관계상세" dataDxfId="13"/>
-    <x:tableColumn id="7" name="담당자" dataDxfId="15"/>
+    <x:tableColumn id="7" name="인도자" dataDxfId="15"/>
     <x:tableColumn id="8" name="소속부서/소그룹"/>
     <x:tableColumn id="9" name="기도제목구분" dataDxfId="12"/>
     <x:tableColumn id="10" name="기도제목상세"/>
@@ -3494,7 +3521,7 @@
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
     <x:col min="1" max="1" width="14" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="62.81640625" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="28" style="3" customWidth="1"/>
     <x:col min="4" max="4" width="26" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="25" style="3" customWidth="1"/>
@@ -3504,16 +3531,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:52">
-      <x:c r="A1" s="44" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="B1" s="44"/>
-      <x:c r="C1" s="44"/>
-      <x:c r="D1" s="44"/>
-      <x:c r="E1" s="44"/>
-      <x:c r="F1" s="44"/>
-      <x:c r="G1" s="44"/>
-      <x:c r="H1" s="44"/>
+      <x:c r="A1" s="43" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
       <x:c r="I1" s="4"/>
       <x:c r="J1" s="4"/>
       <x:c r="K1" s="4"/>
@@ -3560,14 +3587,14 @@
       <x:c r="AZ1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:52">
-      <x:c r="A2" s="44"/>
-      <x:c r="B2" s="44"/>
-      <x:c r="C2" s="44"/>
-      <x:c r="D2" s="44"/>
-      <x:c r="E2" s="44"/>
-      <x:c r="F2" s="44"/>
-      <x:c r="G2" s="44"/>
-      <x:c r="H2" s="44"/>
+      <x:c r="A2" s="43"/>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+      <x:c r="F2" s="43"/>
+      <x:c r="G2" s="43"/>
+      <x:c r="H2" s="43"/>
       <x:c r="I2" s="4"/>
       <x:c r="J2" s="4"/>
       <x:c r="K2" s="4"/>
@@ -3669,28 +3696,28 @@
     </x:row>
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G4" s="5" t="s">
-        <x:v>172</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>140</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -3739,28 +3766,28 @@
     </x:row>
     <x:row r="5" spans="1:52" ht="26.350000000000001">
       <x:c r="A5" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>355</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>332</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E5" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
-        <x:v>360</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H5" s="6" t="s">
-        <x:v>235</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -3809,28 +3836,28 @@
     </x:row>
     <x:row r="6" spans="1:52" ht="26.350000000000001">
       <x:c r="A6" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>237</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>236</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E6" s="6" t="s">
-        <x:v>359</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>369</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="6" t="s">
-        <x:v>141</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H6" s="6" t="s">
-        <x:v>357</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="J6" s="4"/>
@@ -3879,28 +3906,28 @@
     </x:row>
     <x:row r="7" spans="1:52" ht="26.350000000000001">
       <x:c r="A7" s="6" t="s">
-        <x:v>325</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>333</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>239</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>238</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E7" s="6" t="s">
-        <x:v>364</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="6" t="s">
-        <x:v>370</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>356</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -4002,16 +4029,16 @@
       <x:c r="AZ8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:52">
-      <x:c r="A9" s="46" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="B9" s="46"/>
-      <x:c r="C9" s="46"/>
-      <x:c r="D9" s="46"/>
-      <x:c r="E9" s="46"/>
-      <x:c r="F9" s="46"/>
-      <x:c r="G9" s="46"/>
-      <x:c r="H9" s="46"/>
+      <x:c r="A9" s="45" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B9" s="45"/>
+      <x:c r="C9" s="45"/>
+      <x:c r="D9" s="45"/>
+      <x:c r="E9" s="45"/>
+      <x:c r="F9" s="45"/>
+      <x:c r="G9" s="45"/>
+      <x:c r="H9" s="45"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -4057,12 +4084,12 @@
       <x:c r="AY9" s="4"/>
       <x:c r="AZ9" s="4"/>
     </x:row>
-    <x:row r="10" spans="1:52" ht="39.549999999999997">
+    <x:row r="10" spans="1:52">
       <x:c r="A10" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="4"/>
@@ -4115,12 +4142,12 @@
       <x:c r="AY10" s="4"/>
       <x:c r="AZ10" s="4"/>
     </x:row>
-    <x:row r="11" spans="1:52" ht="39.549999999999997">
+    <x:row r="11" spans="1:52">
       <x:c r="A11" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>232</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C11" s="4"/>
       <x:c r="D11" s="4"/>
@@ -4173,12 +4200,12 @@
       <x:c r="AY11" s="4"/>
       <x:c r="AZ11" s="4"/>
     </x:row>
-    <x:row r="12" spans="1:52" ht="39.549999999999997">
+    <x:row r="12" spans="1:52">
       <x:c r="A12" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B12" s="8" t="s">
-        <x:v>352</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
@@ -4231,12 +4258,12 @@
       <x:c r="AY12" s="4"/>
       <x:c r="AZ12" s="4"/>
     </x:row>
-    <x:row r="13" spans="1:52" ht="39.549999999999997">
+    <x:row r="13" spans="1:52">
       <x:c r="A13" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B13" s="8" t="s">
-        <x:v>242</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
@@ -4289,12 +4316,12 @@
       <x:c r="AY13" s="4"/>
       <x:c r="AZ13" s="4"/>
     </x:row>
-    <x:row r="14" spans="1:52" ht="52.700000000000003">
+    <x:row r="14" spans="1:52">
       <x:c r="A14" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="8" t="s">
-        <x:v>240</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="4"/>
@@ -15484,7 +15511,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet2"/>
-  <x:dimension ref="A1:AZ220"/>
+  <x:dimension ref="A1:AZ218"/>
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
     <x:col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -15511,38 +15538,38 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:52">
-      <x:c r="A1" s="44" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B1" s="44"/>
-      <x:c r="C1" s="44"/>
-      <x:c r="D1" s="44"/>
-      <x:c r="E1" s="44"/>
-      <x:c r="F1" s="44"/>
-      <x:c r="G1" s="44"/>
-      <x:c r="H1" s="44"/>
-      <x:c r="I1" s="44"/>
-      <x:c r="J1" s="44"/>
-      <x:c r="K1" s="44"/>
-      <x:c r="L1" s="44"/>
-      <x:c r="M1" s="44"/>
-      <x:c r="N1" s="44"/>
-      <x:c r="O1" s="44"/>
-      <x:c r="P1" s="44"/>
-      <x:c r="Q1" s="44"/>
-      <x:c r="R1" s="44"/>
-      <x:c r="S1" s="44"/>
-      <x:c r="T1" s="44"/>
-      <x:c r="U1" s="44"/>
-      <x:c r="V1" s="44"/>
-      <x:c r="W1" s="44"/>
-      <x:c r="X1" s="44"/>
-      <x:c r="Y1" s="44"/>
-      <x:c r="Z1" s="44"/>
-      <x:c r="AA1" s="44"/>
-      <x:c r="AB1" s="44"/>
-      <x:c r="AC1" s="44"/>
-      <x:c r="AD1" s="44"/>
+      <x:c r="A1" s="43" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
+      <x:c r="I1" s="43"/>
+      <x:c r="J1" s="43"/>
+      <x:c r="K1" s="43"/>
+      <x:c r="L1" s="43"/>
+      <x:c r="M1" s="43"/>
+      <x:c r="N1" s="43"/>
+      <x:c r="O1" s="43"/>
+      <x:c r="P1" s="43"/>
+      <x:c r="Q1" s="43"/>
+      <x:c r="R1" s="43"/>
+      <x:c r="S1" s="43"/>
+      <x:c r="T1" s="43"/>
+      <x:c r="U1" s="43"/>
+      <x:c r="V1" s="43"/>
+      <x:c r="W1" s="43"/>
+      <x:c r="X1" s="43"/>
+      <x:c r="Y1" s="43"/>
+      <x:c r="Z1" s="43"/>
+      <x:c r="AA1" s="43"/>
+      <x:c r="AB1" s="43"/>
+      <x:c r="AC1" s="43"/>
+      <x:c r="AD1" s="43"/>
       <x:c r="AE1" s="4"/>
       <x:c r="AF1" s="4"/>
       <x:c r="AG1" s="4"/>
@@ -15567,36 +15594,36 @@
       <x:c r="AZ1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:52">
-      <x:c r="A2" s="44"/>
-      <x:c r="B2" s="44"/>
-      <x:c r="C2" s="44"/>
-      <x:c r="D2" s="44"/>
-      <x:c r="E2" s="44"/>
-      <x:c r="F2" s="44"/>
-      <x:c r="G2" s="44"/>
-      <x:c r="H2" s="44"/>
-      <x:c r="I2" s="44"/>
-      <x:c r="J2" s="44"/>
-      <x:c r="K2" s="44"/>
-      <x:c r="L2" s="44"/>
-      <x:c r="M2" s="44"/>
-      <x:c r="N2" s="44"/>
-      <x:c r="O2" s="44"/>
-      <x:c r="P2" s="44"/>
-      <x:c r="Q2" s="44"/>
-      <x:c r="R2" s="44"/>
-      <x:c r="S2" s="44"/>
-      <x:c r="T2" s="44"/>
-      <x:c r="U2" s="44"/>
-      <x:c r="V2" s="44"/>
-      <x:c r="W2" s="44"/>
-      <x:c r="X2" s="44"/>
-      <x:c r="Y2" s="44"/>
-      <x:c r="Z2" s="44"/>
-      <x:c r="AA2" s="44"/>
-      <x:c r="AB2" s="44"/>
-      <x:c r="AC2" s="44"/>
-      <x:c r="AD2" s="44"/>
+      <x:c r="A2" s="43"/>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+      <x:c r="F2" s="43"/>
+      <x:c r="G2" s="43"/>
+      <x:c r="H2" s="43"/>
+      <x:c r="I2" s="43"/>
+      <x:c r="J2" s="43"/>
+      <x:c r="K2" s="43"/>
+      <x:c r="L2" s="43"/>
+      <x:c r="M2" s="43"/>
+      <x:c r="N2" s="43"/>
+      <x:c r="O2" s="43"/>
+      <x:c r="P2" s="43"/>
+      <x:c r="Q2" s="43"/>
+      <x:c r="R2" s="43"/>
+      <x:c r="S2" s="43"/>
+      <x:c r="T2" s="43"/>
+      <x:c r="U2" s="43"/>
+      <x:c r="V2" s="43"/>
+      <x:c r="W2" s="43"/>
+      <x:c r="X2" s="43"/>
+      <x:c r="Y2" s="43"/>
+      <x:c r="Z2" s="43"/>
+      <x:c r="AA2" s="43"/>
+      <x:c r="AB2" s="43"/>
+      <x:c r="AC2" s="43"/>
+      <x:c r="AD2" s="43"/>
       <x:c r="AE2" s="4"/>
       <x:c r="AF2" s="4"/>
       <x:c r="AG2" s="4"/>
@@ -15621,38 +15648,38 @@
       <x:c r="AZ2" s="4"/>
     </x:row>
     <x:row r="3" spans="1:52">
-      <x:c r="A3" s="45" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="B3" s="45"/>
-      <x:c r="C3" s="45"/>
-      <x:c r="D3" s="45"/>
-      <x:c r="E3" s="45"/>
-      <x:c r="F3" s="45"/>
-      <x:c r="G3" s="45"/>
-      <x:c r="H3" s="45"/>
-      <x:c r="I3" s="45"/>
-      <x:c r="J3" s="45"/>
-      <x:c r="K3" s="45"/>
-      <x:c r="L3" s="45"/>
-      <x:c r="M3" s="45"/>
-      <x:c r="N3" s="45"/>
-      <x:c r="O3" s="45"/>
-      <x:c r="P3" s="45"/>
-      <x:c r="Q3" s="45"/>
-      <x:c r="R3" s="45"/>
-      <x:c r="S3" s="45"/>
-      <x:c r="T3" s="45"/>
-      <x:c r="U3" s="45"/>
-      <x:c r="V3" s="45"/>
-      <x:c r="W3" s="45"/>
-      <x:c r="X3" s="45"/>
-      <x:c r="Y3" s="45"/>
-      <x:c r="Z3" s="45"/>
-      <x:c r="AA3" s="45"/>
-      <x:c r="AB3" s="45"/>
-      <x:c r="AC3" s="45"/>
-      <x:c r="AD3" s="45"/>
+      <x:c r="A3" s="44" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="44"/>
+      <x:c r="C3" s="44"/>
+      <x:c r="D3" s="44"/>
+      <x:c r="E3" s="44"/>
+      <x:c r="F3" s="44"/>
+      <x:c r="G3" s="44"/>
+      <x:c r="H3" s="44"/>
+      <x:c r="I3" s="44"/>
+      <x:c r="J3" s="44"/>
+      <x:c r="K3" s="44"/>
+      <x:c r="L3" s="44"/>
+      <x:c r="M3" s="44"/>
+      <x:c r="N3" s="44"/>
+      <x:c r="O3" s="44"/>
+      <x:c r="P3" s="44"/>
+      <x:c r="Q3" s="44"/>
+      <x:c r="R3" s="44"/>
+      <x:c r="S3" s="44"/>
+      <x:c r="T3" s="44"/>
+      <x:c r="U3" s="44"/>
+      <x:c r="V3" s="44"/>
+      <x:c r="W3" s="44"/>
+      <x:c r="X3" s="44"/>
+      <x:c r="Y3" s="44"/>
+      <x:c r="Z3" s="44"/>
+      <x:c r="AA3" s="44"/>
+      <x:c r="AB3" s="44"/>
+      <x:c r="AC3" s="44"/>
+      <x:c r="AD3" s="44"/>
       <x:c r="AE3" s="4"/>
       <x:c r="AF3" s="4"/>
       <x:c r="AG3" s="4"/>
@@ -15678,94 +15705,94 @@
     </x:row>
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="21" t="s">
-        <x:v>138</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B4" s="21" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G4" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>331</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>162</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J4" s="21" t="s">
-        <x:v>145</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="K4" s="5" t="s">
-        <x:v>156</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="L4" s="21" t="s">
-        <x:v>158</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="M4" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="N4" s="5" t="s">
-        <x:v>182</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="O4" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="P4" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q4" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="R4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="S4" s="5" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="T4" s="5" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="T4" s="5" t="s">
-        <x:v>153</x:v>
-      </x:c>
       <x:c r="U4" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="V4" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="W4" s="5" t="s">
-        <x:v>178</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="X4" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Y4" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="Z4" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="AA4" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="AB4" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="AC4" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AD4" s="21" t="s">
-        <x:v>154</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="AE4" s="4"/>
       <x:c r="AF4" s="4"/>
@@ -15792,30 +15819,30 @@
     </x:row>
     <x:row r="5" spans="1:52">
       <x:c r="A5" s="9" t="s">
-        <x:v>166</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B5" s="22" t="s">
-        <x:v>81</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C5" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D5" s="18"/>
       <x:c r="E5" s="18"/>
       <x:c r="F5" s="18"/>
       <x:c r="G5" s="25"/>
       <x:c r="H5" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I5" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J5" s="9"/>
       <x:c r="K5" s="26">
         <x:v>45689</x:v>
       </x:c>
-      <x:c r="L5" s="33" t="s">
-        <x:v>22</x:v>
+      <x:c r="L5" s="32" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M5" s="18"/>
       <x:c r="N5" s="18"/>
@@ -15860,38 +15887,38 @@
     </x:row>
     <x:row r="6" spans="1:52">
       <x:c r="A6" s="9" t="s">
-        <x:v>165</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B6" s="23" t="s">
-        <x:v>94</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C6" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D6" s="18"/>
       <x:c r="E6" s="18" t="s">
-        <x:v>21</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F6" s="18" t="s">
-        <x:v>204</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G6" s="25" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I6" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J6" s="9" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K6" s="26">
         <x:v>45809</x:v>
       </x:c>
       <x:c r="L6" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M6" s="18"/>
       <x:c r="N6" s="18"/>
@@ -15936,30 +15963,30 @@
     </x:row>
     <x:row r="7" spans="1:52">
       <x:c r="A7" s="9" t="s">
-        <x:v>222</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B7" s="22" t="s">
-        <x:v>86</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C7" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D7" s="18"/>
       <x:c r="E7" s="18"/>
       <x:c r="F7" s="18"/>
       <x:c r="G7" s="25"/>
       <x:c r="H7" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I7" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J7" s="9"/>
       <x:c r="K7" s="26">
         <x:v>45689</x:v>
       </x:c>
-      <x:c r="L7" s="33" t="s">
-        <x:v>22</x:v>
+      <x:c r="L7" s="32" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M7" s="18"/>
       <x:c r="N7" s="18"/>
@@ -16004,38 +16031,38 @@
     </x:row>
     <x:row r="8" spans="1:52">
       <x:c r="A8" s="9" t="s">
-        <x:v>209</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B8" s="23" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C8" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D8" s="18"/>
       <x:c r="E8" s="18" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F8" s="18" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G8" s="25" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H8" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I8" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J8" s="9" t="s">
-        <x:v>365</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="26">
         <x:v>43831</x:v>
       </x:c>
       <x:c r="L8" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M8" s="18"/>
       <x:c r="N8" s="18"/>
@@ -16044,7 +16071,7 @@
       <x:c r="Q8" s="18"/>
       <x:c r="R8" s="18"/>
       <x:c r="S8" s="18" t="s">
-        <x:v>1</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="T8" s="18"/>
       <x:c r="U8" s="26"/>
@@ -16082,30 +16109,30 @@
     </x:row>
     <x:row r="9" spans="1:52">
       <x:c r="A9" s="9" t="s">
-        <x:v>211</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B9" s="22" t="s">
-        <x:v>83</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C9" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D9" s="18"/>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18"/>
       <x:c r="G9" s="25"/>
       <x:c r="H9" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I9" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J9" s="9"/>
       <x:c r="K9" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L9" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M9" s="18"/>
       <x:c r="N9" s="18"/>
@@ -16150,30 +16177,30 @@
     </x:row>
     <x:row r="10" spans="1:52">
       <x:c r="A10" s="9" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B10" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C10" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D10" s="18"/>
       <x:c r="E10" s="18"/>
       <x:c r="F10" s="18"/>
       <x:c r="G10" s="25"/>
       <x:c r="H10" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I10" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J10" s="9"/>
       <x:c r="K10" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L10" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M10" s="18"/>
       <x:c r="N10" s="18"/>
@@ -16218,30 +16245,30 @@
     </x:row>
     <x:row r="11" spans="1:52">
       <x:c r="A11" s="9" t="s">
-        <x:v>228</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B11" s="22" t="s">
-        <x:v>88</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D11" s="18"/>
       <x:c r="E11" s="18"/>
       <x:c r="F11" s="18"/>
       <x:c r="G11" s="25"/>
       <x:c r="H11" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I11" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J11" s="9"/>
       <x:c r="K11" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L11" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M11" s="18"/>
       <x:c r="N11" s="18"/>
@@ -16286,38 +16313,38 @@
     </x:row>
     <x:row r="12" spans="1:52">
       <x:c r="A12" s="9" t="s">
-        <x:v>227</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B12" s="23" t="s">
-        <x:v>78</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C12" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D12" s="18"/>
       <x:c r="E12" s="18" t="s">
-        <x:v>57</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F12" s="18" t="s">
-        <x:v>173</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G12" s="25" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H12" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I12" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>366</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K12" s="26">
         <x:v>42860</x:v>
       </x:c>
       <x:c r="L12" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M12" s="18"/>
       <x:c r="N12" s="18"/>
@@ -16362,30 +16389,30 @@
     </x:row>
     <x:row r="13" spans="1:52">
       <x:c r="A13" s="9" t="s">
-        <x:v>193</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B13" s="22" t="s">
-        <x:v>71</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C13" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="18"/>
       <x:c r="E13" s="18"/>
       <x:c r="F13" s="18"/>
       <x:c r="G13" s="25"/>
       <x:c r="H13" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I13" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J13" s="9"/>
       <x:c r="K13" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L13" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M13" s="18"/>
       <x:c r="N13" s="18"/>
@@ -16430,36 +16457,36 @@
     </x:row>
     <x:row r="14" spans="1:52">
       <x:c r="A14" s="9" t="s">
-        <x:v>206</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B14" s="23" t="s">
-        <x:v>59</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C14" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="18"/>
       <x:c r="E14" s="18" t="s">
-        <x:v>55</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F14" s="18" t="s">
-        <x:v>171</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G14" s="25" t="s">
-        <x:v>96</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H14" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I14" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J14" s="9"/>
       <x:c r="K14" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L14" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M14" s="18"/>
       <x:c r="N14" s="18"/>
@@ -16504,30 +16531,30 @@
     </x:row>
     <x:row r="15" spans="1:52">
       <x:c r="A15" s="9" t="s">
-        <x:v>226</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B15" s="22" t="s">
-        <x:v>75</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C15" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="18"/>
       <x:c r="E15" s="18"/>
       <x:c r="F15" s="18"/>
       <x:c r="G15" s="25"/>
       <x:c r="H15" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I15" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J15" s="9"/>
       <x:c r="K15" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L15" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M15" s="18"/>
       <x:c r="N15" s="18"/>
@@ -16572,38 +16599,30 @@
     </x:row>
     <x:row r="16" spans="1:52">
       <x:c r="A16" s="9" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="B16" s="23" t="s">
-        <x:v>80</x:v>
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="s">
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C16" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D16" s="18"/>
-      <x:c r="E16" s="18" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G16" s="25" t="s">
-        <x:v>87</x:v>
-      </x:c>
+      <x:c r="E16" s="18"/>
+      <x:c r="F16" s="18"/>
+      <x:c r="G16" s="25"/>
       <x:c r="H16" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I16" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="s">
-        <x:v>234</x:v>
-      </x:c>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="J16" s="9"/>
       <x:c r="K16" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L16" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M16" s="18"/>
       <x:c r="N16" s="18"/>
@@ -16648,30 +16667,30 @@
     </x:row>
     <x:row r="17" spans="1:52">
       <x:c r="A17" s="9" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B17" s="22" t="s">
-        <x:v>67</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B17" s="23" t="s">
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C17" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="18"/>
       <x:c r="E17" s="18"/>
       <x:c r="F17" s="18"/>
       <x:c r="G17" s="25"/>
       <x:c r="H17" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I17" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J17" s="9"/>
       <x:c r="K17" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L17" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M17" s="18"/>
       <x:c r="N17" s="18"/>
@@ -16716,30 +16735,38 @@
     </x:row>
     <x:row r="18" spans="1:52">
       <x:c r="A18" s="9" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="B18" s="23" t="s">
-        <x:v>89</x:v>
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="s">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C18" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D18" s="18"/>
-      <x:c r="E18" s="18"/>
-      <x:c r="F18" s="18"/>
-      <x:c r="G18" s="25"/>
+      <x:c r="E18" s="18" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="G18" s="25" t="s">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="H18" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I18" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J18" s="9"/>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="J18" s="9" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="K18" s="26">
-        <x:v>45689</x:v>
+        <x:v>44228</x:v>
       </x:c>
       <x:c r="L18" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M18" s="18"/>
       <x:c r="N18" s="18"/>
@@ -16784,38 +16811,30 @@
     </x:row>
     <x:row r="19" spans="1:52">
       <x:c r="A19" s="9" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="B19" s="22" t="s">
-        <x:v>82</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C19" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D19" s="18"/>
-      <x:c r="E19" s="18" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="G19" s="25" t="s">
-        <x:v>84</x:v>
-      </x:c>
+      <x:c r="E19" s="18"/>
+      <x:c r="F19" s="18"/>
+      <x:c r="G19" s="25"/>
       <x:c r="H19" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I19" s="18" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="J19" s="9" t="s">
-        <x:v>367</x:v>
-      </x:c>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="J19" s="9"/>
       <x:c r="K19" s="26">
-        <x:v>44228</x:v>
+        <x:v>45689</x:v>
       </x:c>
       <x:c r="L19" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M19" s="18"/>
       <x:c r="N19" s="18"/>
@@ -16860,30 +16879,30 @@
     </x:row>
     <x:row r="20" spans="1:52">
       <x:c r="A20" s="9" t="s">
-        <x:v>208</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B20" s="23" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="C20" s="18" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D20" s="18"/>
       <x:c r="E20" s="18"/>
       <x:c r="F20" s="18"/>
       <x:c r="G20" s="25"/>
       <x:c r="H20" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I20" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J20" s="9"/>
       <x:c r="K20" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L20" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M20" s="18"/>
       <x:c r="N20" s="18"/>
@@ -16928,30 +16947,30 @@
     </x:row>
     <x:row r="21" spans="1:52">
       <x:c r="A21" s="9" t="s">
-        <x:v>192</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B21" s="22" t="s">
-        <x:v>63</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C21" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D21" s="18"/>
       <x:c r="E21" s="18"/>
       <x:c r="F21" s="18"/>
       <x:c r="G21" s="25"/>
       <x:c r="H21" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J21" s="9"/>
       <x:c r="K21" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L21" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M21" s="18"/>
       <x:c r="N21" s="18"/>
@@ -16996,30 +17015,30 @@
     </x:row>
     <x:row r="22" spans="1:52">
       <x:c r="A22" s="9" t="s">
-        <x:v>215</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B22" s="23" t="s">
-        <x:v>72</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C22" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="18"/>
       <x:c r="E22" s="18"/>
       <x:c r="F22" s="18"/>
       <x:c r="G22" s="25"/>
       <x:c r="H22" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I22" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J22" s="9"/>
       <x:c r="K22" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L22" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M22" s="18"/>
       <x:c r="N22" s="18"/>
@@ -17064,30 +17083,30 @@
     </x:row>
     <x:row r="23" spans="1:52">
       <x:c r="A23" s="9" t="s">
-        <x:v>216</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B23" s="22" t="s">
-        <x:v>70</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C23" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D23" s="18"/>
       <x:c r="E23" s="18"/>
       <x:c r="F23" s="18"/>
       <x:c r="G23" s="25"/>
       <x:c r="H23" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I23" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J23" s="9"/>
       <x:c r="K23" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L23" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M23" s="18"/>
       <x:c r="N23" s="18"/>
@@ -17132,30 +17151,30 @@
     </x:row>
     <x:row r="24" spans="1:52">
       <x:c r="A24" s="9" t="s">
-        <x:v>213</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B24" s="23" t="s">
-        <x:v>93</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C24" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="18"/>
       <x:c r="E24" s="18"/>
       <x:c r="F24" s="18"/>
       <x:c r="G24" s="25"/>
       <x:c r="H24" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I24" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J24" s="9"/>
       <x:c r="K24" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L24" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M24" s="18"/>
       <x:c r="N24" s="18"/>
@@ -17200,30 +17219,30 @@
     </x:row>
     <x:row r="25" spans="1:52">
       <x:c r="A25" s="9" t="s">
-        <x:v>223</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B25" s="22" t="s">
-        <x:v>218</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C25" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="18"/>
       <x:c r="E25" s="18"/>
       <x:c r="F25" s="18"/>
       <x:c r="G25" s="25"/>
       <x:c r="H25" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I25" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J25" s="9"/>
       <x:c r="K25" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L25" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M25" s="18"/>
       <x:c r="N25" s="18"/>
@@ -17268,30 +17287,30 @@
     </x:row>
     <x:row r="26" spans="1:52">
       <x:c r="A26" s="9" t="s">
-        <x:v>221</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B26" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D26" s="18"/>
       <x:c r="E26" s="18"/>
       <x:c r="F26" s="18"/>
       <x:c r="G26" s="25"/>
       <x:c r="H26" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I26" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J26" s="9"/>
       <x:c r="K26" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L26" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M26" s="18"/>
       <x:c r="N26" s="18"/>
@@ -17336,30 +17355,30 @@
     </x:row>
     <x:row r="27" spans="1:52">
       <x:c r="A27" s="9" t="s">
-        <x:v>212</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B27" s="22" t="s">
-        <x:v>60</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C27" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D27" s="18"/>
       <x:c r="E27" s="18"/>
       <x:c r="F27" s="18"/>
       <x:c r="G27" s="25"/>
       <x:c r="H27" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I27" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J27" s="9"/>
       <x:c r="K27" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L27" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M27" s="18"/>
       <x:c r="N27" s="18"/>
@@ -17404,30 +17423,30 @@
     </x:row>
     <x:row r="28" spans="1:52">
       <x:c r="A28" s="9" t="s">
-        <x:v>217</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B28" s="23" t="s">
-        <x:v>66</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C28" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D28" s="18"/>
       <x:c r="E28" s="18"/>
       <x:c r="F28" s="18"/>
       <x:c r="G28" s="25"/>
       <x:c r="H28" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I28" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L28" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M28" s="18"/>
       <x:c r="N28" s="18"/>
@@ -17472,30 +17491,30 @@
     </x:row>
     <x:row r="29" spans="1:52">
       <x:c r="A29" s="9" t="s">
-        <x:v>220</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B29" s="22" t="s">
-        <x:v>92</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C29" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D29" s="18"/>
       <x:c r="E29" s="18"/>
       <x:c r="F29" s="18"/>
       <x:c r="G29" s="25"/>
       <x:c r="H29" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I29" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J29" s="9"/>
       <x:c r="K29" s="26">
         <x:v>45689</x:v>
       </x:c>
       <x:c r="L29" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M29" s="18"/>
       <x:c r="N29" s="18"/>
@@ -17540,39 +17559,57 @@
     </x:row>
     <x:row r="30" spans="1:52">
       <x:c r="A30" s="9" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B30" s="23" t="s">
-        <x:v>68</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B30" s="24" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C30" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D30" s="18"/>
       <x:c r="E30" s="18"/>
       <x:c r="F30" s="18"/>
-      <x:c r="G30" s="25"/>
+      <x:c r="G30" s="25" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="H30" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I30" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J30" s="9"/>
       <x:c r="K30" s="26">
-        <x:v>45689</x:v>
+        <x:v>45992</x:v>
       </x:c>
       <x:c r="L30" s="25" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="M30" s="18"/>
-      <x:c r="N30" s="18"/>
-      <x:c r="O30" s="18"/>
-      <x:c r="P30" s="18"/>
-      <x:c r="Q30" s="18"/>
-      <x:c r="R30" s="18"/>
-      <x:c r="S30" s="18"/>
-      <x:c r="T30" s="18"/>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="M30" s="18" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="O30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="S30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="T30" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="U30" s="26"/>
       <x:c r="V30" s="26"/>
       <x:c r="W30" s="26"/>
@@ -17608,39 +17645,57 @@
     </x:row>
     <x:row r="31" spans="1:52">
       <x:c r="A31" s="9" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B31" s="22" t="s">
-        <x:v>95</x:v>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B31" s="25" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C31" s="18" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D31" s="18"/>
       <x:c r="E31" s="18"/>
       <x:c r="F31" s="18"/>
-      <x:c r="G31" s="25"/>
+      <x:c r="G31" s="25" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="H31" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I31" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J31" s="9"/>
       <x:c r="K31" s="26">
-        <x:v>45689</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L31" s="25" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="M31" s="18"/>
-      <x:c r="N31" s="18"/>
-      <x:c r="O31" s="18"/>
-      <x:c r="P31" s="18"/>
-      <x:c r="Q31" s="18"/>
-      <x:c r="R31" s="18"/>
-      <x:c r="S31" s="18"/>
-      <x:c r="T31" s="18"/>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="M31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="O31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="S31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="T31" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="U31" s="26"/>
       <x:c r="V31" s="26"/>
       <x:c r="W31" s="26"/>
@@ -17675,26 +17730,58 @@
       <x:c r="AZ31" s="4"/>
     </x:row>
     <x:row r="32" spans="1:52">
-      <x:c r="A32" s="9"/>
-      <x:c r="B32" s="24"/>
-      <x:c r="C32" s="18"/>
+      <x:c r="A32" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B32" s="25" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C32" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="D32" s="18"/>
       <x:c r="E32" s="18"/>
       <x:c r="F32" s="18"/>
-      <x:c r="G32" s="25"/>
-      <x:c r="H32" s="8"/>
-      <x:c r="I32" s="18"/>
+      <x:c r="G32" s="25" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H32" s="51" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="I32" s="18" t="s">
+        <x:v>119</x:v>
+      </x:c>
       <x:c r="J32" s="9"/>
-      <x:c r="K32" s="26"/>
-      <x:c r="L32" s="25"/>
-      <x:c r="M32" s="18"/>
-      <x:c r="N32" s="18"/>
-      <x:c r="O32" s="18"/>
-      <x:c r="P32" s="18"/>
-      <x:c r="Q32" s="18"/>
-      <x:c r="R32" s="18"/>
-      <x:c r="S32" s="18"/>
-      <x:c r="T32" s="18"/>
+      <x:c r="K32" s="26">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="L32" s="25" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="M32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="O32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="S32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="T32" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="U32" s="26"/>
       <x:c r="V32" s="26"/>
       <x:c r="W32" s="26"/>
@@ -17729,26 +17816,58 @@
       <x:c r="AZ32" s="4"/>
     </x:row>
     <x:row r="33" spans="1:52">
-      <x:c r="A33" s="9"/>
-      <x:c r="B33" s="25"/>
-      <x:c r="C33" s="18"/>
+      <x:c r="A33" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B33" s="25" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C33" s="18" t="s">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="D33" s="18"/>
       <x:c r="E33" s="18"/>
       <x:c r="F33" s="18"/>
-      <x:c r="G33" s="25"/>
-      <x:c r="H33" s="8"/>
-      <x:c r="I33" s="18"/>
+      <x:c r="G33" s="25" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H33" s="51" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="I33" s="18" t="s">
+        <x:v>119</x:v>
+      </x:c>
       <x:c r="J33" s="9"/>
-      <x:c r="K33" s="26"/>
-      <x:c r="L33" s="25"/>
-      <x:c r="M33" s="18"/>
-      <x:c r="N33" s="18"/>
-      <x:c r="O33" s="18"/>
-      <x:c r="P33" s="18"/>
-      <x:c r="Q33" s="18"/>
-      <x:c r="R33" s="18"/>
-      <x:c r="S33" s="18"/>
-      <x:c r="T33" s="18"/>
+      <x:c r="K33" s="26">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="L33" s="25" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="M33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="O33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="S33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="T33" s="52" t="s">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="U33" s="26"/>
       <x:c r="V33" s="26"/>
       <x:c r="W33" s="26"/>
@@ -26693,36 +26812,36 @@
       <x:c r="AZ198" s="4"/>
     </x:row>
     <x:row r="199" spans="1:52">
-      <x:c r="A199" s="9"/>
-      <x:c r="B199" s="25"/>
-      <x:c r="C199" s="18"/>
-      <x:c r="D199" s="18"/>
-      <x:c r="E199" s="18"/>
-      <x:c r="F199" s="18"/>
-      <x:c r="G199" s="25"/>
-      <x:c r="H199" s="8"/>
-      <x:c r="I199" s="18"/>
-      <x:c r="J199" s="9"/>
-      <x:c r="K199" s="26"/>
-      <x:c r="L199" s="25"/>
-      <x:c r="M199" s="18"/>
-      <x:c r="N199" s="18"/>
-      <x:c r="O199" s="18"/>
-      <x:c r="P199" s="18"/>
-      <x:c r="Q199" s="18"/>
-      <x:c r="R199" s="18"/>
-      <x:c r="S199" s="18"/>
-      <x:c r="T199" s="18"/>
-      <x:c r="U199" s="26"/>
-      <x:c r="V199" s="26"/>
-      <x:c r="W199" s="26"/>
-      <x:c r="X199" s="26"/>
-      <x:c r="Y199" s="26"/>
-      <x:c r="Z199" s="26"/>
-      <x:c r="AA199" s="26"/>
-      <x:c r="AB199" s="8"/>
-      <x:c r="AC199" s="8"/>
-      <x:c r="AD199" s="9"/>
+      <x:c r="A199" s="4"/>
+      <x:c r="B199" s="19"/>
+      <x:c r="C199" s="19"/>
+      <x:c r="D199" s="19"/>
+      <x:c r="E199" s="19"/>
+      <x:c r="F199" s="19"/>
+      <x:c r="G199" s="19"/>
+      <x:c r="H199" s="4"/>
+      <x:c r="I199" s="19"/>
+      <x:c r="J199" s="4"/>
+      <x:c r="K199" s="19"/>
+      <x:c r="L199" s="19"/>
+      <x:c r="M199" s="19"/>
+      <x:c r="N199" s="19"/>
+      <x:c r="O199" s="19"/>
+      <x:c r="P199" s="19"/>
+      <x:c r="Q199" s="19"/>
+      <x:c r="R199" s="19"/>
+      <x:c r="S199" s="19"/>
+      <x:c r="T199" s="19"/>
+      <x:c r="U199" s="19"/>
+      <x:c r="V199" s="19"/>
+      <x:c r="W199" s="19"/>
+      <x:c r="X199" s="19"/>
+      <x:c r="Y199" s="19"/>
+      <x:c r="Z199" s="19"/>
+      <x:c r="AA199" s="19"/>
+      <x:c r="AB199" s="4"/>
+      <x:c r="AC199" s="4"/>
+      <x:c r="AD199" s="4"/>
       <x:c r="AE199" s="4"/>
       <x:c r="AF199" s="4"/>
       <x:c r="AG199" s="4"/>
@@ -26747,36 +26866,36 @@
       <x:c r="AZ199" s="4"/>
     </x:row>
     <x:row r="200" spans="1:52">
-      <x:c r="A200" s="9"/>
-      <x:c r="B200" s="25"/>
-      <x:c r="C200" s="18"/>
-      <x:c r="D200" s="18"/>
-      <x:c r="E200" s="18"/>
-      <x:c r="F200" s="18"/>
-      <x:c r="G200" s="25"/>
-      <x:c r="H200" s="8"/>
-      <x:c r="I200" s="18"/>
-      <x:c r="J200" s="9"/>
-      <x:c r="K200" s="26"/>
-      <x:c r="L200" s="25"/>
-      <x:c r="M200" s="18"/>
-      <x:c r="N200" s="18"/>
-      <x:c r="O200" s="18"/>
-      <x:c r="P200" s="18"/>
-      <x:c r="Q200" s="18"/>
-      <x:c r="R200" s="18"/>
-      <x:c r="S200" s="18"/>
-      <x:c r="T200" s="18"/>
-      <x:c r="U200" s="26"/>
-      <x:c r="V200" s="26"/>
-      <x:c r="W200" s="26"/>
-      <x:c r="X200" s="26"/>
-      <x:c r="Y200" s="26"/>
-      <x:c r="Z200" s="26"/>
-      <x:c r="AA200" s="26"/>
-      <x:c r="AB200" s="8"/>
-      <x:c r="AC200" s="8"/>
-      <x:c r="AD200" s="9"/>
+      <x:c r="A200" s="4"/>
+      <x:c r="B200" s="19"/>
+      <x:c r="C200" s="19"/>
+      <x:c r="D200" s="19"/>
+      <x:c r="E200" s="19"/>
+      <x:c r="F200" s="19"/>
+      <x:c r="G200" s="19"/>
+      <x:c r="H200" s="4"/>
+      <x:c r="I200" s="19"/>
+      <x:c r="J200" s="4"/>
+      <x:c r="K200" s="19"/>
+      <x:c r="L200" s="19"/>
+      <x:c r="M200" s="19"/>
+      <x:c r="N200" s="19"/>
+      <x:c r="O200" s="19"/>
+      <x:c r="P200" s="19"/>
+      <x:c r="Q200" s="19"/>
+      <x:c r="R200" s="19"/>
+      <x:c r="S200" s="19"/>
+      <x:c r="T200" s="19"/>
+      <x:c r="U200" s="19"/>
+      <x:c r="V200" s="19"/>
+      <x:c r="W200" s="19"/>
+      <x:c r="X200" s="19"/>
+      <x:c r="Y200" s="19"/>
+      <x:c r="Z200" s="19"/>
+      <x:c r="AA200" s="19"/>
+      <x:c r="AB200" s="4"/>
+      <x:c r="AC200" s="4"/>
+      <x:c r="AD200" s="4"/>
       <x:c r="AE200" s="4"/>
       <x:c r="AF200" s="4"/>
       <x:c r="AG200" s="4"/>
@@ -27772,125 +27891,17 @@
       <x:c r="AY218" s="4"/>
       <x:c r="AZ218" s="4"/>
     </x:row>
-    <x:row r="219" spans="1:52">
-      <x:c r="A219" s="4"/>
-      <x:c r="B219" s="19"/>
-      <x:c r="C219" s="19"/>
-      <x:c r="D219" s="19"/>
-      <x:c r="E219" s="19"/>
-      <x:c r="F219" s="19"/>
-      <x:c r="G219" s="19"/>
-      <x:c r="H219" s="4"/>
-      <x:c r="I219" s="19"/>
-      <x:c r="J219" s="4"/>
-      <x:c r="K219" s="19"/>
-      <x:c r="L219" s="19"/>
-      <x:c r="M219" s="19"/>
-      <x:c r="N219" s="19"/>
-      <x:c r="O219" s="19"/>
-      <x:c r="P219" s="19"/>
-      <x:c r="Q219" s="19"/>
-      <x:c r="R219" s="19"/>
-      <x:c r="S219" s="19"/>
-      <x:c r="T219" s="19"/>
-      <x:c r="U219" s="19"/>
-      <x:c r="V219" s="19"/>
-      <x:c r="W219" s="19"/>
-      <x:c r="X219" s="19"/>
-      <x:c r="Y219" s="19"/>
-      <x:c r="Z219" s="19"/>
-      <x:c r="AA219" s="19"/>
-      <x:c r="AB219" s="4"/>
-      <x:c r="AC219" s="4"/>
-      <x:c r="AD219" s="4"/>
-      <x:c r="AE219" s="4"/>
-      <x:c r="AF219" s="4"/>
-      <x:c r="AG219" s="4"/>
-      <x:c r="AH219" s="4"/>
-      <x:c r="AI219" s="4"/>
-      <x:c r="AJ219" s="4"/>
-      <x:c r="AK219" s="4"/>
-      <x:c r="AL219" s="4"/>
-      <x:c r="AM219" s="4"/>
-      <x:c r="AN219" s="4"/>
-      <x:c r="AO219" s="4"/>
-      <x:c r="AP219" s="4"/>
-      <x:c r="AQ219" s="4"/>
-      <x:c r="AR219" s="4"/>
-      <x:c r="AS219" s="4"/>
-      <x:c r="AT219" s="4"/>
-      <x:c r="AU219" s="4"/>
-      <x:c r="AV219" s="4"/>
-      <x:c r="AW219" s="4"/>
-      <x:c r="AX219" s="4"/>
-      <x:c r="AY219" s="4"/>
-      <x:c r="AZ219" s="4"/>
-    </x:row>
-    <x:row r="220" spans="1:52">
-      <x:c r="A220" s="4"/>
-      <x:c r="B220" s="19"/>
-      <x:c r="C220" s="19"/>
-      <x:c r="D220" s="19"/>
-      <x:c r="E220" s="19"/>
-      <x:c r="F220" s="19"/>
-      <x:c r="G220" s="19"/>
-      <x:c r="H220" s="4"/>
-      <x:c r="I220" s="19"/>
-      <x:c r="J220" s="4"/>
-      <x:c r="K220" s="19"/>
-      <x:c r="L220" s="19"/>
-      <x:c r="M220" s="19"/>
-      <x:c r="N220" s="19"/>
-      <x:c r="O220" s="19"/>
-      <x:c r="P220" s="19"/>
-      <x:c r="Q220" s="19"/>
-      <x:c r="R220" s="19"/>
-      <x:c r="S220" s="19"/>
-      <x:c r="T220" s="19"/>
-      <x:c r="U220" s="19"/>
-      <x:c r="V220" s="19"/>
-      <x:c r="W220" s="19"/>
-      <x:c r="X220" s="19"/>
-      <x:c r="Y220" s="19"/>
-      <x:c r="Z220" s="19"/>
-      <x:c r="AA220" s="19"/>
-      <x:c r="AB220" s="4"/>
-      <x:c r="AC220" s="4"/>
-      <x:c r="AD220" s="4"/>
-      <x:c r="AE220" s="4"/>
-      <x:c r="AF220" s="4"/>
-      <x:c r="AG220" s="4"/>
-      <x:c r="AH220" s="4"/>
-      <x:c r="AI220" s="4"/>
-      <x:c r="AJ220" s="4"/>
-      <x:c r="AK220" s="4"/>
-      <x:c r="AL220" s="4"/>
-      <x:c r="AM220" s="4"/>
-      <x:c r="AN220" s="4"/>
-      <x:c r="AO220" s="4"/>
-      <x:c r="AP220" s="4"/>
-      <x:c r="AQ220" s="4"/>
-      <x:c r="AR220" s="4"/>
-      <x:c r="AS220" s="4"/>
-      <x:c r="AT220" s="4"/>
-      <x:c r="AU220" s="4"/>
-      <x:c r="AV220" s="4"/>
-      <x:c r="AW220" s="4"/>
-      <x:c r="AX220" s="4"/>
-      <x:c r="AY220" s="4"/>
-      <x:c r="AZ220" s="4"/>
-    </x:row>
   </x:sheetData>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AD2"/>
     <x:mergeCell ref="A3:AD3"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="L6:L6 L8:L200">
+  <x:conditionalFormatting sqref="L6:L6 L8:L198">
     <x:cfRule type="expression" dxfId="21" priority="3">
       <x:formula>L6="군우편입"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="V5:V200">
+  <x:conditionalFormatting sqref="V5:V198">
     <x:cfRule type="expression" dxfId="22" priority="4">
       <x:formula>AND(V5&lt;&gt;"",V5&lt;TODAY(),AD5="사용")</x:formula>
     </x:cfRule>
@@ -27905,50 +27916,50 @@
       <x:formula>L7="군우편입"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="17">
-    <x:dataValidation type="list" sqref="C5:C200">
+  <x:dataValidations count="19">
+    <x:dataValidation type="list" sqref="C5:C198">
       <x:formula1>목록!$A$2:$A$3</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E5:E200">
+    <x:dataValidation type="list" sqref="E5:E198">
       <x:formula1>목록!$B$2:$B$7</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H5:H200">
+    <x:dataValidation type="list" sqref="H5:H31 H34:H198">
       <x:formula1>목록!$J$2:$J$6</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I5:I200">
+    <x:dataValidation type="list" sqref="I5:I198">
       <x:formula1>목록!$D$2:$D$8</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="L8:L200 L6:L6">
+    <x:dataValidation type="list" sqref="L8:L198 L6:L6">
       <x:formula1>목록!$C$2:$C$10</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="AB5:AB200">
+    <x:dataValidation type="list" sqref="AB5:AB198">
       <x:formula1>목록!$E$2:$E$5</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="AD5:AD200">
+    <x:dataValidation type="list" sqref="AD5:AD198">
       <x:formula1>목록!$F$2:$F$3</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="M5:M200">
+    <x:dataValidation type="list" sqref="M5:M30 M34:M198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="N5:N200">
+    <x:dataValidation type="list" sqref="N5:N29 N34:N198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="O5:O200">
+    <x:dataValidation type="list" sqref="O5:O29 O34:O198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="P5:P200">
+    <x:dataValidation type="list" sqref="P5:P29 P34:P198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="Q5:Q200">
+    <x:dataValidation type="list" sqref="Q5:Q29 Q34:Q198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="R5:R200">
+    <x:dataValidation type="list" sqref="R5:R29 R34:R198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="S5:S200">
+    <x:dataValidation type="list" sqref="S5:S29 S34:S198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="T5:T200">
+    <x:dataValidation type="list" sqref="T5:T30 M31:T33 N30:S30 T34:T198">
       <x:formula1>",Y"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L5:L5">
@@ -27956,6 +27967,12 @@
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L7:L7">
       <x:formula1>목록!$C$2:$C$10</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H32:H32">
+      <x:formula1>목록!$J$2:$J$6</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H33:H33">
+      <x:formula1>목록!$J$2:$J$6</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -27993,30 +28010,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:52">
-      <x:c r="A1" s="44" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B1" s="44"/>
-      <x:c r="C1" s="44"/>
-      <x:c r="D1" s="44"/>
-      <x:c r="E1" s="44"/>
-      <x:c r="F1" s="44"/>
-      <x:c r="G1" s="44"/>
-      <x:c r="H1" s="44"/>
-      <x:c r="I1" s="44"/>
-      <x:c r="J1" s="44"/>
-      <x:c r="K1" s="44"/>
-      <x:c r="L1" s="44"/>
-      <x:c r="M1" s="44"/>
-      <x:c r="N1" s="44"/>
-      <x:c r="O1" s="44"/>
-      <x:c r="P1" s="44"/>
-      <x:c r="Q1" s="44"/>
-      <x:c r="R1" s="44"/>
-      <x:c r="S1" s="44"/>
-      <x:c r="T1" s="44"/>
-      <x:c r="U1" s="44"/>
-      <x:c r="V1" s="44"/>
+      <x:c r="A1" s="43" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
+      <x:c r="I1" s="43"/>
+      <x:c r="J1" s="43"/>
+      <x:c r="K1" s="43"/>
+      <x:c r="L1" s="43"/>
+      <x:c r="M1" s="43"/>
+      <x:c r="N1" s="43"/>
+      <x:c r="O1" s="43"/>
+      <x:c r="P1" s="43"/>
+      <x:c r="Q1" s="43"/>
+      <x:c r="R1" s="43"/>
+      <x:c r="S1" s="43"/>
+      <x:c r="T1" s="43"/>
+      <x:c r="U1" s="43"/>
+      <x:c r="V1" s="43"/>
       <x:c r="W1" s="4"/>
       <x:c r="X1" s="4"/>
       <x:c r="Y1" s="4"/>
@@ -28049,28 +28066,28 @@
       <x:c r="AZ1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:52">
-      <x:c r="A2" s="44"/>
-      <x:c r="B2" s="44"/>
-      <x:c r="C2" s="44"/>
-      <x:c r="D2" s="44"/>
-      <x:c r="E2" s="44"/>
-      <x:c r="F2" s="44"/>
-      <x:c r="G2" s="44"/>
-      <x:c r="H2" s="44"/>
-      <x:c r="I2" s="44"/>
-      <x:c r="J2" s="44"/>
-      <x:c r="K2" s="44"/>
-      <x:c r="L2" s="44"/>
-      <x:c r="M2" s="44"/>
-      <x:c r="N2" s="44"/>
-      <x:c r="O2" s="44"/>
-      <x:c r="P2" s="44"/>
-      <x:c r="Q2" s="44"/>
-      <x:c r="R2" s="44"/>
-      <x:c r="S2" s="44"/>
-      <x:c r="T2" s="44"/>
-      <x:c r="U2" s="44"/>
-      <x:c r="V2" s="44"/>
+      <x:c r="A2" s="43"/>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+      <x:c r="F2" s="43"/>
+      <x:c r="G2" s="43"/>
+      <x:c r="H2" s="43"/>
+      <x:c r="I2" s="43"/>
+      <x:c r="J2" s="43"/>
+      <x:c r="K2" s="43"/>
+      <x:c r="L2" s="43"/>
+      <x:c r="M2" s="43"/>
+      <x:c r="N2" s="43"/>
+      <x:c r="O2" s="43"/>
+      <x:c r="P2" s="43"/>
+      <x:c r="Q2" s="43"/>
+      <x:c r="R2" s="43"/>
+      <x:c r="S2" s="43"/>
+      <x:c r="T2" s="43"/>
+      <x:c r="U2" s="43"/>
+      <x:c r="V2" s="43"/>
       <x:c r="W2" s="4"/>
       <x:c r="X2" s="4"/>
       <x:c r="Y2" s="4"/>
@@ -28103,30 +28120,30 @@
       <x:c r="AZ2" s="4"/>
     </x:row>
     <x:row r="3" spans="1:52">
-      <x:c r="A3" s="45" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="B3" s="45"/>
-      <x:c r="C3" s="45"/>
-      <x:c r="D3" s="45"/>
-      <x:c r="E3" s="45"/>
-      <x:c r="F3" s="45"/>
-      <x:c r="G3" s="45"/>
-      <x:c r="H3" s="45"/>
-      <x:c r="I3" s="45"/>
-      <x:c r="J3" s="45"/>
-      <x:c r="K3" s="45"/>
-      <x:c r="L3" s="45"/>
-      <x:c r="M3" s="45"/>
-      <x:c r="N3" s="45"/>
-      <x:c r="O3" s="45"/>
-      <x:c r="P3" s="45"/>
-      <x:c r="Q3" s="45"/>
-      <x:c r="R3" s="45"/>
-      <x:c r="S3" s="45"/>
-      <x:c r="T3" s="45"/>
-      <x:c r="U3" s="45"/>
-      <x:c r="V3" s="45"/>
+      <x:c r="A3" s="44" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B3" s="44"/>
+      <x:c r="C3" s="44"/>
+      <x:c r="D3" s="44"/>
+      <x:c r="E3" s="44"/>
+      <x:c r="F3" s="44"/>
+      <x:c r="G3" s="44"/>
+      <x:c r="H3" s="44"/>
+      <x:c r="I3" s="44"/>
+      <x:c r="J3" s="44"/>
+      <x:c r="K3" s="44"/>
+      <x:c r="L3" s="44"/>
+      <x:c r="M3" s="44"/>
+      <x:c r="N3" s="44"/>
+      <x:c r="O3" s="44"/>
+      <x:c r="P3" s="44"/>
+      <x:c r="Q3" s="44"/>
+      <x:c r="R3" s="44"/>
+      <x:c r="S3" s="44"/>
+      <x:c r="T3" s="44"/>
+      <x:c r="U3" s="44"/>
+      <x:c r="V3" s="44"/>
       <x:c r="W3" s="4"/>
       <x:c r="X3" s="4"/>
       <x:c r="Y3" s="4"/>
@@ -28160,70 +28177,70 @@
     </x:row>
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="21" t="s">
-        <x:v>164</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B4" s="21" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="F4" s="21" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G4" s="21" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C4" s="21" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="F4" s="21" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G4" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J4" s="21" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="K4" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L4" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="M4" s="5" t="s">
-        <x:v>199</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="N4" s="5" t="s">
-        <x:v>198</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="O4" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="P4" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Q4" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="R4" s="5" t="s">
-        <x:v>190</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="S4" s="5" t="s">
-        <x:v>330</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="T4" s="5" t="s">
-        <x:v>205</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="U4" s="5" t="s">
-        <x:v>170</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="V4" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="W4" s="4"/>
       <x:c r="X4" s="4"/>
@@ -28258,25 +28275,25 @@
     </x:row>
     <x:row r="5" spans="1:52">
       <x:c r="A5" s="30" t="s">
-        <x:v>338</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B5" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F5" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G5" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H5" s="28">
         <x:v>46214</x:v>
@@ -28285,7 +28302,7 @@
         <x:v>46214</x:v>
       </x:c>
       <x:c r="J5" s="27" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K5" s="12">
         <x:v>0</x:v>
@@ -28303,10 +28320,10 @@
         <x:v>0.33000000000000002</x:v>
       </x:c>
       <x:c r="P5" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R5" s="4"/>
       <x:c r="S5" s="4"/>
@@ -28346,25 +28363,25 @@
     </x:row>
     <x:row r="6" spans="1:52" s="2" customFormat="1">
       <x:c r="A6" s="30" t="s">
-        <x:v>344</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>260</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F6" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G6" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="28">
         <x:v>46217</x:v>
@@ -28373,7 +28390,7 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="J6" s="27" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K6" s="12">
         <x:v>0</x:v>
@@ -28391,10 +28408,10 @@
         <x:v>0.40999999999999998</x:v>
       </x:c>
       <x:c r="P6" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R6" s="4"/>
       <x:c r="S6" s="4"/>
@@ -28434,25 +28451,25 @@
     </x:row>
     <x:row r="7" spans="1:52" s="1" customFormat="1">
       <x:c r="A7" s="30" t="s">
-        <x:v>335</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B7" s="29" t="s">
-        <x:v>257</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F7" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G7" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H7" s="28">
         <x:v>46221</x:v>
@@ -28461,7 +28478,7 @@
         <x:v>46221</x:v>
       </x:c>
       <x:c r="J7" s="27" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K7" s="12">
         <x:v>0</x:v>
@@ -28479,10 +28496,10 @@
         <x:v>0.35999999999999999</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R7" s="4"/>
       <x:c r="S7" s="4"/>
@@ -28522,25 +28539,25 @@
     </x:row>
     <x:row r="8" spans="1:52" s="1" customFormat="1">
       <x:c r="A8" s="30" t="s">
-        <x:v>347</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B8" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C8" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F8" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G8" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="28">
         <x:v>46228</x:v>
@@ -28549,7 +28566,7 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="J8" s="27" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K8" s="12">
         <x:v>0</x:v>
@@ -28567,10 +28584,10 @@
         <x:v>0.40000000000000002</x:v>
       </x:c>
       <x:c r="P8" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R8" s="4"/>
       <x:c r="S8" s="4"/>
@@ -28610,34 +28627,34 @@
     </x:row>
     <x:row r="9" spans="1:52" s="2" customFormat="1">
       <x:c r="A9" s="30" t="s">
-        <x:v>311</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
-        <x:v>245</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F9" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G9" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="28" t="s">
-        <x:v>329</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="I9" s="28">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="J9" s="27" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K9" s="12">
         <x:v>0</x:v>
@@ -28654,11 +28671,11 @@
       <x:c r="O9" s="13">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P9" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P9" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4"/>
@@ -28698,25 +28715,25 @@
     </x:row>
     <x:row r="10" spans="1:52" s="1" customFormat="1">
       <x:c r="A10" s="30" t="s">
-        <x:v>277</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B10" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C10" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F10" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G10" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H10" s="28">
         <x:v>46235</x:v>
@@ -28725,7 +28742,7 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K10" s="12">
         <x:v>0</x:v>
@@ -28743,10 +28760,10 @@
         <x:v>0.42999999999999999</x:v>
       </x:c>
       <x:c r="P10" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4"/>
@@ -28786,25 +28803,25 @@
     </x:row>
     <x:row r="11" spans="1:52" s="2" customFormat="1">
       <x:c r="A11" s="30" t="s">
-        <x:v>293</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B11" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>368</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F11" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G11" s="31" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H11" s="28">
         <x:v>46232</x:v>
@@ -28813,7 +28830,7 @@
         <x:v>46232</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K11" s="12">
         <x:v>176000</x:v>
@@ -28831,10 +28848,10 @@
         <x:v>0.31</x:v>
       </x:c>
       <x:c r="P11" s="4" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="Q11" s="40" t="s">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="39" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4"/>
@@ -28874,55 +28891,55 @@
     </x:row>
     <x:row r="12" spans="1:52">
       <x:c r="A12" s="30" t="s">
-        <x:v>284</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B12" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E12" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D12" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F12" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G12" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H12" s="40">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="I12" s="41">
+      <x:c r="I12" s="40">
         <x:v>46233</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K12" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K12" s="41">
         <x:v>134000</x:v>
       </x:c>
-      <x:c r="L12" s="42">
+      <x:c r="L12" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="40">
+      <x:c r="M12" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N12" s="40">
+      <x:c r="N12" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O12" s="13">
         <x:v>0.34000000000000002</x:v>
       </x:c>
-      <x:c r="P12" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P12" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4"/>
@@ -28962,55 +28979,55 @@
     </x:row>
     <x:row r="13" spans="1:52" s="1" customFormat="1">
       <x:c r="A13" s="30" t="s">
-        <x:v>302</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B13" s="29" t="s">
-        <x:v>97</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D13" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E13" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F13" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G13" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H13" s="40">
         <x:v>46239</x:v>
       </x:c>
-      <x:c r="I13" s="41">
+      <x:c r="I13" s="40">
         <x:v>46239</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K13" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K13" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L13" s="42">
+      <x:c r="L13" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40">
+      <x:c r="M13" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N13" s="40">
+      <x:c r="N13" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O13" s="13">
         <x:v>0.35999999999999999</x:v>
       </x:c>
-      <x:c r="P13" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P13" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="4"/>
@@ -29050,55 +29067,55 @@
     </x:row>
     <x:row r="14" spans="1:52" s="1" customFormat="1">
       <x:c r="A14" s="30" t="s">
-        <x:v>280</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B14" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D14" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E14" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D14" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E14" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F14" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G14" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H14" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H14" s="40">
         <x:v>46240</x:v>
       </x:c>
-      <x:c r="I14" s="41">
+      <x:c r="I14" s="40">
         <x:v>46240</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K14" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K14" s="41">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="L14" s="42">
+      <x:c r="L14" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="40">
+      <x:c r="M14" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N14" s="40">
+      <x:c r="N14" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O14" s="13">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="P14" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P14" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4"/>
@@ -29138,25 +29155,25 @@
     </x:row>
     <x:row r="15" spans="1:52" s="1" customFormat="1">
       <x:c r="A15" s="30" t="s">
-        <x:v>291</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B15" s="29" t="s">
-        <x:v>256</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C15" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F15" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G15" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="28">
         <x:v>46242</x:v>
@@ -29165,7 +29182,7 @@
         <x:v>46242</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K15" s="12">
         <x:v>0</x:v>
@@ -29183,10 +29200,10 @@
         <x:v>0.46000000000000002</x:v>
       </x:c>
       <x:c r="P15" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4"/>
@@ -29226,25 +29243,25 @@
     </x:row>
     <x:row r="16" spans="1:52" s="1" customFormat="1">
       <x:c r="A16" s="30" t="s">
-        <x:v>301</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B16" s="10" t="s">
-        <x:v>309</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F16" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G16" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="28">
         <x:v>46245</x:v>
@@ -29253,7 +29270,7 @@
         <x:v>46245</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K16" s="12">
         <x:v>0</x:v>
@@ -29270,11 +29287,11 @@
       <x:c r="O16" s="13">
         <x:v>0.57999999999999996</x:v>
       </x:c>
-      <x:c r="P16" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P16" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4"/>
@@ -29314,55 +29331,55 @@
     </x:row>
     <x:row r="17" spans="1:52" s="1" customFormat="1">
       <x:c r="A17" s="30" t="s">
-        <x:v>300</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B17" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D17" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E17" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D17" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E17" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F17" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G17" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H17" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H17" s="40">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I17" s="41">
+      <x:c r="I17" s="40">
         <x:v>46246</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K17" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K17" s="41">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="L17" s="42">
+      <x:c r="L17" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40">
+      <x:c r="M17" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N17" s="40">
+      <x:c r="N17" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O17" s="13">
         <x:v>0.40999999999999998</x:v>
       </x:c>
-      <x:c r="P17" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P17" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R17" s="4"/>
       <x:c r="S17" s="4"/>
@@ -29402,55 +29419,55 @@
     </x:row>
     <x:row r="18" spans="1:52" s="1" customFormat="1">
       <x:c r="A18" s="30" t="s">
-        <x:v>294</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B18" s="29" t="s">
-        <x:v>104</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D18" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E18" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D18" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E18" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F18" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G18" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H18" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="40">
         <x:v>46247</x:v>
       </x:c>
-      <x:c r="I18" s="41">
+      <x:c r="I18" s="40">
         <x:v>46247</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K18" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K18" s="41">
         <x:v>104000</x:v>
       </x:c>
-      <x:c r="L18" s="42">
+      <x:c r="L18" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="40">
+      <x:c r="M18" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N18" s="40">
+      <x:c r="N18" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O18" s="13">
         <x:v>0.42999999999999999</x:v>
       </x:c>
-      <x:c r="P18" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P18" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R18" s="4"/>
       <x:c r="S18" s="4"/>
@@ -29490,25 +29507,25 @@
     </x:row>
     <x:row r="19" spans="1:52" s="1" customFormat="1">
       <x:c r="A19" s="30" t="s">
-        <x:v>298</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B19" s="10" t="s">
-        <x:v>253</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E19" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F19" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G19" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H19" s="28">
         <x:v>46249</x:v>
@@ -29517,7 +29534,7 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K19" s="12">
         <x:v>0</x:v>
@@ -29535,10 +29552,10 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="P19" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R19" s="4"/>
       <x:c r="S19" s="4"/>
@@ -29578,55 +29595,55 @@
     </x:row>
     <x:row r="20" spans="1:52" s="1" customFormat="1">
       <x:c r="A20" s="30" t="s">
-        <x:v>296</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B20" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D20" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E20" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D20" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E20" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F20" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G20" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H20" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H20" s="40">
         <x:v>46253</x:v>
       </x:c>
-      <x:c r="I20" s="41">
+      <x:c r="I20" s="40">
         <x:v>46253</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K20" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K20" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L20" s="42">
+      <x:c r="L20" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="40">
+      <x:c r="M20" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N20" s="40">
+      <x:c r="N20" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O20" s="13">
         <x:v>0.45000000000000001</x:v>
       </x:c>
-      <x:c r="P20" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P20" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R20" s="4"/>
       <x:c r="S20" s="4"/>
@@ -29666,55 +29683,55 @@
     </x:row>
     <x:row r="21" spans="1:52" s="1" customFormat="1">
       <x:c r="A21" s="30" t="s">
-        <x:v>295</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B21" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D21" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E21" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D21" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E21" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F21" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G21" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H21" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H21" s="40">
         <x:v>46254</x:v>
       </x:c>
-      <x:c r="I21" s="41">
+      <x:c r="I21" s="40">
         <x:v>46254</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K21" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K21" s="41">
         <x:v>104000</x:v>
       </x:c>
-      <x:c r="L21" s="42">
+      <x:c r="L21" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40">
+      <x:c r="M21" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N21" s="40">
+      <x:c r="N21" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O21" s="13">
         <x:v>0.46999999999999997</x:v>
       </x:c>
-      <x:c r="P21" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P21" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R21" s="4"/>
       <x:c r="S21" s="4"/>
@@ -29754,55 +29771,55 @@
     </x:row>
     <x:row r="22" spans="1:52" s="1" customFormat="1">
       <x:c r="A22" s="30" t="s">
-        <x:v>299</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B22" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D22" s="40" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E22" s="40" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D22" s="39" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E22" s="39" t="s">
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F22" s="31" t="s">
-        <x:v>219</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G22" s="31" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H22" s="41">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H22" s="40">
         <x:v>46256</x:v>
       </x:c>
-      <x:c r="I22" s="41">
+      <x:c r="I22" s="40">
         <x:v>46256</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K22" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K22" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="42">
+      <x:c r="L22" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="40">
+      <x:c r="M22" s="39">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N22" s="40">
+      <x:c r="N22" s="39">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O22" s="13">
         <x:v>1</x:v>
       </x:c>
       <x:c r="P22" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R22" s="4"/>
       <x:c r="S22" s="4"/>
@@ -29842,25 +29859,25 @@
     </x:row>
     <x:row r="23" spans="1:52" s="1" customFormat="1">
       <x:c r="A23" s="30" t="s">
-        <x:v>307</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B23" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C23" s="10" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E23" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F23" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G23" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H23" s="28">
         <x:v>46256</x:v>
@@ -29869,7 +29886,7 @@
         <x:v>46256</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K23" s="12">
         <x:v>0</x:v>
@@ -29887,10 +29904,10 @@
         <x:v>0.53000000000000003</x:v>
       </x:c>
       <x:c r="P23" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R23" s="4"/>
       <x:c r="S23" s="4"/>
@@ -29930,55 +29947,55 @@
     </x:row>
     <x:row r="24" spans="1:52" s="1" customFormat="1">
       <x:c r="A24" s="30" t="s">
-        <x:v>275</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B24" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C24" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D24" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E24" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D24" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E24" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F24" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G24" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H24" s="40">
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="I24" s="41">
+      <x:c r="I24" s="40">
         <x:v>46260</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K24" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K24" s="41">
         <x:v>134000</x:v>
       </x:c>
-      <x:c r="L24" s="42">
+      <x:c r="L24" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="40">
+      <x:c r="M24" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N24" s="40">
+      <x:c r="N24" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O24" s="13">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P24" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P24" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R24" s="4"/>
       <x:c r="S24" s="4"/>
@@ -30018,55 +30035,55 @@
     </x:row>
     <x:row r="25" spans="1:52" s="1" customFormat="1">
       <x:c r="A25" s="30" t="s">
-        <x:v>303</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B25" s="29" t="s">
-        <x:v>98</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C25" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D25" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E25" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D25" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E25" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F25" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G25" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H25" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H25" s="40">
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="I25" s="41">
+      <x:c r="I25" s="40">
         <x:v>46261</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K25" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K25" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L25" s="42">
+      <x:c r="L25" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40">
+      <x:c r="M25" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N25" s="40">
+      <x:c r="N25" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O25" s="13">
         <x:v>0.52000000000000002</x:v>
       </x:c>
-      <x:c r="P25" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P25" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R25" s="4"/>
       <x:c r="S25" s="4"/>
@@ -30106,25 +30123,25 @@
     </x:row>
     <x:row r="26" spans="1:52" s="1" customFormat="1">
       <x:c r="A26" s="30" t="s">
-        <x:v>304</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B26" s="29" t="s">
-        <x:v>305</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C26" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F26" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G26" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H26" s="28">
         <x:v>46263</x:v>
@@ -30133,7 +30150,7 @@
         <x:v>46263</x:v>
       </x:c>
       <x:c r="J26" s="27" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K26" s="12">
         <x:v>0</x:v>
@@ -30150,11 +30167,11 @@
       <x:c r="O26" s="13">
         <x:v>0.66000000000000003</x:v>
       </x:c>
-      <x:c r="P26" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P26" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R26" s="4"/>
       <x:c r="S26" s="4"/>
@@ -30194,25 +30211,25 @@
     </x:row>
     <x:row r="27" spans="1:52" s="1" customFormat="1">
       <x:c r="A27" s="30" t="s">
-        <x:v>308</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B27" s="10" t="s">
-        <x:v>255</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F27" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G27" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H27" s="28">
         <x:v>46263</x:v>
@@ -30221,7 +30238,7 @@
         <x:v>46263</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K27" s="12">
         <x:v>0</x:v>
@@ -30239,10 +30256,10 @@
         <x:v>0.56000000000000005</x:v>
       </x:c>
       <x:c r="P27" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R27" s="4"/>
       <x:c r="S27" s="4"/>
@@ -30282,55 +30299,55 @@
     </x:row>
     <x:row r="28" spans="1:52" s="1" customFormat="1">
       <x:c r="A28" s="30" t="s">
-        <x:v>316</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B28" s="29" t="s">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D28" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E28" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D28" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E28" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F28" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G28" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H28" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H28" s="40">
         <x:v>46267</x:v>
       </x:c>
-      <x:c r="I28" s="41">
+      <x:c r="I28" s="40">
         <x:v>46267</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K28" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K28" s="41">
         <x:v>176000</x:v>
       </x:c>
-      <x:c r="L28" s="42">
+      <x:c r="L28" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="40">
+      <x:c r="M28" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N28" s="40">
+      <x:c r="N28" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O28" s="13">
         <x:v>0.54000000000000004</x:v>
       </x:c>
-      <x:c r="P28" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P28" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R28" s="4"/>
       <x:c r="S28" s="4"/>
@@ -30370,55 +30387,55 @@
     </x:row>
     <x:row r="29" spans="1:52" s="1" customFormat="1">
       <x:c r="A29" s="30" t="s">
-        <x:v>315</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B29" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D29" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E29" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D29" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E29" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F29" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G29" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H29" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H29" s="40">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="I29" s="41">
+      <x:c r="I29" s="40">
         <x:v>46268</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K29" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K29" s="41">
         <x:v>176000</x:v>
       </x:c>
-      <x:c r="L29" s="42">
+      <x:c r="L29" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40">
+      <x:c r="M29" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N29" s="40">
+      <x:c r="N29" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O29" s="13">
         <x:v>0.56000000000000005</x:v>
       </x:c>
-      <x:c r="P29" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P29" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q29" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R29" s="4"/>
       <x:c r="S29" s="4"/>
@@ -30458,25 +30475,25 @@
     </x:row>
     <x:row r="30" spans="1:52" s="1" customFormat="1">
       <x:c r="A30" s="30" t="s">
-        <x:v>322</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
-        <x:v>254</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E30" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F30" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G30" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H30" s="28">
         <x:v>46270</x:v>
@@ -30485,7 +30502,7 @@
         <x:v>46270</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>0</x:v>
@@ -30503,10 +30520,10 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="P30" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R30" s="4"/>
       <x:c r="S30" s="4"/>
@@ -30546,25 +30563,25 @@
     </x:row>
     <x:row r="31" spans="1:52" s="1" customFormat="1">
       <x:c r="A31" s="30" t="s">
-        <x:v>319</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B31" s="10" t="s">
-        <x:v>306</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E31" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F31" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G31" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H31" s="28">
         <x:v>46273</x:v>
@@ -30573,7 +30590,7 @@
         <x:v>46273</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K31" s="12">
         <x:v>0</x:v>
@@ -30590,11 +30607,11 @@
       <x:c r="O31" s="13">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="P31" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P31" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R31" s="4"/>
       <x:c r="S31" s="4"/>
@@ -30634,55 +30651,55 @@
     </x:row>
     <x:row r="32" spans="1:52" s="1" customFormat="1">
       <x:c r="A32" s="30" t="s">
-        <x:v>324</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B32" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C32" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D32" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E32" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D32" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E32" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F32" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G32" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H32" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H32" s="40">
         <x:v>46274</x:v>
       </x:c>
-      <x:c r="I32" s="41">
+      <x:c r="I32" s="40">
         <x:v>46274</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K32" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K32" s="41">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="L32" s="42">
+      <x:c r="L32" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="40">
+      <x:c r="M32" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N32" s="40">
+      <x:c r="N32" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O32" s="13">
         <x:v>0.58999999999999997</x:v>
       </x:c>
-      <x:c r="P32" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P32" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R32" s="4"/>
       <x:c r="S32" s="4"/>
@@ -30722,55 +30739,55 @@
     </x:row>
     <x:row r="33" spans="1:52" s="1" customFormat="1">
       <x:c r="A33" s="30" t="s">
-        <x:v>313</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B33" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C33" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D33" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E33" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D33" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E33" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F33" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G33" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H33" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H33" s="40">
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="I33" s="41">
+      <x:c r="I33" s="40">
         <x:v>46275</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K33" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K33" s="41">
         <x:v>80000</x:v>
       </x:c>
-      <x:c r="L33" s="42">
+      <x:c r="L33" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40">
+      <x:c r="M33" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N33" s="40">
+      <x:c r="N33" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O33" s="13">
         <x:v>0.60999999999999999</x:v>
       </x:c>
-      <x:c r="P33" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P33" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R33" s="4"/>
       <x:c r="S33" s="4"/>
@@ -30810,25 +30827,25 @@
     </x:row>
     <x:row r="34" spans="1:52" s="1" customFormat="1">
       <x:c r="A34" s="30" t="s">
-        <x:v>320</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B34" s="10" t="s">
-        <x:v>258</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E34" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F34" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G34" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H34" s="28">
         <x:v>46277</x:v>
@@ -30837,7 +30854,7 @@
         <x:v>46277</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K34" s="12">
         <x:v>0</x:v>
@@ -30855,10 +30872,10 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="P34" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R34" s="4"/>
       <x:c r="S34" s="4"/>
@@ -30898,55 +30915,55 @@
     </x:row>
     <x:row r="35" spans="1:52" s="1" customFormat="1">
       <x:c r="A35" s="30" t="s">
-        <x:v>321</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B35" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D35" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E35" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D35" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F35" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G35" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H35" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H35" s="40">
         <x:v>46281</x:v>
       </x:c>
-      <x:c r="I35" s="41">
+      <x:c r="I35" s="40">
         <x:v>46281</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K35" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K35" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L35" s="42">
+      <x:c r="L35" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40">
+      <x:c r="M35" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N35" s="40">
+      <x:c r="N35" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O35" s="13">
         <x:v>0.63</x:v>
       </x:c>
-      <x:c r="P35" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P35" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R35" s="4"/>
       <x:c r="S35" s="4"/>
@@ -30986,55 +31003,55 @@
     </x:row>
     <x:row r="36" spans="1:52" s="1" customFormat="1">
       <x:c r="A36" s="30" t="s">
-        <x:v>310</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B36" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D36" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E36" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D36" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E36" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F36" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G36" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H36" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H36" s="40">
         <x:v>46282</x:v>
       </x:c>
-      <x:c r="I36" s="41">
+      <x:c r="I36" s="40">
         <x:v>46282</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K36" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K36" s="41">
         <x:v>134000</x:v>
       </x:c>
-      <x:c r="L36" s="42">
+      <x:c r="L36" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M36" s="40">
+      <x:c r="M36" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N36" s="40">
+      <x:c r="N36" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O36" s="13">
         <x:v>0.66000000000000003</x:v>
       </x:c>
-      <x:c r="P36" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P36" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R36" s="4"/>
       <x:c r="S36" s="4"/>
@@ -31074,25 +31091,25 @@
     </x:row>
     <x:row r="37" spans="1:52" s="1" customFormat="1">
       <x:c r="A37" s="30" t="s">
-        <x:v>323</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B37" s="10" t="s">
-        <x:v>247</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C37" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E37" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F37" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G37" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H37" s="28">
         <x:v>46284</x:v>
@@ -31101,7 +31118,7 @@
         <x:v>46284</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K37" s="12">
         <x:v>0</x:v>
@@ -31119,10 +31136,10 @@
         <x:v>0.66000000000000003</x:v>
       </x:c>
       <x:c r="P37" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R37" s="4"/>
       <x:c r="S37" s="4"/>
@@ -31162,25 +31179,25 @@
     </x:row>
     <x:row r="38" spans="1:52" s="1" customFormat="1">
       <x:c r="A38" s="30" t="s">
-        <x:v>314</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B38" s="10" t="s">
-        <x:v>243</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C38" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E38" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F38" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G38" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H38" s="28">
         <x:v>46291</x:v>
@@ -31189,7 +31206,7 @@
         <x:v>46291</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K38" s="12">
         <x:v>0</x:v>
@@ -31207,10 +31224,10 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="P38" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R38" s="4"/>
       <x:c r="S38" s="4"/>
@@ -31250,55 +31267,55 @@
     </x:row>
     <x:row r="39" spans="1:52" s="1" customFormat="1">
       <x:c r="A39" s="30" t="s">
-        <x:v>317</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B39" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C39" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D39" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E39" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D39" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E39" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F39" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G39" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H39" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H39" s="40">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="I39" s="41">
+      <x:c r="I39" s="40">
         <x:v>46295</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K39" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K39" s="41">
         <x:v>92000</x:v>
       </x:c>
-      <x:c r="L39" s="42">
+      <x:c r="L39" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M39" s="40">
+      <x:c r="M39" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N39" s="40">
+      <x:c r="N39" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O39" s="13">
         <x:v>0.68000000000000005</x:v>
       </x:c>
-      <x:c r="P39" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P39" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R39" s="4"/>
       <x:c r="S39" s="4"/>
@@ -31338,55 +31355,55 @@
     </x:row>
     <x:row r="40" spans="1:52" s="1" customFormat="1">
       <x:c r="A40" s="30" t="s">
-        <x:v>318</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B40" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C40" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D40" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E40" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D40" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E40" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F40" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G40" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H40" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H40" s="40">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="I40" s="41">
+      <x:c r="I40" s="40">
         <x:v>46296</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K40" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K40" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L40" s="42">
+      <x:c r="L40" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M40" s="40">
+      <x:c r="M40" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N40" s="40">
+      <x:c r="N40" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O40" s="13">
         <x:v>0.69999999999999996</x:v>
       </x:c>
-      <x:c r="P40" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P40" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R40" s="4"/>
       <x:c r="S40" s="4"/>
@@ -31426,25 +31443,25 @@
     </x:row>
     <x:row r="41" spans="1:52" s="1" customFormat="1">
       <x:c r="A41" s="30" t="s">
-        <x:v>265</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B41" s="10" t="s">
-        <x:v>249</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C41" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E41" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F41" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G41" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H41" s="28">
         <x:v>46298</x:v>
@@ -31453,7 +31470,7 @@
         <x:v>46298</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K41" s="12">
         <x:v>0</x:v>
@@ -31471,10 +31488,10 @@
         <x:v>0.72999999999999998</x:v>
       </x:c>
       <x:c r="P41" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R41" s="4"/>
       <x:c r="S41" s="4"/>
@@ -31514,55 +31531,55 @@
     </x:row>
     <x:row r="42" spans="1:52" s="1" customFormat="1">
       <x:c r="A42" s="30" t="s">
-        <x:v>274</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B42" s="29" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C42" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D42" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E42" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D42" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E42" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F42" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G42" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H42" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H42" s="40">
         <x:v>46302</x:v>
       </x:c>
-      <x:c r="I42" s="41">
+      <x:c r="I42" s="40">
         <x:v>46302</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K42" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K42" s="41">
         <x:v>104000</x:v>
       </x:c>
-      <x:c r="L42" s="42">
+      <x:c r="L42" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="40">
+      <x:c r="M42" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N42" s="40">
+      <x:c r="N42" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O42" s="13">
         <x:v>0.71999999999999997</x:v>
       </x:c>
-      <x:c r="P42" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P42" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R42" s="4"/>
       <x:c r="S42" s="4"/>
@@ -31602,55 +31619,55 @@
     </x:row>
     <x:row r="43" spans="1:52" s="1" customFormat="1">
       <x:c r="A43" s="30" t="s">
-        <x:v>272</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B43" s="29" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D43" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E43" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D43" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E43" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F43" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G43" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H43" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H43" s="40">
         <x:v>46303</x:v>
       </x:c>
-      <x:c r="I43" s="41">
+      <x:c r="I43" s="40">
         <x:v>46303</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K43" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K43" s="41">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="L43" s="42">
+      <x:c r="L43" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M43" s="40">
+      <x:c r="M43" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N43" s="40">
+      <x:c r="N43" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O43" s="13">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="P43" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P43" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R43" s="4"/>
       <x:c r="S43" s="4"/>
@@ -31690,25 +31707,25 @@
     </x:row>
     <x:row r="44" spans="1:52" s="1" customFormat="1">
       <x:c r="A44" s="30" t="s">
-        <x:v>264</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B44" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C44" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E44" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F44" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G44" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H44" s="28">
         <x:v>46305</x:v>
@@ -31717,7 +31734,7 @@
         <x:v>46305</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>0</x:v>
@@ -31735,10 +31752,10 @@
         <x:v>0.76000000000000001</x:v>
       </x:c>
       <x:c r="P44" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R44" s="4"/>
       <x:c r="S44" s="4"/>
@@ -31778,25 +31795,25 @@
     </x:row>
     <x:row r="45" spans="1:52" s="1" customFormat="1">
       <x:c r="A45" s="30" t="s">
-        <x:v>276</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B45" s="10" t="s">
-        <x:v>312</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C45" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E45" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F45" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G45" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H45" s="28">
         <x:v>46308</x:v>
@@ -31805,7 +31822,7 @@
         <x:v>46308</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K45" s="12">
         <x:v>0</x:v>
@@ -31822,11 +31839,11 @@
       <x:c r="O45" s="13">
         <x:v>0.82999999999999996</x:v>
       </x:c>
-      <x:c r="P45" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P45" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R45" s="4"/>
       <x:c r="S45" s="4"/>
@@ -31866,55 +31883,55 @@
     </x:row>
     <x:row r="46" spans="1:52" s="1" customFormat="1">
       <x:c r="A46" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B46" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D46" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E46" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D46" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E46" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F46" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G46" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H46" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H46" s="40">
         <x:v>46309</x:v>
       </x:c>
-      <x:c r="I46" s="41">
+      <x:c r="I46" s="40">
         <x:v>46309</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K46" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K46" s="41">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="L46" s="42">
+      <x:c r="L46" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M46" s="40">
+      <x:c r="M46" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N46" s="40">
+      <x:c r="N46" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O46" s="13">
         <x:v>0.77000000000000002</x:v>
       </x:c>
-      <x:c r="P46" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P46" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R46" s="4"/>
       <x:c r="S46" s="4"/>
@@ -31954,55 +31971,55 @@
     </x:row>
     <x:row r="47" spans="1:52" s="1" customFormat="1">
       <x:c r="A47" s="30" t="s">
-        <x:v>269</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B47" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D47" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E47" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D47" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E47" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F47" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G47" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H47" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H47" s="40">
         <x:v>46310</x:v>
       </x:c>
-      <x:c r="I47" s="41">
+      <x:c r="I47" s="40">
         <x:v>46310</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K47" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K47" s="41">
         <x:v>134000</x:v>
       </x:c>
-      <x:c r="L47" s="42">
+      <x:c r="L47" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M47" s="40">
+      <x:c r="M47" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N47" s="40">
+      <x:c r="N47" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O47" s="13">
         <x:v>0.79000000000000004</x:v>
       </x:c>
-      <x:c r="P47" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P47" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R47" s="4"/>
       <x:c r="S47" s="4"/>
@@ -32042,25 +32059,25 @@
     </x:row>
     <x:row r="48" spans="1:52" s="1" customFormat="1">
       <x:c r="A48" s="30" t="s">
-        <x:v>266</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B48" s="10" t="s">
-        <x:v>341</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C48" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D48" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E48" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F48" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G48" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H48" s="28">
         <x:v>46312</x:v>
@@ -32069,7 +32086,7 @@
         <x:v>46312</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K48" s="12">
         <x:v>0</x:v>
@@ -32087,10 +32104,10 @@
         <x:v>0.80000000000000004</x:v>
       </x:c>
       <x:c r="P48" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R48" s="4"/>
       <x:c r="S48" s="4"/>
@@ -32130,55 +32147,55 @@
     </x:row>
     <x:row r="49" spans="1:52" s="1" customFormat="1">
       <x:c r="A49" s="30" t="s">
-        <x:v>267</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B49" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C49" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D49" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E49" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D49" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E49" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F49" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G49" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H49" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H49" s="40">
         <x:v>46316</x:v>
       </x:c>
-      <x:c r="I49" s="41">
+      <x:c r="I49" s="40">
         <x:v>46316</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K49" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K49" s="41">
         <x:v>76000</x:v>
       </x:c>
-      <x:c r="L49" s="42">
+      <x:c r="L49" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M49" s="40">
+      <x:c r="M49" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N49" s="40">
+      <x:c r="N49" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O49" s="13">
         <x:v>0.81000000000000005</x:v>
       </x:c>
-      <x:c r="P49" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P49" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R49" s="4"/>
       <x:c r="S49" s="4"/>
@@ -32218,55 +32235,55 @@
     </x:row>
     <x:row r="50" spans="1:52" s="1" customFormat="1">
       <x:c r="A50" s="30" t="s">
-        <x:v>271</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B50" s="29" t="s">
-        <x:v>106</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C50" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D50" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E50" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D50" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E50" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F50" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G50" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H50" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H50" s="40">
         <x:v>46317</x:v>
       </x:c>
-      <x:c r="I50" s="41">
+      <x:c r="I50" s="40">
         <x:v>46317</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K50" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K50" s="41">
         <x:v>176000</x:v>
       </x:c>
-      <x:c r="L50" s="42">
+      <x:c r="L50" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M50" s="40">
+      <x:c r="M50" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N50" s="40">
+      <x:c r="N50" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O50" s="13">
         <x:v>0.83999999999999997</x:v>
       </x:c>
-      <x:c r="P50" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P50" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R50" s="4"/>
       <x:c r="S50" s="4"/>
@@ -32306,25 +32323,25 @@
     </x:row>
     <x:row r="51" spans="1:52" s="1" customFormat="1">
       <x:c r="A51" s="30" t="s">
-        <x:v>262</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B51" s="10" t="s">
-        <x:v>350</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C51" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D51" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E51" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F51" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G51" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H51" s="28">
         <x:v>46319</x:v>
@@ -32333,7 +32350,7 @@
         <x:v>46319</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K51" s="12">
         <x:v>0</x:v>
@@ -32351,10 +32368,10 @@
         <x:v>0.82999999999999996</x:v>
       </x:c>
       <x:c r="P51" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R51" s="4"/>
       <x:c r="S51" s="4"/>
@@ -32394,55 +32411,55 @@
     </x:row>
     <x:row r="52" spans="1:52" s="1" customFormat="1">
       <x:c r="A52" s="30" t="s">
-        <x:v>292</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B52" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C52" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D52" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E52" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D52" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E52" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F52" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G52" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H52" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H52" s="40">
         <x:v>46323</x:v>
       </x:c>
-      <x:c r="I52" s="41">
+      <x:c r="I52" s="40">
         <x:v>46323</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K52" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K52" s="41">
         <x:v>92000</x:v>
       </x:c>
-      <x:c r="L52" s="42">
+      <x:c r="L52" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M52" s="40">
+      <x:c r="M52" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N52" s="40">
+      <x:c r="N52" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O52" s="13">
         <x:v>0.85999999999999999</x:v>
       </x:c>
-      <x:c r="P52" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P52" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R52" s="4"/>
       <x:c r="S52" s="4"/>
@@ -32482,55 +32499,55 @@
     </x:row>
     <x:row r="53" spans="1:52" s="1" customFormat="1">
       <x:c r="A53" s="30" t="s">
-        <x:v>278</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B53" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C53" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D53" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E53" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D53" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E53" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F53" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G53" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H53" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H53" s="40">
         <x:v>46324</x:v>
       </x:c>
-      <x:c r="I53" s="41">
+      <x:c r="I53" s="40">
         <x:v>46324</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K53" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K53" s="41">
         <x:v>134000</x:v>
       </x:c>
-      <x:c r="L53" s="42">
+      <x:c r="L53" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M53" s="40">
+      <x:c r="M53" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N53" s="40">
+      <x:c r="N53" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O53" s="13">
         <x:v>0.88</x:v>
       </x:c>
-      <x:c r="P53" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P53" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R53" s="4"/>
       <x:c r="S53" s="4"/>
@@ -32570,25 +32587,25 @@
     </x:row>
     <x:row r="54" spans="1:52" s="1" customFormat="1">
       <x:c r="A54" s="30" t="s">
-        <x:v>279</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B54" s="29" t="s">
-        <x:v>351</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C54" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D54" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E54" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F54" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G54" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H54" s="28">
         <x:v>46326</x:v>
@@ -32597,7 +32614,7 @@
         <x:v>46326</x:v>
       </x:c>
       <x:c r="J54" s="27" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K54" s="12">
         <x:v>0</x:v>
@@ -32614,11 +32631,11 @@
       <x:c r="O54" s="13">
         <x:v>0.91000000000000003</x:v>
       </x:c>
-      <x:c r="P54" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P54" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q54" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R54" s="4"/>
       <x:c r="S54" s="4"/>
@@ -32658,25 +32675,25 @@
     </x:row>
     <x:row r="55" spans="1:52" s="1" customFormat="1">
       <x:c r="A55" s="30" t="s">
-        <x:v>289</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B55" s="10" t="s">
-        <x:v>349</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C55" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D55" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E55" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F55" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G55" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H55" s="28">
         <x:v>46326</x:v>
@@ -32685,7 +32702,7 @@
         <x:v>46326</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K55" s="12">
         <x:v>0</x:v>
@@ -32703,10 +32720,10 @@
         <x:v>0.85999999999999999</x:v>
       </x:c>
       <x:c r="P55" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q55" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R55" s="4"/>
       <x:c r="S55" s="4"/>
@@ -32746,55 +32763,55 @@
     </x:row>
     <x:row r="56" spans="1:52" s="1" customFormat="1">
       <x:c r="A56" s="30" t="s">
-        <x:v>288</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B56" s="29" t="s">
-        <x:v>101</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C56" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D56" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E56" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D56" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E56" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F56" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G56" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H56" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H56" s="40">
         <x:v>46330</x:v>
       </x:c>
-      <x:c r="I56" s="41">
+      <x:c r="I56" s="40">
         <x:v>46330</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K56" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K56" s="41">
         <x:v>176000</x:v>
       </x:c>
-      <x:c r="L56" s="42">
+      <x:c r="L56" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M56" s="40">
+      <x:c r="M56" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N56" s="40">
+      <x:c r="N56" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O56" s="13">
         <x:v>0.90000000000000002</x:v>
       </x:c>
-      <x:c r="P56" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P56" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q56" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R56" s="4"/>
       <x:c r="S56" s="4"/>
@@ -32834,55 +32851,55 @@
     </x:row>
     <x:row r="57" spans="1:52" s="1" customFormat="1">
       <x:c r="A57" s="30" t="s">
-        <x:v>285</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B57" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D57" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E57" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D57" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E57" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F57" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G57" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H57" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H57" s="40">
         <x:v>46331</x:v>
       </x:c>
-      <x:c r="I57" s="41">
+      <x:c r="I57" s="40">
         <x:v>46331</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K57" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K57" s="41">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="L57" s="42">
+      <x:c r="L57" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M57" s="40">
+      <x:c r="M57" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N57" s="40">
+      <x:c r="N57" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O57" s="13">
         <x:v>0.93000000000000005</x:v>
       </x:c>
-      <x:c r="P57" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P57" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R57" s="4"/>
       <x:c r="S57" s="4"/>
@@ -32922,25 +32939,25 @@
     </x:row>
     <x:row r="58" spans="1:52" s="1" customFormat="1">
       <x:c r="A58" s="30" t="s">
-        <x:v>281</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B58" s="10" t="s">
-        <x:v>261</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C58" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D58" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E58" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F58" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G58" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H58" s="28">
         <x:v>46333</x:v>
@@ -32949,7 +32966,7 @@
         <x:v>46333</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K58" s="12">
         <x:v>0</x:v>
@@ -32967,10 +32984,10 @@
         <x:v>0.90000000000000002</x:v>
       </x:c>
       <x:c r="P58" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R58" s="4"/>
       <x:c r="S58" s="4"/>
@@ -33010,25 +33027,25 @@
     </x:row>
     <x:row r="59" spans="1:52" s="1" customFormat="1">
       <x:c r="A59" s="30" t="s">
-        <x:v>282</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B59" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C59" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D59" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E59" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F59" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G59" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H59" s="28">
         <x:v>46336</x:v>
@@ -33037,7 +33054,7 @@
         <x:v>46336</x:v>
       </x:c>
       <x:c r="J59" s="27" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K59" s="12">
         <x:v>0</x:v>
@@ -33054,11 +33071,11 @@
       <x:c r="O59" s="13">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P59" s="40" t="s">
-        <x:v>128</x:v>
+      <x:c r="P59" s="39" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R59" s="4"/>
       <x:c r="S59" s="4"/>
@@ -33098,55 +33115,55 @@
     </x:row>
     <x:row r="60" spans="1:52" s="1" customFormat="1">
       <x:c r="A60" s="30" t="s">
-        <x:v>263</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B60" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C60" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D60" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E60" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D60" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E60" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F60" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G60" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H60" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H60" s="40">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="I60" s="41">
+      <x:c r="I60" s="40">
         <x:v>46337</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K60" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K60" s="41">
         <x:v>176000</x:v>
       </x:c>
-      <x:c r="L60" s="42">
+      <x:c r="L60" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M60" s="40">
+      <x:c r="M60" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N60" s="40">
+      <x:c r="N60" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O60" s="13">
         <x:v>0.94999999999999996</x:v>
       </x:c>
-      <x:c r="P60" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P60" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q60" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R60" s="4"/>
       <x:c r="S60" s="4"/>
@@ -33186,55 +33203,55 @@
     </x:row>
     <x:row r="61" spans="1:52" s="1" customFormat="1">
       <x:c r="A61" s="30" t="s">
-        <x:v>283</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B61" s="29" t="s">
-        <x:v>105</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C61" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D61" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E61" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D61" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E61" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F61" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G61" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H61" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H61" s="40">
         <x:v>46338</x:v>
       </x:c>
-      <x:c r="I61" s="41">
+      <x:c r="I61" s="40">
         <x:v>46338</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K61" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K61" s="41">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="L61" s="42">
+      <x:c r="L61" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M61" s="40">
+      <x:c r="M61" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N61" s="40">
+      <x:c r="N61" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O61" s="13">
         <x:v>0.96999999999999997</x:v>
       </x:c>
-      <x:c r="P61" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P61" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q61" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R61" s="4"/>
       <x:c r="S61" s="4"/>
@@ -33274,25 +33291,25 @@
     </x:row>
     <x:row r="62" spans="1:52" s="1" customFormat="1">
       <x:c r="A62" s="30" t="s">
-        <x:v>286</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B62" s="10" t="s">
-        <x:v>273</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C62" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D62" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E62" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F62" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G62" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H62" s="28">
         <x:v>46340</x:v>
@@ -33301,7 +33318,7 @@
         <x:v>46340</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K62" s="12">
         <x:v>0</x:v>
@@ -33319,10 +33336,10 @@
         <x:v>0.93000000000000005</x:v>
       </x:c>
       <x:c r="P62" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q62" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R62" s="4"/>
       <x:c r="S62" s="4"/>
@@ -33362,25 +33379,25 @@
     </x:row>
     <x:row r="63" spans="1:52" s="1" customFormat="1">
       <x:c r="A63" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B63" s="10" t="s">
-        <x:v>248</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C63" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D63" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E63" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F63" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G63" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H63" s="28">
         <x:v>46347</x:v>
@@ -33389,7 +33406,7 @@
         <x:v>46347</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K63" s="12">
         <x:v>0</x:v>
@@ -33407,10 +33424,10 @@
         <x:v>0.95999999999999996</x:v>
       </x:c>
       <x:c r="P63" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q63" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R63" s="4"/>
       <x:c r="S63" s="4"/>
@@ -33450,55 +33467,55 @@
     </x:row>
     <x:row r="64" spans="1:52" s="1" customFormat="1">
       <x:c r="A64" s="30" t="s">
-        <x:v>287</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B64" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C64" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D64" s="40" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="E64" s="40" t="s">
-        <x:v>214</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D64" s="39" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E64" s="39" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F64" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G64" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H64" s="41">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H64" s="40">
         <x:v>46351</x:v>
       </x:c>
-      <x:c r="I64" s="41">
+      <x:c r="I64" s="40">
         <x:v>46351</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K64" s="42">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K64" s="41">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="L64" s="42">
+      <x:c r="L64" s="41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M64" s="40">
+      <x:c r="M64" s="39">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N64" s="40">
+      <x:c r="N64" s="39">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O64" s="13">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P64" s="43" t="s">
-        <x:v>361</x:v>
+      <x:c r="P64" s="42" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q64" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R64" s="4"/>
       <x:c r="S64" s="4"/>
@@ -33538,25 +33555,25 @@
     </x:row>
     <x:row r="65" spans="1:52" s="1" customFormat="1">
       <x:c r="A65" s="30" t="s">
-        <x:v>270</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B65" s="10" t="s">
-        <x:v>246</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C65" s="10" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D65" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E65" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F65" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G65" s="27" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H65" s="28">
         <x:v>46354</x:v>
@@ -33565,7 +33582,7 @@
         <x:v>46354</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K65" s="12">
         <x:v>0</x:v>
@@ -33583,10 +33600,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P65" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q65" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="R65" s="4"/>
       <x:c r="S65" s="4"/>
@@ -45244,18 +45261,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:52">
-      <x:c r="A1" s="44" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B1" s="44"/>
-      <x:c r="C1" s="44"/>
-      <x:c r="D1" s="44"/>
-      <x:c r="E1" s="44"/>
-      <x:c r="F1" s="44"/>
-      <x:c r="G1" s="44"/>
-      <x:c r="H1" s="44"/>
-      <x:c r="I1" s="44"/>
-      <x:c r="J1" s="44"/>
+      <x:c r="A1" s="43" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
+      <x:c r="I1" s="43"/>
+      <x:c r="J1" s="43"/>
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
       <x:c r="M1" s="4"/>
@@ -45300,16 +45317,16 @@
       <x:c r="AZ1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:52">
-      <x:c r="A2" s="44"/>
-      <x:c r="B2" s="44"/>
-      <x:c r="C2" s="44"/>
-      <x:c r="D2" s="44"/>
-      <x:c r="E2" s="44"/>
-      <x:c r="F2" s="44"/>
-      <x:c r="G2" s="44"/>
-      <x:c r="H2" s="44"/>
-      <x:c r="I2" s="44"/>
-      <x:c r="J2" s="44"/>
+      <x:c r="A2" s="43"/>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+      <x:c r="F2" s="43"/>
+      <x:c r="G2" s="43"/>
+      <x:c r="H2" s="43"/>
+      <x:c r="I2" s="43"/>
+      <x:c r="J2" s="43"/>
       <x:c r="K2" s="4"/>
       <x:c r="L2" s="4"/>
       <x:c r="M2" s="4"/>
@@ -45354,18 +45371,18 @@
       <x:c r="AZ2" s="4"/>
     </x:row>
     <x:row r="3" spans="1:52">
-      <x:c r="A3" s="47" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="B3" s="47"/>
-      <x:c r="C3" s="47"/>
-      <x:c r="D3" s="47"/>
-      <x:c r="E3" s="47"/>
-      <x:c r="F3" s="47"/>
-      <x:c r="G3" s="47"/>
-      <x:c r="H3" s="47"/>
-      <x:c r="I3" s="47"/>
-      <x:c r="J3" s="47"/>
+      <x:c r="A3" s="46" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="46"/>
+      <x:c r="C3" s="46"/>
+      <x:c r="D3" s="46"/>
+      <x:c r="E3" s="46"/>
+      <x:c r="F3" s="46"/>
+      <x:c r="G3" s="46"/>
+      <x:c r="H3" s="46"/>
+      <x:c r="I3" s="46"/>
+      <x:c r="J3" s="46"/>
       <x:c r="K3" s="4"/>
       <x:c r="L3" s="4"/>
       <x:c r="M3" s="4"/>
@@ -45464,26 +45481,26 @@
       <x:c r="AZ4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:52">
-      <x:c r="A5" s="48" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="B5" s="48"/>
-      <x:c r="C5" s="48" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="D5" s="48"/>
-      <x:c r="E5" s="48" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F5" s="48"/>
-      <x:c r="G5" s="48" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H5" s="48"/>
-      <x:c r="I5" s="48" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="J5" s="48"/>
+      <x:c r="A5" s="47" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B5" s="47"/>
+      <x:c r="C5" s="47" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D5" s="47"/>
+      <x:c r="E5" s="47" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F5" s="47"/>
+      <x:c r="G5" s="47" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H5" s="47"/>
+      <x:c r="I5" s="47" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J5" s="47"/>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
@@ -45528,16 +45545,16 @@
       <x:c r="AZ5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:52">
-      <x:c r="A6" s="48"/>
-      <x:c r="B6" s="48"/>
-      <x:c r="C6" s="48"/>
-      <x:c r="D6" s="48"/>
-      <x:c r="E6" s="48"/>
-      <x:c r="F6" s="48"/>
-      <x:c r="G6" s="48"/>
-      <x:c r="H6" s="48"/>
-      <x:c r="I6" s="48"/>
-      <x:c r="J6" s="48"/>
+      <x:c r="A6" s="47"/>
+      <x:c r="B6" s="47"/>
+      <x:c r="C6" s="47"/>
+      <x:c r="D6" s="47"/>
+      <x:c r="E6" s="47"/>
+      <x:c r="F6" s="47"/>
+      <x:c r="G6" s="47"/>
+      <x:c r="H6" s="47"/>
+      <x:c r="I6" s="47"/>
+      <x:c r="J6" s="47"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
@@ -45582,31 +45599,31 @@
       <x:c r="AZ6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:52">
-      <x:c r="A7" s="49">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$B$5:$B$200,"&lt;&gt;")</x:f>
+      <x:c r="A7" s="48">
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$B$5:$B$198,"&lt;&gt;")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B7" s="49"/>
-      <x:c r="C7" s="49">
-        <x:f ca="1">COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$V$5:$V$200,"&gt;="&amp;TODAY(),기도대상자관리!$V$5:$V$200,"&lt;="&amp;TODAY()+7)</x:f>
+      <x:c r="B7" s="48"/>
+      <x:c r="C7" s="48">
+        <x:f ca="1">COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$V$5:$V$198,"&gt;="&amp;TODAY(),기도대상자관리!$V$5:$V$198,"&lt;="&amp;TODAY()+7)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="49"/>
-      <x:c r="E7" s="49">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,"교회방문")+COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,"새가족")+COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,"등록교인")+COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,"군우편입")</x:f>
+      <x:c r="D7" s="48"/>
+      <x:c r="E7" s="48">
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,"교회방문")+COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,"새가족")+COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,"등록교인")+COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,"군우편입")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="49"/>
-      <x:c r="G7" s="49">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,"군우편입")</x:f>
+      <x:c r="F7" s="48"/>
+      <x:c r="G7" s="48">
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,"군우편입")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H7" s="49"/>
-      <x:c r="I7" s="49">
+      <x:c r="H7" s="48"/>
+      <x:c r="I7" s="48">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$245,"진행중",일만상상프로젝트!$B$5:$B$245,"&lt;&gt;")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J7" s="49"/>
+      <x:c r="J7" s="48"/>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
@@ -45651,16 +45668,16 @@
       <x:c r="AZ7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:52">
-      <x:c r="A8" s="49"/>
-      <x:c r="B8" s="49"/>
-      <x:c r="C8" s="49"/>
-      <x:c r="D8" s="49"/>
-      <x:c r="E8" s="49"/>
-      <x:c r="F8" s="49"/>
-      <x:c r="G8" s="49"/>
-      <x:c r="H8" s="49"/>
-      <x:c r="I8" s="49"/>
-      <x:c r="J8" s="49"/>
+      <x:c r="A8" s="48"/>
+      <x:c r="B8" s="48"/>
+      <x:c r="C8" s="48"/>
+      <x:c r="D8" s="48"/>
+      <x:c r="E8" s="48"/>
+      <x:c r="F8" s="48"/>
+      <x:c r="G8" s="48"/>
+      <x:c r="H8" s="48"/>
+      <x:c r="I8" s="48"/>
+      <x:c r="J8" s="48"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
@@ -45760,23 +45777,23 @@
     </x:row>
     <x:row r="10" spans="1:52">
       <x:c r="A10" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B10" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="15" t="s">
-        <x:v>167</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F10" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>196</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
@@ -45826,10 +45843,10 @@
     </x:row>
     <x:row r="11" spans="1:52">
       <x:c r="A11" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A11)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A11)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="13">
@@ -45838,7 +45855,7 @@
       </x:c>
       <x:c r="D11" s="4"/>
       <x:c r="E11" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F11" s="4">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$245,E11,일만상상프로젝트!$B$5:$B$245,"&lt;&gt;")</x:f>
@@ -45896,10 +45913,10 @@
     </x:row>
     <x:row r="12" spans="1:52">
       <x:c r="A12" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B12" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A12)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A12)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="13">
@@ -45908,7 +45925,7 @@
       </x:c>
       <x:c r="D12" s="4"/>
       <x:c r="E12" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F12" s="4">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$245,E12,일만상상프로젝트!$B$5:$B$245,"&lt;&gt;")</x:f>
@@ -45966,10 +45983,10 @@
     </x:row>
     <x:row r="13" spans="1:52">
       <x:c r="A13" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A13)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A13)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="13">
@@ -45978,7 +45995,7 @@
       </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F13" s="4">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$245,E13,일만상상프로젝트!$B$5:$B$245,"&lt;&gt;")</x:f>
@@ -46036,10 +46053,10 @@
     </x:row>
     <x:row r="14" spans="1:52">
       <x:c r="A14" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B14" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A14)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="13">
@@ -46048,7 +46065,7 @@
       </x:c>
       <x:c r="D14" s="4"/>
       <x:c r="E14" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F14" s="4">
         <x:f>COUNTIFS(일만상상프로젝트!$J$5:$J$245,E14,일만상상프로젝트!$B$5:$B$245,"&lt;&gt;")</x:f>
@@ -46106,10 +46123,10 @@
     </x:row>
     <x:row r="15" spans="1:52">
       <x:c r="A15" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B15" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A15)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="13">
@@ -46168,10 +46185,10 @@
     </x:row>
     <x:row r="16" spans="1:52">
       <x:c r="A16" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B16" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A16)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="13">
@@ -46230,10 +46247,10 @@
     </x:row>
     <x:row r="17" spans="1:52">
       <x:c r="A17" s="4" t="s">
-        <x:v>187</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B17" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A17)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="13">
@@ -46292,10 +46309,10 @@
     </x:row>
     <x:row r="18" spans="1:52">
       <x:c r="A18" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B18" s="4">
-        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$200,"사용",기도대상자관리!$L$5:$L$200,A18)</x:f>
+        <x:f>COUNTIFS(기도대상자관리!$AD$5:$AD$198,"사용",기도대상자관리!$L$5:$L$198,A18)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="13">
@@ -46407,18 +46424,18 @@
       <x:c r="AZ19" s="4"/>
     </x:row>
     <x:row r="20" spans="1:52">
-      <x:c r="A20" s="50" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B20" s="50"/>
-      <x:c r="C20" s="50"/>
-      <x:c r="D20" s="50"/>
-      <x:c r="E20" s="50"/>
-      <x:c r="F20" s="50"/>
-      <x:c r="G20" s="50"/>
-      <x:c r="H20" s="50"/>
-      <x:c r="I20" s="50"/>
-      <x:c r="J20" s="50"/>
+      <x:c r="A20" s="49" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B20" s="49"/>
+      <x:c r="C20" s="49"/>
+      <x:c r="D20" s="49"/>
+      <x:c r="E20" s="49"/>
+      <x:c r="F20" s="49"/>
+      <x:c r="G20" s="49"/>
+      <x:c r="H20" s="49"/>
+      <x:c r="I20" s="49"/>
+      <x:c r="J20" s="49"/>
       <x:c r="K20" s="4"/>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="4"/>
@@ -57304,34 +57321,34 @@
   <x:sheetData>
     <x:row r="1" spans="1:52">
       <x:c r="A1" s="16" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B1" s="16" t="s">
-        <x:v>142</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C1" s="16" t="s">
-        <x:v>158</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D1" s="16" t="s">
-        <x:v>162</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E1" s="16" t="s">
-        <x:v>161</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F1" s="16" t="s">
-        <x:v>154</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G1" s="16" t="s">
-        <x:v>163</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H1" s="16" t="s">
-        <x:v>183</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="I1" s="16" t="s">
-        <x:v>179</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="J1" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
@@ -57378,34 +57395,34 @@
     </x:row>
     <x:row r="2" spans="1:52">
       <x:c r="A2" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K2" s="4"/>
       <x:c r="L2" s="4"/>
@@ -57452,34 +57469,34 @@
     </x:row>
     <x:row r="3" spans="1:52">
       <x:c r="A3" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E3" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F3" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G3" s="4" t="s">
-        <x:v>203</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J3" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K3" s="4"/>
       <x:c r="L3" s="4"/>
@@ -57527,29 +57544,29 @@
     <x:row r="4" spans="1:52">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4" t="s">
-        <x:v>207</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="J4" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
@@ -57597,29 +57614,29 @@
     <x:row r="5" spans="1:52">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>185</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
@@ -57667,25 +57684,25 @@
     <x:row r="6" spans="1:52">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="J6" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
@@ -57733,22 +57750,22 @@
     <x:row r="7" spans="1:52">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
@@ -57798,17 +57815,17 @@
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="4"/>
       <x:c r="C8" s="4" t="s">
-        <x:v>187</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
@@ -57858,7 +57875,7 @@
       <x:c r="A9" s="4"/>
       <x:c r="B9" s="4"/>
       <x:c r="C9" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D9" s="4"/>
       <x:c r="E9" s="4"/>
@@ -57866,7 +57883,7 @@
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -57916,7 +57933,7 @@
       <x:c r="A10" s="4"/>
       <x:c r="B10" s="4"/>
       <x:c r="C10" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="4"/>
@@ -57924,7 +57941,7 @@
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
@@ -69322,88 +69339,88 @@
   <x:dimension ref="A1:D7"/>
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" style="34" customWidth="1"/>
-    <x:col min="2" max="2" width="16" style="34" customWidth="1"/>
-    <x:col min="3" max="3" width="42" style="34" customWidth="1"/>
-    <x:col min="4" max="4" width="24" style="34" customWidth="1"/>
+    <x:col min="1" max="1" width="22" style="33" customWidth="1"/>
+    <x:col min="2" max="2" width="16" style="33" customWidth="1"/>
+    <x:col min="3" max="3" width="42" style="33" customWidth="1"/>
+    <x:col min="4" max="4" width="24" style="33" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="30" customHeight="1">
-      <x:c r="A1" s="51" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="B1" s="51"/>
-      <x:c r="C1" s="51"/>
-      <x:c r="D1" s="51"/>
+      <x:c r="A1" s="50" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B1" s="50"/>
+      <x:c r="C1" s="50"/>
+      <x:c r="D1" s="50"/>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="35" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B3" s="35" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C3" s="35" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D3" s="35" t="s">
-        <x:v>175</x:v>
+      <x:c r="A3" s="34" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B3" s="34" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C3" s="34" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D3" s="34" t="s">
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="36" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="B4" s="37">
+      <x:c r="A4" s="35" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B4" s="36">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="38" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="D4" s="38" t="s">
-        <x:v>337</x:v>
+      <x:c r="C4" s="37" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D4" s="37" t="s">
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="36" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="B5" s="37">
+      <x:c r="A5" s="35" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B5" s="36">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="D5" s="38" t="s">
-        <x:v>337</x:v>
+      <x:c r="C5" s="37" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="s">
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="36" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="B6" s="37">
+      <x:c r="A6" s="35" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B6" s="36">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="C6" s="38" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="D6" s="38" t="s">
-        <x:v>327</x:v>
+      <x:c r="C6" s="37" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="37" t="s">
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
-      <x:c r="A7" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B7" s="39" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C7" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D7" s="38" t="s">
-        <x:v>326</x:v>
+      <x:c r="A7" s="35" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B7" s="38" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="s">
+        <x:v>375</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
